--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I85" headerRowCount="1">
-  <autoFilter ref="A1:I85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I70" headerRowCount="1">
+  <autoFilter ref="A1:I70"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,27 +491,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,17 +541,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -571,17 +576,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -606,17 +611,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -641,17 +646,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -676,17 +681,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -711,17 +716,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -746,17 +751,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -781,17 +786,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -802,41 +807,31 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -851,32 +846,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CVE-2026-58612</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-62815</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1851,32 +1851,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1909,9 +1909,14 @@
           <t>""</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1926,27 +1931,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1957,36 +1962,31 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
+          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-50376</t>
+          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2051,22 +2051,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-62880</t>
+          <t>CVE-2026-50376</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2091,22 +2091,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CVE-2026-62768</t>
+          <t>CVE-2026-62880</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2121,37 +2121,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-62768</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2176,7 +2171,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2186,17 +2181,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
+          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2221,7 +2216,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2231,12 +2226,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2271,17 +2271,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-20281</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>7.5</t>
+          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2306,7 +2301,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2316,17 +2311,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-20212</t>
+          <t>CVE-2026-20281</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2341,27 +2336,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CVE-2026-20212</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2386,17 +2391,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2421,17 +2426,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2456,17 +2461,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2491,17 +2496,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2526,17 +2531,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2561,17 +2566,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2596,17 +2601,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2631,17 +2636,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2666,17 +2671,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
+          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
+          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2687,41 +2692,31 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"SonicWall SMA1000 Series Appliances Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-83548 - Pre-authentication SSRF via unintended forward-proxy A Pre-authentication SSRF vulnerability exists in the SMA1000 Appliance Work Place interface due to an unintended alternate access path. A remote unauthenticated attacker could potentially exploit this vulnerability to gain unauthorized access to sensitive functionality and perform unauthorized operations.. CVSS Score: 10.0 CVSS Vector: CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H CWE-918: Server-Side Request Forgery (SSRF) CWE-441: Unintended Proxy or Intermediary ('Confused Deputy') 2) CVE-2026-83549 - Post-authentication Remote Code Execution (RCE) Vulnerability Post-authentication Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability has been identified in the SMA1000 Appliance Management Console (AMC) which in specific conditions could potentially enable a remote authenticated attacker as administrator to execute arbitrary OS commands, resulting in remote code execution. CVSS Score: 7.8 CVSS Vector: CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') IMPORTANT: SonicWall PSIRT has investigated a case indicating the active exploitation of the vulnerabilities described in this advisory. Customers are strongly urged to upgrade to the hotfix release as soon as possible to remediate this vulnerability. CVE: CVE-2026-83548, CVE-2026-83549 Last updated: Sept. 1, 2026, 5:43 a.m.""</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>CVE-2026-83548, CVE-2026-83549</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0016</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2736,32 +2731,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"MFSA 2026-84 Security Vulnerabilities fixed in Firefox ESR 140.15"</t>
+          <t>"SonicWall SMA1000 Series Appliances Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""1) CVE-2026-83548 - Pre-authentication SSRF via unintended forward-proxy A Pre-authentication SSRF vulnerability exists in the SMA1000 Appliance Work Place interface due to an unintended alternate access path. A remote unauthenticated attacker could potentially exploit this vulnerability to gain unauthorized access to sensitive functionality and perform unauthorized operations.. CVSS Score: 10.0 CVSS Vector: CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H CWE-918: Server-Side Request Forgery (SSRF) CWE-441: Unintended Proxy or Intermediary ('Confused Deputy') 2) CVE-2026-83549 - Post-authentication Remote Code Execution (RCE) Vulnerability Post-authentication Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability has been identified in the SMA1000 Appliance Management Console (AMC) which in specific conditions could potentially enable a remote authenticated attacker as administrator to execute arbitrary OS commands, resulting in remote code execution. CVSS Score: 7.8 CVSS Vector: CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') IMPORTANT: SonicWall PSIRT has investigated a case indicating the active exploitation of the vulnerabilities described in this advisory. Customers are strongly urged to upgrade to the hotfix release as soon as possible to remediate this vulnerability. CVE: CVE-2026-83548, CVE-2026-83549 Last updated: Sept. 1, 2026, 5:43 a.m.""</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-16371, CVE-2026-75874, CVE-2026-16365, CVE-2026-84143, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84124, CVE-2026-84122, CVE-2026-84120</t>
+          <t>CVE-2026-83548, CVE-2026-83549</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-84/</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0016</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2776,32 +2776,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"MFSA 2026-85 Security Vulnerabilities fixed in Firefox ESR 153.2"</t>
+          <t>"Automated workflow email notifications disabled"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-74952, CVE-2026-84131, CVE-2026-84140, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-75874, CVE-2026-84136, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84144</t>
+          <t>""Sep 1 , 13:34 EDT Resolved - The ability to send emails through an automated workflow has been been restored. Sep 1 , 13:33 EDT Update - The ability to send emails through an automated workflow has been been restored. Aug 31 , 18:56 EDT Investigating - The ability to send emails through an automated workflow has been temporarily disabled. We will post an update when this functionality is restored.""</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-85/</t>
+          <t>https://status.sharefile.com/incidents/tpf30l4kyq08</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2826,7 +2821,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"MFSA 2026-82 Security Vulnerabilities fixed in Firefox 155"</t>
+          <t>"MFSA 2026-84 Security Vulnerabilities fixed in Firefox ESR 140.15"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2836,12 +2831,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-84131, CVE-2026-84126, CVE-2026-84140, CVE-2026-84142, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84138, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84135, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-84128, CVE-2026-84136, CVE-2026-84117, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84127, CVE-2026-84144</t>
+          <t>CVE-2026-16371, CVE-2026-75874, CVE-2026-16365, CVE-2026-84143, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84124, CVE-2026-84122, CVE-2026-84120</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-82/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-84/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2866,7 +2861,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"MFSA 2026-83 Security Vulnerabilities fixed in Firefox ESR 115.40"</t>
+          <t>"MFSA 2026-85 Security Vulnerabilities fixed in Firefox ESR 153.2"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2876,12 +2871,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CVE-2026-75874, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84120</t>
+          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-74952, CVE-2026-84131, CVE-2026-84140, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-75874, CVE-2026-84136, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84144</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-83/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-85/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2906,7 +2901,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"MFSA 2026-87 Security Vulnerabilities fixed in Thunderbird 140.15"</t>
+          <t>"MFSA 2026-82 Security Vulnerabilities fixed in Firefox 155"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2916,12 +2911,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CVE-2026-75874, CVE-2026-84119, CVE-2026-84124, CVE-2026-84641, CVE-2026-84639, CVE-2026-84145, CVE-2026-84640, CVE-2026-84131, CVE-2026-84121, CVE-2026-84120, CVE-2026-16371, CVE-2026-84122, CVE-2026-16365, CVE-2026-84143</t>
+          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-84131, CVE-2026-84126, CVE-2026-84140, CVE-2026-84142, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84138, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84135, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-84128, CVE-2026-84136, CVE-2026-84117, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84127, CVE-2026-84144</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-87/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-82/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2946,7 +2941,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"MFSA 2026-88 Security Vulnerabilities fixed in Thunderbird 153.2"</t>
+          <t>"MFSA 2026-83 Security Vulnerabilities fixed in Firefox ESR 115.40"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2956,12 +2951,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CVE-2026-84141, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-74952, CVE-2026-84133, CVE-2026-84639, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-75874, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84637, CVE-2026-84139, CVE-2026-84143</t>
+          <t>CVE-2026-75874, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84120</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-88/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-83/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2986,7 +2981,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"MFSA 2026-86 Security Vulnerabilities fixed in Thunderbird 155"</t>
+          <t>"MFSA 2026-87 Security Vulnerabilities fixed in Thunderbird 140.15"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2996,12 +2991,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CVE-2026-84141, CVE-2026-84138, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-84133, CVE-2026-84639, CVE-2026-84126, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84128, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84139, CVE-2026-84142, CVE-2026-84143</t>
+          <t>CVE-2026-75874, CVE-2026-84119, CVE-2026-84124, CVE-2026-84641, CVE-2026-84639, CVE-2026-84145, CVE-2026-84640, CVE-2026-84131, CVE-2026-84121, CVE-2026-84120, CVE-2026-16371, CVE-2026-84122, CVE-2026-16365, CVE-2026-84143</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-86/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-87/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3016,32 +3011,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"MFSA 2026-88 Security Vulnerabilities fixed in Thunderbird 153.2"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>"Microsoft is aware of the recent Chromium security fixes. We are actively working on releasing a security fix."</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVE-2021-36929, CVE-2021-30551, CVE-2025-21267, CVE-2026-11645, CVE-2023-4863, CVE-2022-23264, CVE-2023-35618, CVE-2024-49025, CVE-2020-16013, CVE-2023-38174, CVE-2024-0519, CVE-2026-66314, CVE-2023-21720, CVE-2024-21423, CVE-2022-33639, CVE-2022-21930, CVE-2025-21262, CVE-2022-29146, CVE-2026-66323, CVE-2023-36880, CVE-2026-0385, CVE-2026-66310, CVE-2022-22021, CVE-2022-26891, CVE-2021-34475, CVE-2021-37973, CVE-2024-21399, CVE-2026-66311, CVE-2023-2033, CVE-2025-53791, CVE-2025-47964, CVE-2024-30057, CVE-2023-21795, CVE-2025-26643, CVE-2024-43578, CVE-2022-26899, CVE-2020-16009, CVE-2024-30056, CVE-2024-7965, CVE-2023-36741, CVE-2025-21404, CVE-2022-3723, CVE-2021-30633, CVE-2024-2883, CVE-2026-72970, CVE-2024-38221, CVE-2026-33118, CVE-2022-33636, CVE-2022-1364, CVE-2026-70341, CVE-2021-4102, CVE-2026-5281, CVE-2021-43220, CVE-2023-28301, CVE-2024-38103, CVE-2024-30058, CVE-2023-36014, CVE-2024-29991, CVE-2026-66312, CVE-2026-66317, CVE-2026-45494, CVE-2023-36026, CVE-2024-38210, CVE-2023-29334, CVE-2023-36878, CVE-2024-38209, CVE-2025-47963, CVE-2025-21279, CVE-2025-24201, CVE-2024-26192, CVE-2022-26908, CVE-2023-7024, CVE-2021-38641, CVE-2023-21796, CVE-2025-10585, CVE-2022-4262, CVE-2024-43577, CVE-2021-21193, CVE-2022-2856, CVE-2021-43221, CVE-2026-41107, CVE-2024-43595, CVE-2021-30563, CVE-2025-5419, CVE-2023-5217, CVE-2025-6554, CVE-2024-49041, CVE-2024-21383, CVE-2023-36727, CVE-2021-36928, CVE-2021-37976, CVE-2023-28286, CVE-2024-38207, CVE-2021-21166, CVE-2020-16017, CVE-2023-33145, CVE-2026-66316, CVE-2022-26912, CVE-2024-29986, CVE-2022-44708, CVE-2023-23374, CVE-2022-3075, CVE-2025-21342, CVE-2021-33741, CVE-2020-6418, CVE-2024-21388, CVE-2023-24935, CVE-2024-21336, CVE-2025-29795, CVE-2021-36931, CVE-2026-42838, CVE-2022-33680, CVE-2023-0941, CVE-2026-62904, CVE-2024-20675, CVE-2026-45495, CVE-2023-38158, CVE-2022-29144, CVE-2022-0609, CVE-2024-38082, CVE-2024-20709, CVE-2022-1096, CVE-2025-25000, CVE-2026-3909, CVE-2026-3910, CVE-2024-38093, CVE-2023-36008, CVE-2026-0102, CVE-2025-6558, CVE-2025-21408, CVE-2023-36559, CVE-2024-21385, CVE-2021-30632, CVE-2025-29825, CVE-2021-31982, CVE-2024-43496, CVE-2021-38669, CVE-2023-29354, CVE-2024-26188, CVE-2024-4947, CVE-2026-72984, CVE-2024-26196, CVE-2023-29350, CVE-2024-30055, CVE-2022-38012, CVE-2025-60711, CVE-2022-30127, CVE-2022-33649, CVE-2022-23258, CVE-2024-29049, CVE-2021-34506, CVE-2025-49713, CVE-2024-43566, CVE-2024-43472, CVE-2021-21148, CVE-2023-35392, CVE-2022-2294, CVE-2022-21931, CVE-2024-20721, CVE-2024-41879, CVE-2023-36887, CVE-2023-38173, CVE-2024-4671, CVE-2024-26247, CVE-2023-21719, CVE-2021-21220, CVE-2024-26167, CVE-2025-21185, CVE-2025-21253, CVE-2023-36562, CVE-2023-21794, CVE-2023-28284, CVE-2022-23263, CVE-2026-66326, CVE-2023-38187, CVE-2022-26895, CVE-2025-21401, CVE-2023-36024, CVE-2022-29147, CVE-2021-26436, CVE-2025-21399, CVE-2026-65802, CVE-2025-47182, CVE-2022-30128, CVE-2024-38208, CVE-2024-21387, CVE-2026-66322, CVE-2024-7971, CVE-2021-37975, CVE-2021-38642, CVE-2025-13223, CVE-2025-29834, CVE-2024-49023, CVE-2022-33638, CVE-2021-38000, CVE-2026-33119, CVE-2023-36735, CVE-2021-36930, CVE-2023-44323, CVE-2022-44688, CVE-2024-4761, CVE-2023-36022, CVE-2020-1341, CVE-2022-41115, CVE-2020-1195, CVE-2024-29981, CVE-2025-47181, CVE-2022-21954, CVE-2024-49054, CVE-2024-43489, CVE-2022-21970, CVE-2026-58616, CVE-2026-66798, CVE-2022-24523, CVE-2025-4664, CVE-2022-24475, CVE-2024-43579, CVE-2024-5274, CVE-2025-29796, CVE-2023-3079, CVE-2023-33143, CVE-2026-66315, CVE-2022-26909, CVE-2026-66325, CVE-2024-38156, CVE-2023-38157, CVE-2021-21224, CVE-2021-21206, CVE-2021-31937, CVE-2022-23261, CVE-2024-43580, CVE-2021-24113, CVE-2023-36787, CVE-2021-42308, CVE-2024-38219, CVE-2023-28261, CVE-2022-26894, CVE-2023-36029, CVE-2021-26439, CVE-2025-2783, CVE-2024-39379, CVE-2026-65804, CVE-2023-36888, CVE-2024-43587, CVE-2024-38222, CVE-2023-36034, CVE-2026-66324, CVE-2024-21382, CVE-2022-41035, CVE-2026-66318, CVE-2024-21326, CVE-2022-35796, CVE-2026-40416, CVE-2020-15999, CVE-2024-29057, CVE-2025-21283, CVE-2022-30192, CVE-2025-62223, CVE-2024-38083, CVE-2023-6345, CVE-2022-4135, CVE-2021-38003, CVE-2021-30554, CVE-2026-66321, CVE-2022-21929, CVE-2024-29987, CVE-2023-36883, CVE-2022-26900, CVE-2026-21223, CVE-2023-21775, CVE-2026-66313, CVE-2025-47967, CVE-2022-26905, CVE-2024-26163, CVE-2023-2136, CVE-2024-38218, CVE-2024-43596, CVE-2023-29345, CVE-2022-23262, CVE-2026-2441, CVE-2024-21337, CVE-2023-36027, CVE-2026-45492, CVE-2026-26133, CVE-2024-26246</t>
+          <t>CVE-2026-84141, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-74952, CVE-2026-84133, CVE-2026-84639, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-75874, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84637, CVE-2026-84139, CVE-2026-84143</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-1-2026</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-88/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3056,17 +3051,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"MFSA 2026-86 Security Vulnerabilities fixed in Thunderbird 155"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3076,12 +3071,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CVE-2026-84335, CVE-2026-84356, CVE-2026-84358, CVE-2026-84354, CVE-2026-84351, CVE-2026-84330, CVE-2026-84353, CVE-2026-84352, CVE-2026-84324, CVE-2026-84334, CVE-2026-84328, CVE-2026-84355, CVE-2026-84357, CVE-2026-84326, CVE-2026-84325, CVE-2026-84327, CVE-2026-84347, CVE-2026-84349, CVE-2026-84329, CVE-2026-84331, CVE-2026-84323, CVE-2026-84350, CVE-2026-84359, CVE-2026-84333, CVE-2026-84332, CVE-2026-84348</t>
+          <t>CVE-2026-84141, CVE-2026-84138, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-84133, CVE-2026-84639, CVE-2026-84126, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84128, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84139, CVE-2026-84142, CVE-2026-84143</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop.html</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-86/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3092,31 +3087,36 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Automated workflow email notifications disabled"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""Aug 31 , 18:56 EDT Investigating - The ability to send emails through an automated workflow has been temporarily disabled. We will post an update when this functionality is restored.""</t>
+          <t>"Microsoft is aware of the recent Chromium security fixes. We are actively working on releasing a security fix."</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CVE-2021-36929, CVE-2021-30551, CVE-2025-21267, CVE-2026-11645, CVE-2023-4863, CVE-2022-23264, CVE-2023-35618, CVE-2024-49025, CVE-2020-16013, CVE-2023-38174, CVE-2024-0519, CVE-2026-66314, CVE-2023-21720, CVE-2024-21423, CVE-2022-33639, CVE-2022-21930, CVE-2025-21262, CVE-2022-29146, CVE-2026-66323, CVE-2023-36880, CVE-2026-0385, CVE-2026-66310, CVE-2022-22021, CVE-2022-26891, CVE-2021-34475, CVE-2021-37973, CVE-2024-21399, CVE-2026-66311, CVE-2023-2033, CVE-2025-53791, CVE-2025-47964, CVE-2024-30057, CVE-2023-21795, CVE-2025-26643, CVE-2024-43578, CVE-2022-26899, CVE-2020-16009, CVE-2024-30056, CVE-2024-7965, CVE-2023-36741, CVE-2025-21404, CVE-2022-3723, CVE-2021-30633, CVE-2024-2883, CVE-2026-72970, CVE-2024-38221, CVE-2026-33118, CVE-2022-33636, CVE-2022-1364, CVE-2026-70341, CVE-2021-4102, CVE-2026-5281, CVE-2021-43220, CVE-2023-28301, CVE-2024-38103, CVE-2024-30058, CVE-2023-36014, CVE-2024-29991, CVE-2026-66312, CVE-2026-66317, CVE-2026-45494, CVE-2023-36026, CVE-2024-38210, CVE-2023-29334, CVE-2023-36878, CVE-2024-38209, CVE-2025-47963, CVE-2025-21279, CVE-2025-24201, CVE-2024-26192, CVE-2022-26908, CVE-2023-7024, CVE-2021-38641, CVE-2023-21796, CVE-2025-10585, CVE-2022-4262, CVE-2024-43577, CVE-2021-21193, CVE-2022-2856, CVE-2021-43221, CVE-2026-41107, CVE-2024-43595, CVE-2021-30563, CVE-2025-5419, CVE-2023-5217, CVE-2025-6554, CVE-2024-49041, CVE-2024-21383, CVE-2023-36727, CVE-2021-36928, CVE-2021-37976, CVE-2023-28286, CVE-2024-38207, CVE-2021-21166, CVE-2020-16017, CVE-2023-33145, CVE-2026-66316, CVE-2022-26912, CVE-2024-29986, CVE-2022-44708, CVE-2023-23374, CVE-2022-3075, CVE-2025-21342, CVE-2021-33741, CVE-2020-6418, CVE-2024-21388, CVE-2023-24935, CVE-2024-21336, CVE-2025-29795, CVE-2021-36931, CVE-2026-42838, CVE-2022-33680, CVE-2023-0941, CVE-2026-62904, CVE-2024-20675, CVE-2026-45495, CVE-2023-38158, CVE-2022-29144, CVE-2022-0609, CVE-2024-38082, CVE-2024-20709, CVE-2022-1096, CVE-2025-25000, CVE-2026-3909, CVE-2026-3910, CVE-2024-38093, CVE-2023-36008, CVE-2026-0102, CVE-2025-6558, CVE-2025-21408, CVE-2023-36559, CVE-2024-21385, CVE-2021-30632, CVE-2025-29825, CVE-2021-31982, CVE-2024-43496, CVE-2021-38669, CVE-2023-29354, CVE-2024-26188, CVE-2024-4947, CVE-2026-72984, CVE-2024-26196, CVE-2023-29350, CVE-2024-30055, CVE-2022-38012, CVE-2025-60711, CVE-2022-30127, CVE-2022-33649, CVE-2022-23258, CVE-2024-29049, CVE-2021-34506, CVE-2025-49713, CVE-2024-43566, CVE-2024-43472, CVE-2021-21148, CVE-2023-35392, CVE-2022-2294, CVE-2022-21931, CVE-2024-20721, CVE-2024-41879, CVE-2023-36887, CVE-2023-38173, CVE-2024-4671, CVE-2024-26247, CVE-2023-21719, CVE-2021-21220, CVE-2024-26167, CVE-2025-21185, CVE-2025-21253, CVE-2023-36562, CVE-2023-21794, CVE-2023-28284, CVE-2022-23263, CVE-2026-66326, CVE-2023-38187, CVE-2022-26895, CVE-2025-21401, CVE-2023-36024, CVE-2022-29147, CVE-2021-26436, CVE-2025-21399, CVE-2026-65802, CVE-2025-47182, CVE-2022-30128, CVE-2024-38208, CVE-2024-21387, CVE-2026-66322, CVE-2024-7971, CVE-2021-37975, CVE-2021-38642, CVE-2025-13223, CVE-2025-29834, CVE-2024-49023, CVE-2022-33638, CVE-2021-38000, CVE-2026-33119, CVE-2023-36735, CVE-2021-36930, CVE-2023-44323, CVE-2022-44688, CVE-2024-4761, CVE-2023-36022, CVE-2020-1341, CVE-2022-41115, CVE-2020-1195, CVE-2024-29981, CVE-2025-47181, CVE-2022-21954, CVE-2024-49054, CVE-2024-43489, CVE-2022-21970, CVE-2026-58616, CVE-2026-66798, CVE-2022-24523, CVE-2025-4664, CVE-2022-24475, CVE-2024-43579, CVE-2024-5274, CVE-2025-29796, CVE-2023-3079, CVE-2023-33143, CVE-2026-66315, CVE-2022-26909, CVE-2026-66325, CVE-2024-38156, CVE-2023-38157, CVE-2021-21224, CVE-2021-21206, CVE-2021-31937, CVE-2022-23261, CVE-2024-43580, CVE-2021-24113, CVE-2023-36787, CVE-2021-42308, CVE-2024-38219, CVE-2023-28261, CVE-2022-26894, CVE-2023-36029, CVE-2021-26439, CVE-2025-2783, CVE-2024-39379, CVE-2026-65804, CVE-2023-36888, CVE-2024-43587, CVE-2024-38222, CVE-2023-36034, CVE-2026-66324, CVE-2024-21382, CVE-2022-41035, CVE-2026-66318, CVE-2024-21326, CVE-2022-35796, CVE-2026-40416, CVE-2020-15999, CVE-2024-29057, CVE-2025-21283, CVE-2022-30192, CVE-2025-62223, CVE-2024-38083, CVE-2023-6345, CVE-2022-4135, CVE-2021-38003, CVE-2021-30554, CVE-2026-66321, CVE-2022-21929, CVE-2024-29987, CVE-2023-36883, CVE-2022-26900, CVE-2026-21223, CVE-2023-21775, CVE-2026-66313, CVE-2025-47967, CVE-2022-26905, CVE-2024-26163, CVE-2023-2136, CVE-2024-38218, CVE-2024-43596, CVE-2023-29345, CVE-2022-23262, CVE-2026-2441, CVE-2024-21337, CVE-2023-36027, CVE-2026-45492, CVE-2026-26133, CVE-2024-26246</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/tpf30l4kyq08</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-1-2026</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3127,21 +3127,21 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"MFSA 2026-81 Security Vulnerabilities fixed in Firefox for iOS 155.0"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3151,605 +3151,15 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CVE-2026-81267</t>
+          <t>CVE-2026-84335, CVE-2026-84356, CVE-2026-84358, CVE-2026-84354, CVE-2026-84351, CVE-2026-84330, CVE-2026-84353, CVE-2026-84352, CVE-2026-84324, CVE-2026-84334, CVE-2026-84328, CVE-2026-84355, CVE-2026-84357, CVE-2026-84326, CVE-2026-84325, CVE-2026-84327, CVE-2026-84347, CVE-2026-84349, CVE-2026-84329, CVE-2026-84331, CVE-2026-84323, CVE-2026-84350, CVE-2026-84359, CVE-2026-84333, CVE-2026-84332, CVE-2026-84348</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-81/</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop.html</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Microsoft Edge Security Updates</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>"Microsoft Edge Security Updates"</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android and iOS (Version 152.0.4191.53) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>CVE-2024-49025, CVE-2023-36024, CVE-2024-38222, CVE-2026-66325, CVE-2025-49713, CVE-2026-45495, CVE-2024-26167, CVE-2021-30632, CVE-2024-38156, CVE-2020-1341, CVE-2025-4664, CVE-2025-47963, CVE-2024-38210, CVE-2022-4262, CVE-2023-24935, CVE-2022-33639, CVE-2026-66315, CVE-2021-21224, CVE-2026-40416, CVE-2022-29147, CVE-2021-21193, CVE-2024-30055, CVE-2024-38209, CVE-2026-2441, CVE-2023-2136, CVE-2023-38157, CVE-2024-43472, CVE-2021-4102, CVE-2022-21970, CVE-2024-38093, CVE-2022-26891, CVE-2024-43587, CVE-2025-6554, CVE-2022-41115, CVE-2022-26895, CVE-2022-26908, CVE-2021-30633, CVE-2022-26905, CVE-2022-0609, CVE-2022-26899, CVE-2024-20721, CVE-2022-26912, CVE-2026-70341, CVE-2021-38003, CVE-2025-29825, CVE-2021-37975, CVE-2021-36929, CVE-2024-43496, CVE-2024-43566, CVE-2024-38221, CVE-2023-36741, CVE-2025-21408, CVE-2022-26909, CVE-2023-36559, CVE-2026-66326, CVE-2024-26196, CVE-2021-30563, CVE-2024-43579, CVE-2024-29987, CVE-2023-36562, CVE-2024-49054, CVE-2024-5274, CVE-2024-21388, CVE-2024-21383, CVE-2026-66312, CVE-2021-38669, CVE-2026-66324, CVE-2024-20675, CVE-2023-36878, CVE-2023-33143, CVE-2023-2033, CVE-2024-26188, CVE-2023-36888, CVE-2026-66311, CVE-2026-21223, CVE-2024-30057, CVE-2026-33118, CVE-2021-30551, CVE-2025-60711, CVE-2026-66314, CVE-2023-36026, CVE-2022-26900, CVE-2022-30128, CVE-2022-24475, CVE-2026-66318, CVE-2022-33638, CVE-2022-35796, CVE-2026-65804, CVE-2025-21185, CVE-2022-22021, CVE-2022-4135, CVE-2020-16009, CVE-2023-36014, CVE-2025-24201, CVE-2023-21775, CVE-2022-38012, CVE-2021-21148, CVE-2026-42838, CVE-2026-3909, CVE-2025-21399, CVE-2020-16013, CVE-2023-28301, CVE-2024-38207, CVE-2026-66798, CVE-2022-1364, CVE-2024-7971, CVE-2021-37976, CVE-2025-2783, CVE-2025-10585, CVE-2023-36027, CVE-2023-28284, CVE-2025-47964, CVE-2023-36008, CVE-2025-13223, CVE-2023-0941, CVE-2023-21719, CVE-2021-38642, CVE-2024-7965, CVE-2021-43220, CVE-2026-65802, CVE-2026-0385, CVE-2022-41035, CVE-2024-29057, CVE-2022-21931, CVE-2025-29796, CVE-2025-25000, CVE-2026-62904, CVE-2025-53791, CVE-2023-5217, CVE-2024-21326, CVE-2026-45492, CVE-2025-29834, CVE-2022-23264, CVE-2024-26246, CVE-2022-3075, CVE-2023-21796, CVE-2025-5419, CVE-2022-29146, CVE-2022-3723, CVE-2024-43595, CVE-2026-41107, CVE-2026-66316, CVE-2024-4671, CVE-2026-26133, CVE-2024-21382, CVE-2026-72970, CVE-2023-33145, CVE-2022-23262, CVE-2024-30058, CVE-2022-33649, CVE-2021-31982, CVE-2024-2883, CVE-2025-21342, CVE-2024-38218, CVE-2025-29795, CVE-2022-33680, CVE-2020-1195, CVE-2026-66313, CVE-2026-66322, CVE-2026-5281, CVE-2025-47967, CVE-2024-49041, CVE-2023-36029, CVE-2020-15999, CVE-2024-0519, CVE-2021-37973, CVE-2025-21283, CVE-2022-21930, CVE-2023-21795, CVE-2022-23258, CVE-2024-29981, CVE-2024-21387, CVE-2022-33636, CVE-2021-26439, CVE-2024-43580, CVE-2023-38158, CVE-2021-36931, CVE-2022-2294, CVE-2023-23374, CVE-2025-21404, CVE-2025-62223, CVE-2021-30554, CVE-2022-29144, CVE-2020-16017, CVE-2024-43489, CVE-2021-34506, CVE-2021-21166, CVE-2026-11645, CVE-2021-34475, CVE-2022-44688, CVE-2024-4761, CVE-2024-39379, CVE-2023-38187, CVE-2026-3910, CVE-2026-45494, CVE-2024-26247, CVE-2023-36787, CVE-2023-29345, CVE-2024-38208, CVE-2026-58616, CVE-2025-21279, CVE-2024-26192, CVE-2024-21423, CVE-2023-21720, CVE-2022-1096, CVE-2022-21929, CVE-2023-36880, CVE-2022-24523, CVE-2021-21206, CVE-2021-21220, CVE-2024-49023, CVE-2024-43578, CVE-2023-28261, CVE-2025-26643, CVE-2021-38641, CVE-2022-30192, CVE-2024-38083, CVE-2026-0102, CVE-2024-29986, CVE-2026-33119, CVE-2024-38103, CVE-2023-28286, CVE-2024-38082, CVE-2024-29049, CVE-2023-3079, CVE-2023-29354, CVE-2022-30127, CVE-2022-26894, CVE-2021-31937, CVE-2024-26163, CVE-2021-24113, CVE-2026-72984, CVE-2025-47181, CVE-2024-4947, CVE-2024-29991, CVE-2023-36034, CVE-2023-44323, CVE-2023-4863, CVE-2024-43577, CVE-2023-36883, CVE-2023-36887, CVE-2021-43221, CVE-2020-6418, CVE-2022-23261, CVE-2022-2856, CVE-2021-42308, CVE-2023-7024, CVE-2023-36735, CVE-2026-66310, CVE-2022-21954, CVE-2023-35618, CVE-2023-36022, CVE-2024-21336, CVE-2021-36930, CVE-2025-21267, CVE-2025-21401, CVE-2024-41879, CVE-2021-38000, CVE-2024-20709, CVE-2024-38219, CVE-2022-44708, CVE-2025-47182, CVE-2021-33741, CVE-2024-21399, CVE-2023-21794, CVE-2023-38174, CVE-2024-21337, CVE-2026-66317, CVE-2026-66321, CVE-2023-36727, CVE-2024-21385, CVE-2023-29350, CVE-2023-38173, CVE-2023-29334, CVE-2025-21262, CVE-2022-23263, CVE-2024-30056, CVE-2021-26436, CVE-2024-43596, CVE-2021-36928, CVE-2025-6558, CVE-2023-6345, CVE-2023-35392, CVE-2026-66323, CVE-2025-21253</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#august-31-2026</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>"CVE-2026-26174 Windows Server Update Service (WSUS) Elevation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>CVE-2026-26174</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-26174</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>"CVE-2026-62823 Windows DHCP Server Remote Code Execution Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>CVE-2026-62823</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62823</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>"CVE-2026-50344 Windows OLE Elevation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>CVE-2026-50344</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50344</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>"CVE-2026-65776 Windows Win32k Elevation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>CVE-2026-65776</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-65776</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>"CVE-2026-65775 Windows Win32k Elevation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>CVE-2026-65775</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-65775</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>"CVE-2026-62889 Windows Secure Socket Tunneling Protocol (SSTP) Remote Code Execution Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>CVE-2026-62889</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62889</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>"CVE-2026-50462 Windows Ancillary Function Driver for WinSock Elevation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>CVE-2026-50462</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50462</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>"CVE-2026-64899 Microsoft Office Information Disclosure Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>CVE-2026-64899</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-64899</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>"CVE-2026-55134 Microsoft Word Remote Code Execution Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>CVE-2026-55134</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-55134</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>"CVE-2026-49177 Windows TCP/IP Information Disclosure Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>CVE-2026-49177</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-49177</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>"CVE-2026-59134 Remote Desktop Client Remote Code Execution Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>CVE-2026-59134</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-59134</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Microsoft Edge</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>"CVE-2026-50448 Windows NTFS Remote Code Execution Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>CVE-2026-50448</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50448</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>"HPESBHF05127 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>""HPESBHF05127 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05127en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>46264</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>ShareFile</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>https://status.sharefile.com/history.rss</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>"ShareFile Regular Maintenance Notification"</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>""THIS IS A SCHEDULED EVENT Aug 30 , 00:30 - 04:30 EDT Aug 24 , 06:38 EDT Scheduled - ShareFile eSignature will undergo scheduled maintenance on Sunday, August 30, 2026, from 12:30 AM to 4:30 AM ET (04:30 AM to 08:30 AM UTC). During this maintenance window, ShareFile eSignature and RightSignature are expected to be unavailable. Full service will be restored as soon as the maintenance is complete. This site will be updated once maintenance is complete or as additional information becomes available.""</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>https://status.sharefile.com/incidents/kz2dgptz2yqy</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I70" headerRowCount="1">
-  <autoFilter ref="A1:I70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I71" headerRowCount="1">
+  <autoFilter ref="A1:I71"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,36 +487,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -531,27 +526,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -576,17 +576,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -611,17 +611,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -681,17 +681,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -716,17 +716,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -751,17 +751,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -842,41 +842,31 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -891,32 +881,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-58612</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -941,7 +936,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -951,12 +946,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-62815</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -981,22 +976,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1021,7 +1016,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1031,12 +1026,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1061,7 +1056,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1071,12 +1066,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1111,12 +1106,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1141,7 +1136,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1151,12 +1146,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1181,7 +1176,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1191,12 +1186,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1221,7 +1216,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1231,12 +1226,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1261,7 +1256,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1271,12 +1266,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1301,7 +1296,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1311,12 +1306,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1341,7 +1336,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1351,12 +1346,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1381,7 +1376,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1391,12 +1386,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1421,7 +1416,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1431,12 +1426,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1461,7 +1456,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1471,12 +1466,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1501,7 +1496,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1511,12 +1506,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1541,7 +1536,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1551,12 +1546,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1581,7 +1576,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1591,12 +1586,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1621,7 +1616,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1631,12 +1626,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1671,12 +1666,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1701,7 +1696,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1711,12 +1706,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1741,7 +1736,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1751,12 +1746,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1781,7 +1776,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1791,12 +1786,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1821,7 +1816,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1831,12 +1826,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1861,7 +1856,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1871,12 +1866,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1891,32 +1886,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,17 +1926,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1949,9 +1944,14 @@
           <t>""</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1966,27 +1966,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1997,36 +1997,31 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
+          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2041,32 +2036,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-50376</t>
+          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2091,22 +2086,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CVE-2026-62880</t>
+          <t>CVE-2026-50376</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2131,22 +2126,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-62768</t>
+          <t>CVE-2026-62880</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2161,37 +2156,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-62768</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2216,7 +2206,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2226,17 +2216,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
+          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2261,7 +2251,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2271,12 +2261,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2301,7 +2296,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2311,17 +2306,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-20281</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>7.5</t>
+          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2346,7 +2336,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2356,17 +2346,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-20212</t>
+          <t>CVE-2026-20281</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2381,27 +2371,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CVE-2026-20212</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2636,17 +2636,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2671,17 +2671,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
+          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
+          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2727,41 +2727,31 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"SonicWall SMA1000 Series Appliances Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-83548 - Pre-authentication SSRF via unintended forward-proxy A Pre-authentication SSRF vulnerability exists in the SMA1000 Appliance Work Place interface due to an unintended alternate access path. A remote unauthenticated attacker could potentially exploit this vulnerability to gain unauthorized access to sensitive functionality and perform unauthorized operations.. CVSS Score: 10.0 CVSS Vector: CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H CWE-918: Server-Side Request Forgery (SSRF) CWE-441: Unintended Proxy or Intermediary ('Confused Deputy') 2) CVE-2026-83549 - Post-authentication Remote Code Execution (RCE) Vulnerability Post-authentication Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability has been identified in the SMA1000 Appliance Management Console (AMC) which in specific conditions could potentially enable a remote authenticated attacker as administrator to execute arbitrary OS commands, resulting in remote code execution. CVSS Score: 7.8 CVSS Vector: CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') IMPORTANT: SonicWall PSIRT has investigated a case indicating the active exploitation of the vulnerabilities described in this advisory. Customers are strongly urged to upgrade to the hotfix release as soon as possible to remediate this vulnerability. CVE: CVE-2026-83548, CVE-2026-83549 Last updated: Sept. 1, 2026, 5:43 a.m.""</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>CVE-2026-83548, CVE-2026-83549</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0016</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2776,27 +2766,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"Automated workflow email notifications disabled"</t>
+          <t>"SonicWall SMA1000 Series Appliances Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""Sep 1 , 13:34 EDT Resolved - The ability to send emails through an automated workflow has been been restored. Sep 1 , 13:33 EDT Update - The ability to send emails through an automated workflow has been been restored. Aug 31 , 18:56 EDT Investigating - The ability to send emails through an automated workflow has been temporarily disabled. We will post an update when this functionality is restored.""</t>
+          <t>""1) CVE-2026-83548 - Pre-authentication SSRF via unintended forward-proxy A Pre-authentication SSRF vulnerability exists in the SMA1000 Appliance Work Place interface due to an unintended alternate access path. A remote unauthenticated attacker could potentially exploit this vulnerability to gain unauthorized access to sensitive functionality and perform unauthorized operations.. CVSS Score: 10.0 CVSS Vector: CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H CWE-918: Server-Side Request Forgery (SSRF) CWE-441: Unintended Proxy or Intermediary ('Confused Deputy') 2) CVE-2026-83549 - Post-authentication Remote Code Execution (RCE) Vulnerability Post-authentication Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability has been identified in the SMA1000 Appliance Management Console (AMC) which in specific conditions could potentially enable a remote authenticated attacker as administrator to execute arbitrary OS commands, resulting in remote code execution. CVSS Score: 7.8 CVSS Vector: CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') IMPORTANT: SonicWall PSIRT has investigated a case indicating the active exploitation of the vulnerabilities described in this advisory. Customers are strongly urged to upgrade to the hotfix release as soon as possible to remediate this vulnerability. CVE: CVE-2026-83548, CVE-2026-83549 Last updated: Sept. 1, 2026, 5:43 a.m.""</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CVE-2026-83548, CVE-2026-83549</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/tpf30l4kyq08</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0016</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2811,32 +2811,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"MFSA 2026-84 Security Vulnerabilities fixed in Firefox ESR 140.15"</t>
+          <t>"Automated workflow email notifications disabled"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>CVE-2026-16371, CVE-2026-75874, CVE-2026-16365, CVE-2026-84143, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84124, CVE-2026-84122, CVE-2026-84120</t>
+          <t>""Sep 1 , 13:34 EDT Resolved - The ability to send emails through an automated workflow has been been restored. Sep 1 , 13:33 EDT Update - The ability to send emails through an automated workflow has been been restored. Aug 31 , 18:56 EDT Investigating - The ability to send emails through an automated workflow has been temporarily disabled. We will post an update when this functionality is restored.""</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-84/</t>
+          <t>https://status.sharefile.com/incidents/tpf30l4kyq08</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2861,7 +2856,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"MFSA 2026-85 Security Vulnerabilities fixed in Firefox ESR 153.2"</t>
+          <t>"MFSA 2026-84 Security Vulnerabilities fixed in Firefox ESR 140.15"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2871,12 +2866,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-74952, CVE-2026-84131, CVE-2026-84140, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-75874, CVE-2026-84136, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84144</t>
+          <t>CVE-2026-16371, CVE-2026-75874, CVE-2026-16365, CVE-2026-84143, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84124, CVE-2026-84122, CVE-2026-84120</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-85/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-84/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2901,7 +2896,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"MFSA 2026-82 Security Vulnerabilities fixed in Firefox 155"</t>
+          <t>"MFSA 2026-85 Security Vulnerabilities fixed in Firefox ESR 153.2"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2911,12 +2906,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-84131, CVE-2026-84126, CVE-2026-84140, CVE-2026-84142, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84138, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84135, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-84128, CVE-2026-84136, CVE-2026-84117, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84127, CVE-2026-84144</t>
+          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-74952, CVE-2026-84131, CVE-2026-84140, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-75874, CVE-2026-84136, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84144</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-82/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-85/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2941,7 +2936,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"MFSA 2026-83 Security Vulnerabilities fixed in Firefox ESR 115.40"</t>
+          <t>"MFSA 2026-82 Security Vulnerabilities fixed in Firefox 155"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2951,12 +2946,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CVE-2026-75874, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84120</t>
+          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-84131, CVE-2026-84126, CVE-2026-84140, CVE-2026-84142, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84138, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84135, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-84128, CVE-2026-84136, CVE-2026-84117, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84127, CVE-2026-84144</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-83/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-82/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2981,7 +2976,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"MFSA 2026-87 Security Vulnerabilities fixed in Thunderbird 140.15"</t>
+          <t>"MFSA 2026-83 Security Vulnerabilities fixed in Firefox ESR 115.40"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2991,12 +2986,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CVE-2026-75874, CVE-2026-84119, CVE-2026-84124, CVE-2026-84641, CVE-2026-84639, CVE-2026-84145, CVE-2026-84640, CVE-2026-84131, CVE-2026-84121, CVE-2026-84120, CVE-2026-16371, CVE-2026-84122, CVE-2026-16365, CVE-2026-84143</t>
+          <t>CVE-2026-75874, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84120</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-87/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-83/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3021,7 +3016,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"MFSA 2026-88 Security Vulnerabilities fixed in Thunderbird 153.2"</t>
+          <t>"MFSA 2026-87 Security Vulnerabilities fixed in Thunderbird 140.15"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3031,12 +3026,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVE-2026-84141, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-74952, CVE-2026-84133, CVE-2026-84639, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-75874, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84637, CVE-2026-84139, CVE-2026-84143</t>
+          <t>CVE-2026-75874, CVE-2026-84119, CVE-2026-84124, CVE-2026-84641, CVE-2026-84639, CVE-2026-84145, CVE-2026-84640, CVE-2026-84131, CVE-2026-84121, CVE-2026-84120, CVE-2026-16371, CVE-2026-84122, CVE-2026-16365, CVE-2026-84143</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-88/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-87/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3061,7 +3056,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"MFSA 2026-86 Security Vulnerabilities fixed in Thunderbird 155"</t>
+          <t>"MFSA 2026-88 Security Vulnerabilities fixed in Thunderbird 153.2"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3071,12 +3066,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CVE-2026-84141, CVE-2026-84138, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-84133, CVE-2026-84639, CVE-2026-84126, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84128, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84139, CVE-2026-84142, CVE-2026-84143</t>
+          <t>CVE-2026-84141, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-74952, CVE-2026-84133, CVE-2026-84639, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-75874, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84637, CVE-2026-84139, CVE-2026-84143</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-86/</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-88/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3091,32 +3086,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"MFSA 2026-86 Security Vulnerabilities fixed in Thunderbird 155"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>"Microsoft is aware of the recent Chromium security fixes. We are actively working on releasing a security fix."</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CVE-2021-36929, CVE-2021-30551, CVE-2025-21267, CVE-2026-11645, CVE-2023-4863, CVE-2022-23264, CVE-2023-35618, CVE-2024-49025, CVE-2020-16013, CVE-2023-38174, CVE-2024-0519, CVE-2026-66314, CVE-2023-21720, CVE-2024-21423, CVE-2022-33639, CVE-2022-21930, CVE-2025-21262, CVE-2022-29146, CVE-2026-66323, CVE-2023-36880, CVE-2026-0385, CVE-2026-66310, CVE-2022-22021, CVE-2022-26891, CVE-2021-34475, CVE-2021-37973, CVE-2024-21399, CVE-2026-66311, CVE-2023-2033, CVE-2025-53791, CVE-2025-47964, CVE-2024-30057, CVE-2023-21795, CVE-2025-26643, CVE-2024-43578, CVE-2022-26899, CVE-2020-16009, CVE-2024-30056, CVE-2024-7965, CVE-2023-36741, CVE-2025-21404, CVE-2022-3723, CVE-2021-30633, CVE-2024-2883, CVE-2026-72970, CVE-2024-38221, CVE-2026-33118, CVE-2022-33636, CVE-2022-1364, CVE-2026-70341, CVE-2021-4102, CVE-2026-5281, CVE-2021-43220, CVE-2023-28301, CVE-2024-38103, CVE-2024-30058, CVE-2023-36014, CVE-2024-29991, CVE-2026-66312, CVE-2026-66317, CVE-2026-45494, CVE-2023-36026, CVE-2024-38210, CVE-2023-29334, CVE-2023-36878, CVE-2024-38209, CVE-2025-47963, CVE-2025-21279, CVE-2025-24201, CVE-2024-26192, CVE-2022-26908, CVE-2023-7024, CVE-2021-38641, CVE-2023-21796, CVE-2025-10585, CVE-2022-4262, CVE-2024-43577, CVE-2021-21193, CVE-2022-2856, CVE-2021-43221, CVE-2026-41107, CVE-2024-43595, CVE-2021-30563, CVE-2025-5419, CVE-2023-5217, CVE-2025-6554, CVE-2024-49041, CVE-2024-21383, CVE-2023-36727, CVE-2021-36928, CVE-2021-37976, CVE-2023-28286, CVE-2024-38207, CVE-2021-21166, CVE-2020-16017, CVE-2023-33145, CVE-2026-66316, CVE-2022-26912, CVE-2024-29986, CVE-2022-44708, CVE-2023-23374, CVE-2022-3075, CVE-2025-21342, CVE-2021-33741, CVE-2020-6418, CVE-2024-21388, CVE-2023-24935, CVE-2024-21336, CVE-2025-29795, CVE-2021-36931, CVE-2026-42838, CVE-2022-33680, CVE-2023-0941, CVE-2026-62904, CVE-2024-20675, CVE-2026-45495, CVE-2023-38158, CVE-2022-29144, CVE-2022-0609, CVE-2024-38082, CVE-2024-20709, CVE-2022-1096, CVE-2025-25000, CVE-2026-3909, CVE-2026-3910, CVE-2024-38093, CVE-2023-36008, CVE-2026-0102, CVE-2025-6558, CVE-2025-21408, CVE-2023-36559, CVE-2024-21385, CVE-2021-30632, CVE-2025-29825, CVE-2021-31982, CVE-2024-43496, CVE-2021-38669, CVE-2023-29354, CVE-2024-26188, CVE-2024-4947, CVE-2026-72984, CVE-2024-26196, CVE-2023-29350, CVE-2024-30055, CVE-2022-38012, CVE-2025-60711, CVE-2022-30127, CVE-2022-33649, CVE-2022-23258, CVE-2024-29049, CVE-2021-34506, CVE-2025-49713, CVE-2024-43566, CVE-2024-43472, CVE-2021-21148, CVE-2023-35392, CVE-2022-2294, CVE-2022-21931, CVE-2024-20721, CVE-2024-41879, CVE-2023-36887, CVE-2023-38173, CVE-2024-4671, CVE-2024-26247, CVE-2023-21719, CVE-2021-21220, CVE-2024-26167, CVE-2025-21185, CVE-2025-21253, CVE-2023-36562, CVE-2023-21794, CVE-2023-28284, CVE-2022-23263, CVE-2026-66326, CVE-2023-38187, CVE-2022-26895, CVE-2025-21401, CVE-2023-36024, CVE-2022-29147, CVE-2021-26436, CVE-2025-21399, CVE-2026-65802, CVE-2025-47182, CVE-2022-30128, CVE-2024-38208, CVE-2024-21387, CVE-2026-66322, CVE-2024-7971, CVE-2021-37975, CVE-2021-38642, CVE-2025-13223, CVE-2025-29834, CVE-2024-49023, CVE-2022-33638, CVE-2021-38000, CVE-2026-33119, CVE-2023-36735, CVE-2021-36930, CVE-2023-44323, CVE-2022-44688, CVE-2024-4761, CVE-2023-36022, CVE-2020-1341, CVE-2022-41115, CVE-2020-1195, CVE-2024-29981, CVE-2025-47181, CVE-2022-21954, CVE-2024-49054, CVE-2024-43489, CVE-2022-21970, CVE-2026-58616, CVE-2026-66798, CVE-2022-24523, CVE-2025-4664, CVE-2022-24475, CVE-2024-43579, CVE-2024-5274, CVE-2025-29796, CVE-2023-3079, CVE-2023-33143, CVE-2026-66315, CVE-2022-26909, CVE-2026-66325, CVE-2024-38156, CVE-2023-38157, CVE-2021-21224, CVE-2021-21206, CVE-2021-31937, CVE-2022-23261, CVE-2024-43580, CVE-2021-24113, CVE-2023-36787, CVE-2021-42308, CVE-2024-38219, CVE-2023-28261, CVE-2022-26894, CVE-2023-36029, CVE-2021-26439, CVE-2025-2783, CVE-2024-39379, CVE-2026-65804, CVE-2023-36888, CVE-2024-43587, CVE-2024-38222, CVE-2023-36034, CVE-2026-66324, CVE-2024-21382, CVE-2022-41035, CVE-2026-66318, CVE-2024-21326, CVE-2022-35796, CVE-2026-40416, CVE-2020-15999, CVE-2024-29057, CVE-2025-21283, CVE-2022-30192, CVE-2025-62223, CVE-2024-38083, CVE-2023-6345, CVE-2022-4135, CVE-2021-38003, CVE-2021-30554, CVE-2026-66321, CVE-2022-21929, CVE-2024-29987, CVE-2023-36883, CVE-2022-26900, CVE-2026-21223, CVE-2023-21775, CVE-2026-66313, CVE-2025-47967, CVE-2022-26905, CVE-2024-26163, CVE-2023-2136, CVE-2024-38218, CVE-2024-43596, CVE-2023-29345, CVE-2022-23262, CVE-2026-2441, CVE-2024-21337, CVE-2023-36027, CVE-2026-45492, CVE-2026-26133, CVE-2024-26246</t>
+          <t>CVE-2026-84141, CVE-2026-84138, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-84133, CVE-2026-84639, CVE-2026-84126, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84128, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84139, CVE-2026-84142, CVE-2026-84143</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-1-2026</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-86/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3131,35 +3126,75 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>Microsoft Edge Security Updates</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>"Microsoft Edge Security Updates"</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>"Microsoft is aware of the recent Chromium security fixes. We are actively working on releasing a security fix."</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CVE-2021-36929, CVE-2021-30551, CVE-2025-21267, CVE-2026-11645, CVE-2023-4863, CVE-2022-23264, CVE-2023-35618, CVE-2024-49025, CVE-2020-16013, CVE-2023-38174, CVE-2024-0519, CVE-2026-66314, CVE-2023-21720, CVE-2024-21423, CVE-2022-33639, CVE-2022-21930, CVE-2025-21262, CVE-2022-29146, CVE-2026-66323, CVE-2023-36880, CVE-2026-0385, CVE-2026-66310, CVE-2022-22021, CVE-2022-26891, CVE-2021-34475, CVE-2021-37973, CVE-2024-21399, CVE-2026-66311, CVE-2023-2033, CVE-2025-53791, CVE-2025-47964, CVE-2024-30057, CVE-2023-21795, CVE-2025-26643, CVE-2024-43578, CVE-2022-26899, CVE-2020-16009, CVE-2024-30056, CVE-2024-7965, CVE-2023-36741, CVE-2025-21404, CVE-2022-3723, CVE-2021-30633, CVE-2024-2883, CVE-2026-72970, CVE-2024-38221, CVE-2026-33118, CVE-2022-33636, CVE-2022-1364, CVE-2026-70341, CVE-2021-4102, CVE-2026-5281, CVE-2021-43220, CVE-2023-28301, CVE-2024-38103, CVE-2024-30058, CVE-2023-36014, CVE-2024-29991, CVE-2026-66312, CVE-2026-66317, CVE-2026-45494, CVE-2023-36026, CVE-2024-38210, CVE-2023-29334, CVE-2023-36878, CVE-2024-38209, CVE-2025-47963, CVE-2025-21279, CVE-2025-24201, CVE-2024-26192, CVE-2022-26908, CVE-2023-7024, CVE-2021-38641, CVE-2023-21796, CVE-2025-10585, CVE-2022-4262, CVE-2024-43577, CVE-2021-21193, CVE-2022-2856, CVE-2021-43221, CVE-2026-41107, CVE-2024-43595, CVE-2021-30563, CVE-2025-5419, CVE-2023-5217, CVE-2025-6554, CVE-2024-49041, CVE-2024-21383, CVE-2023-36727, CVE-2021-36928, CVE-2021-37976, CVE-2023-28286, CVE-2024-38207, CVE-2021-21166, CVE-2020-16017, CVE-2023-33145, CVE-2026-66316, CVE-2022-26912, CVE-2024-29986, CVE-2022-44708, CVE-2023-23374, CVE-2022-3075, CVE-2025-21342, CVE-2021-33741, CVE-2020-6418, CVE-2024-21388, CVE-2023-24935, CVE-2024-21336, CVE-2025-29795, CVE-2021-36931, CVE-2026-42838, CVE-2022-33680, CVE-2023-0941, CVE-2026-62904, CVE-2024-20675, CVE-2026-45495, CVE-2023-38158, CVE-2022-29144, CVE-2022-0609, CVE-2024-38082, CVE-2024-20709, CVE-2022-1096, CVE-2025-25000, CVE-2026-3909, CVE-2026-3910, CVE-2024-38093, CVE-2023-36008, CVE-2026-0102, CVE-2025-6558, CVE-2025-21408, CVE-2023-36559, CVE-2024-21385, CVE-2021-30632, CVE-2025-29825, CVE-2021-31982, CVE-2024-43496, CVE-2021-38669, CVE-2023-29354, CVE-2024-26188, CVE-2024-4947, CVE-2026-72984, CVE-2024-26196, CVE-2023-29350, CVE-2024-30055, CVE-2022-38012, CVE-2025-60711, CVE-2022-30127, CVE-2022-33649, CVE-2022-23258, CVE-2024-29049, CVE-2021-34506, CVE-2025-49713, CVE-2024-43566, CVE-2024-43472, CVE-2021-21148, CVE-2023-35392, CVE-2022-2294, CVE-2022-21931, CVE-2024-20721, CVE-2024-41879, CVE-2023-36887, CVE-2023-38173, CVE-2024-4671, CVE-2024-26247, CVE-2023-21719, CVE-2021-21220, CVE-2024-26167, CVE-2025-21185, CVE-2025-21253, CVE-2023-36562, CVE-2023-21794, CVE-2023-28284, CVE-2022-23263, CVE-2026-66326, CVE-2023-38187, CVE-2022-26895, CVE-2025-21401, CVE-2023-36024, CVE-2022-29147, CVE-2021-26436, CVE-2025-21399, CVE-2026-65802, CVE-2025-47182, CVE-2022-30128, CVE-2024-38208, CVE-2024-21387, CVE-2026-66322, CVE-2024-7971, CVE-2021-37975, CVE-2021-38642, CVE-2025-13223, CVE-2025-29834, CVE-2024-49023, CVE-2022-33638, CVE-2021-38000, CVE-2026-33119, CVE-2023-36735, CVE-2021-36930, CVE-2023-44323, CVE-2022-44688, CVE-2024-4761, CVE-2023-36022, CVE-2020-1341, CVE-2022-41115, CVE-2020-1195, CVE-2024-29981, CVE-2025-47181, CVE-2022-21954, CVE-2024-49054, CVE-2024-43489, CVE-2022-21970, CVE-2026-58616, CVE-2026-66798, CVE-2022-24523, CVE-2025-4664, CVE-2022-24475, CVE-2024-43579, CVE-2024-5274, CVE-2025-29796, CVE-2023-3079, CVE-2023-33143, CVE-2026-66315, CVE-2022-26909, CVE-2026-66325, CVE-2024-38156, CVE-2023-38157, CVE-2021-21224, CVE-2021-21206, CVE-2021-31937, CVE-2022-23261, CVE-2024-43580, CVE-2021-24113, CVE-2023-36787, CVE-2021-42308, CVE-2024-38219, CVE-2023-28261, CVE-2022-26894, CVE-2023-36029, CVE-2021-26439, CVE-2025-2783, CVE-2024-39379, CVE-2026-65804, CVE-2023-36888, CVE-2024-43587, CVE-2024-38222, CVE-2023-36034, CVE-2026-66324, CVE-2024-21382, CVE-2022-41035, CVE-2026-66318, CVE-2024-21326, CVE-2022-35796, CVE-2026-40416, CVE-2020-15999, CVE-2024-29057, CVE-2025-21283, CVE-2022-30192, CVE-2025-62223, CVE-2024-38083, CVE-2023-6345, CVE-2022-4135, CVE-2021-38003, CVE-2021-30554, CVE-2026-66321, CVE-2022-21929, CVE-2024-29987, CVE-2023-36883, CVE-2022-26900, CVE-2026-21223, CVE-2023-21775, CVE-2026-66313, CVE-2025-47967, CVE-2022-26905, CVE-2024-26163, CVE-2023-2136, CVE-2024-38218, CVE-2024-43596, CVE-2023-29345, CVE-2022-23262, CVE-2026-2441, CVE-2024-21337, CVE-2023-36027, CVE-2026-45492, CVE-2026-26133, CVE-2024-26246</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-1-2026</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>Google Chrome Releases</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>CVE-2026-84335, CVE-2026-84356, CVE-2026-84358, CVE-2026-84354, CVE-2026-84351, CVE-2026-84330, CVE-2026-84353, CVE-2026-84352, CVE-2026-84324, CVE-2026-84334, CVE-2026-84328, CVE-2026-84355, CVE-2026-84357, CVE-2026-84326, CVE-2026-84325, CVE-2026-84327, CVE-2026-84347, CVE-2026-84349, CVE-2026-84329, CVE-2026-84331, CVE-2026-84323, CVE-2026-84350, CVE-2026-84359, CVE-2026-84333, CVE-2026-84332, CVE-2026-84348</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop.html</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I71" headerRowCount="1">
-  <autoFilter ref="A1:I71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I62" headerRowCount="1">
+  <autoFilter ref="A1:I62"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,31 +487,36 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,36 +527,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -562,31 +562,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -601,27 +601,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -646,17 +651,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -681,17 +686,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -716,17 +721,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -751,17 +756,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -786,17 +791,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -821,17 +826,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -856,17 +861,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -877,41 +882,31 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -922,36 +917,31 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CVE-2026-58612</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -966,32 +956,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-62815</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1016,22 +1011,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1056,22 +1051,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1096,7 +1091,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1106,12 +1101,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1136,7 +1131,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1146,12 +1141,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1176,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1186,12 +1181,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1216,7 +1211,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1226,12 +1221,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1256,7 +1251,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1266,12 +1261,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1296,7 +1291,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1306,12 +1301,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1336,7 +1331,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1346,12 +1341,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1376,7 +1371,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1386,12 +1381,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1416,7 +1411,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1426,12 +1421,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1466,12 +1461,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1496,7 +1491,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1506,12 +1501,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1536,7 +1531,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1546,12 +1541,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1576,7 +1571,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1586,12 +1581,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1616,7 +1611,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1626,12 +1621,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1656,7 +1651,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1666,12 +1661,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1696,7 +1691,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1706,12 +1701,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1736,7 +1731,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1746,12 +1741,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1776,7 +1771,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1786,12 +1781,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1816,7 +1811,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1826,12 +1821,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1856,7 +1851,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1866,12 +1861,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1896,7 +1891,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1906,12 +1901,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1926,32 +1921,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1966,27 +1961,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2001,27 +2001,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2032,36 +2037,31 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2072,36 +2072,31 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
+          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>CVE-2026-50376</t>
+          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2116,32 +2111,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-62880</t>
+          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2166,7 +2161,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2176,12 +2171,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-62768</t>
+          <t>CVE-2026-50376</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2196,37 +2191,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-62880</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2241,37 +2231,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>CVE-2026-62768</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2296,7 +2281,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2306,12 +2291,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2336,7 +2326,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2346,17 +2336,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-20281</t>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2381,7 +2371,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2391,17 +2381,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-20212</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2416,27 +2401,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CVE-2026-20281</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2451,27 +2446,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CVE-2026-20212</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2496,17 +2501,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2531,17 +2536,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2566,17 +2571,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2601,17 +2606,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2636,17 +2641,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2671,17 +2676,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2706,17 +2711,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2741,17 +2746,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
+          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
+          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2762,41 +2767,31 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"SonicWall SMA1000 Series Appliances Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-83548 - Pre-authentication SSRF via unintended forward-proxy A Pre-authentication SSRF vulnerability exists in the SMA1000 Appliance Work Place interface due to an unintended alternate access path. A remote unauthenticated attacker could potentially exploit this vulnerability to gain unauthorized access to sensitive functionality and perform unauthorized operations.. CVSS Score: 10.0 CVSS Vector: CVSS:3.0/AV:N/AC:L/PR:N/UI:N/S:C/C:H/I:H/A:H CWE-918: Server-Side Request Forgery (SSRF) CWE-441: Unintended Proxy or Intermediary ('Confused Deputy') 2) CVE-2026-83549 - Post-authentication Remote Code Execution (RCE) Vulnerability Post-authentication Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability has been identified in the SMA1000 Appliance Management Console (AMC) which in specific conditions could potentially enable a remote authenticated attacker as administrator to execute arbitrary OS commands, resulting in remote code execution. CVSS Score: 7.8 CVSS Vector: CVSS:3.0/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') IMPORTANT: SonicWall PSIRT has investigated a case indicating the active exploitation of the vulnerabilities described in this advisory. Customers are strongly urged to upgrade to the hotfix release as soon as possible to remediate this vulnerability. CVE: CVE-2026-83548, CVE-2026-83549 Last updated: Sept. 1, 2026, 5:43 a.m.""</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>CVE-2026-83548, CVE-2026-83549</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0016</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2807,394 +2802,34 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"Automated workflow email notifications disabled"</t>
+          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""Sep 1 , 13:34 EDT Resolved - The ability to send emails through an automated workflow has been been restored. Sep 1 , 13:33 EDT Update - The ability to send emails through an automated workflow has been been restored. Aug 31 , 18:56 EDT Investigating - The ability to send emails through an automated workflow has been temporarily disabled. We will post an update when this functionality is restored.""</t>
+          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/tpf30l4kyq08</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-84 Security Vulnerabilities fixed in Firefox ESR 140.15"</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>CVE-2026-16371, CVE-2026-75874, CVE-2026-16365, CVE-2026-84143, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84124, CVE-2026-84122, CVE-2026-84120</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-84/</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-85 Security Vulnerabilities fixed in Firefox ESR 153.2"</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-74952, CVE-2026-84131, CVE-2026-84140, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-75874, CVE-2026-84136, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84144</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-85/</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-82 Security Vulnerabilities fixed in Firefox 155"</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>CVE-2026-84143, CVE-2026-84134, CVE-2026-84119, CVE-2026-84131, CVE-2026-84126, CVE-2026-84140, CVE-2026-84142, CVE-2026-84125, CVE-2026-84124, CVE-2026-84118, CVE-2026-84122, CVE-2026-84138, CVE-2026-84141, CVE-2026-84120, CVE-2026-84130, CVE-2026-84135, CVE-2026-84129, CVE-2026-84132, CVE-2026-84137, CVE-2026-84128, CVE-2026-84136, CVE-2026-84117, CVE-2026-84139, CVE-2026-84133, CVE-2026-84121, CVE-2026-84123, CVE-2026-84145, CVE-2026-84127, CVE-2026-84144</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-82/</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-83 Security Vulnerabilities fixed in Firefox ESR 115.40"</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>CVE-2026-75874, CVE-2026-84121, CVE-2026-84119, CVE-2026-84131, CVE-2026-84145, CVE-2026-84120</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-83/</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-87 Security Vulnerabilities fixed in Thunderbird 140.15"</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>CVE-2026-75874, CVE-2026-84119, CVE-2026-84124, CVE-2026-84641, CVE-2026-84639, CVE-2026-84145, CVE-2026-84640, CVE-2026-84131, CVE-2026-84121, CVE-2026-84120, CVE-2026-16371, CVE-2026-84122, CVE-2026-16365, CVE-2026-84143</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-87/</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-88 Security Vulnerabilities fixed in Thunderbird 153.2"</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>CVE-2026-84141, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-74952, CVE-2026-84133, CVE-2026-84639, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-75874, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84637, CVE-2026-84139, CVE-2026-84143</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-88/</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Mozilla Security Advisories</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>"MFSA 2026-86 Security Vulnerabilities fixed in Thunderbird 155"</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>CVE-2026-84141, CVE-2026-84138, CVE-2026-84124, CVE-2026-84136, CVE-2026-84120, CVE-2026-84133, CVE-2026-84639, CVE-2026-84126, CVE-2026-84132, CVE-2026-84130, CVE-2026-84137, CVE-2026-84641, CVE-2026-84123, CVE-2026-84640, CVE-2026-84134, CVE-2026-84122, CVE-2026-84129, CVE-2026-84131, CVE-2026-84125, CVE-2026-84642, CVE-2026-84145, CVE-2026-84118, CVE-2026-84128, CVE-2026-84119, CVE-2026-84144, CVE-2026-84121, CVE-2026-84140, CVE-2026-84139, CVE-2026-84142, CVE-2026-84143</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-86/</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Microsoft Edge Security Updates</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>"Microsoft Edge Security Updates"</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>"Microsoft is aware of the recent Chromium security fixes. We are actively working on releasing a security fix."</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>CVE-2021-36929, CVE-2021-30551, CVE-2025-21267, CVE-2026-11645, CVE-2023-4863, CVE-2022-23264, CVE-2023-35618, CVE-2024-49025, CVE-2020-16013, CVE-2023-38174, CVE-2024-0519, CVE-2026-66314, CVE-2023-21720, CVE-2024-21423, CVE-2022-33639, CVE-2022-21930, CVE-2025-21262, CVE-2022-29146, CVE-2026-66323, CVE-2023-36880, CVE-2026-0385, CVE-2026-66310, CVE-2022-22021, CVE-2022-26891, CVE-2021-34475, CVE-2021-37973, CVE-2024-21399, CVE-2026-66311, CVE-2023-2033, CVE-2025-53791, CVE-2025-47964, CVE-2024-30057, CVE-2023-21795, CVE-2025-26643, CVE-2024-43578, CVE-2022-26899, CVE-2020-16009, CVE-2024-30056, CVE-2024-7965, CVE-2023-36741, CVE-2025-21404, CVE-2022-3723, CVE-2021-30633, CVE-2024-2883, CVE-2026-72970, CVE-2024-38221, CVE-2026-33118, CVE-2022-33636, CVE-2022-1364, CVE-2026-70341, CVE-2021-4102, CVE-2026-5281, CVE-2021-43220, CVE-2023-28301, CVE-2024-38103, CVE-2024-30058, CVE-2023-36014, CVE-2024-29991, CVE-2026-66312, CVE-2026-66317, CVE-2026-45494, CVE-2023-36026, CVE-2024-38210, CVE-2023-29334, CVE-2023-36878, CVE-2024-38209, CVE-2025-47963, CVE-2025-21279, CVE-2025-24201, CVE-2024-26192, CVE-2022-26908, CVE-2023-7024, CVE-2021-38641, CVE-2023-21796, CVE-2025-10585, CVE-2022-4262, CVE-2024-43577, CVE-2021-21193, CVE-2022-2856, CVE-2021-43221, CVE-2026-41107, CVE-2024-43595, CVE-2021-30563, CVE-2025-5419, CVE-2023-5217, CVE-2025-6554, CVE-2024-49041, CVE-2024-21383, CVE-2023-36727, CVE-2021-36928, CVE-2021-37976, CVE-2023-28286, CVE-2024-38207, CVE-2021-21166, CVE-2020-16017, CVE-2023-33145, CVE-2026-66316, CVE-2022-26912, CVE-2024-29986, CVE-2022-44708, CVE-2023-23374, CVE-2022-3075, CVE-2025-21342, CVE-2021-33741, CVE-2020-6418, CVE-2024-21388, CVE-2023-24935, CVE-2024-21336, CVE-2025-29795, CVE-2021-36931, CVE-2026-42838, CVE-2022-33680, CVE-2023-0941, CVE-2026-62904, CVE-2024-20675, CVE-2026-45495, CVE-2023-38158, CVE-2022-29144, CVE-2022-0609, CVE-2024-38082, CVE-2024-20709, CVE-2022-1096, CVE-2025-25000, CVE-2026-3909, CVE-2026-3910, CVE-2024-38093, CVE-2023-36008, CVE-2026-0102, CVE-2025-6558, CVE-2025-21408, CVE-2023-36559, CVE-2024-21385, CVE-2021-30632, CVE-2025-29825, CVE-2021-31982, CVE-2024-43496, CVE-2021-38669, CVE-2023-29354, CVE-2024-26188, CVE-2024-4947, CVE-2026-72984, CVE-2024-26196, CVE-2023-29350, CVE-2024-30055, CVE-2022-38012, CVE-2025-60711, CVE-2022-30127, CVE-2022-33649, CVE-2022-23258, CVE-2024-29049, CVE-2021-34506, CVE-2025-49713, CVE-2024-43566, CVE-2024-43472, CVE-2021-21148, CVE-2023-35392, CVE-2022-2294, CVE-2022-21931, CVE-2024-20721, CVE-2024-41879, CVE-2023-36887, CVE-2023-38173, CVE-2024-4671, CVE-2024-26247, CVE-2023-21719, CVE-2021-21220, CVE-2024-26167, CVE-2025-21185, CVE-2025-21253, CVE-2023-36562, CVE-2023-21794, CVE-2023-28284, CVE-2022-23263, CVE-2026-66326, CVE-2023-38187, CVE-2022-26895, CVE-2025-21401, CVE-2023-36024, CVE-2022-29147, CVE-2021-26436, CVE-2025-21399, CVE-2026-65802, CVE-2025-47182, CVE-2022-30128, CVE-2024-38208, CVE-2024-21387, CVE-2026-66322, CVE-2024-7971, CVE-2021-37975, CVE-2021-38642, CVE-2025-13223, CVE-2025-29834, CVE-2024-49023, CVE-2022-33638, CVE-2021-38000, CVE-2026-33119, CVE-2023-36735, CVE-2021-36930, CVE-2023-44323, CVE-2022-44688, CVE-2024-4761, CVE-2023-36022, CVE-2020-1341, CVE-2022-41115, CVE-2020-1195, CVE-2024-29981, CVE-2025-47181, CVE-2022-21954, CVE-2024-49054, CVE-2024-43489, CVE-2022-21970, CVE-2026-58616, CVE-2026-66798, CVE-2022-24523, CVE-2025-4664, CVE-2022-24475, CVE-2024-43579, CVE-2024-5274, CVE-2025-29796, CVE-2023-3079, CVE-2023-33143, CVE-2026-66315, CVE-2022-26909, CVE-2026-66325, CVE-2024-38156, CVE-2023-38157, CVE-2021-21224, CVE-2021-21206, CVE-2021-31937, CVE-2022-23261, CVE-2024-43580, CVE-2021-24113, CVE-2023-36787, CVE-2021-42308, CVE-2024-38219, CVE-2023-28261, CVE-2022-26894, CVE-2023-36029, CVE-2021-26439, CVE-2025-2783, CVE-2024-39379, CVE-2026-65804, CVE-2023-36888, CVE-2024-43587, CVE-2024-38222, CVE-2023-36034, CVE-2026-66324, CVE-2024-21382, CVE-2022-41035, CVE-2026-66318, CVE-2024-21326, CVE-2022-35796, CVE-2026-40416, CVE-2020-15999, CVE-2024-29057, CVE-2025-21283, CVE-2022-30192, CVE-2025-62223, CVE-2024-38083, CVE-2023-6345, CVE-2022-4135, CVE-2021-38003, CVE-2021-30554, CVE-2026-66321, CVE-2022-21929, CVE-2024-29987, CVE-2023-36883, CVE-2022-26900, CVE-2026-21223, CVE-2023-21775, CVE-2026-66313, CVE-2025-47967, CVE-2022-26905, CVE-2024-26163, CVE-2023-2136, CVE-2024-38218, CVE-2024-43596, CVE-2023-29345, CVE-2022-23262, CVE-2026-2441, CVE-2024-21337, CVE-2023-36027, CVE-2026-45492, CVE-2026-26133, CVE-2024-26246</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-1-2026</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Google Chrome Releases</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>"Stable Channel Update for Desktop"</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>CVE-2026-84335, CVE-2026-84356, CVE-2026-84358, CVE-2026-84354, CVE-2026-84351, CVE-2026-84330, CVE-2026-84353, CVE-2026-84352, CVE-2026-84324, CVE-2026-84334, CVE-2026-84328, CVE-2026-84355, CVE-2026-84357, CVE-2026-84326, CVE-2026-84325, CVE-2026-84327, CVE-2026-84347, CVE-2026-84349, CVE-2026-84329, CVE-2026-84331, CVE-2026-84323, CVE-2026-84350, CVE-2026-84359, CVE-2026-84333, CVE-2026-84332, CVE-2026-84348</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop.html</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I62" headerRowCount="1">
-  <autoFilter ref="A1:I62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I78" headerRowCount="1">
+  <autoFilter ref="A1:I78"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -562,31 +567,36 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -597,36 +607,36 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -637,31 +647,31 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -672,31 +682,31 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -707,31 +717,31 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -742,31 +752,31 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -777,31 +787,31 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -812,31 +822,31 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -847,31 +857,31 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -882,31 +892,31 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -917,31 +927,31 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -952,41 +962,31 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -997,36 +997,31 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CVE-2026-58612</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1037,36 +1032,31 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CVE-2026-62815</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1077,36 +1067,41 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1117,36 +1112,31 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CVE-2026-84348</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1157,36 +1147,31 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CVE-2026-84324</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1197,36 +1182,36 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1237,36 +1222,31 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CVE-2026-84325</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1277,36 +1257,31 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>CVE-2026-84349</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1317,36 +1292,31 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CVE-2026-84331</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1357,36 +1327,31 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CVE-2026-84355</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1397,36 +1362,31 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>CVE-2026-84334</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1437,36 +1397,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>CVE-2026-84358</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1477,36 +1432,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>CVE-2026-84351</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1517,36 +1467,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CVE-2026-84323</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1557,36 +1502,31 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>CVE-2026-84332</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1601,32 +1541,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1651,22 +1596,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1691,22 +1636,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1731,7 +1676,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1741,12 +1686,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1771,7 +1716,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1781,12 +1726,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1811,7 +1756,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1821,12 +1766,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1851,7 +1796,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1861,12 +1806,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1891,7 +1836,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1901,12 +1846,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,7 +1876,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1941,12 +1886,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1971,7 +1916,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1981,12 +1926,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2001,32 +1946,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2041,27 +1986,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2076,27 +2026,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2107,36 +2062,36 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2147,7 +2102,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2161,22 +2116,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-50376</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2187,7 +2142,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2201,22 +2156,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-62880</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2227,7 +2182,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2241,22 +2196,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-62768</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2267,41 +2222,36 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2312,41 +2262,36 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2357,36 +2302,36 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2397,41 +2342,36 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CVE-2026-20281</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>7.5</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2442,41 +2382,36 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-20212</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2487,31 +2422,36 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2522,31 +2462,36 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2557,31 +2502,36 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2592,31 +2542,36 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2627,31 +2582,36 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2662,31 +2622,31 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2697,7 +2657,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2711,17 +2671,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2736,27 +2696,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2771,27 +2736,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CVE-2026-50376</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2806,30 +2776,645 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CVE-2026-62880</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CVE-2026-62768</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CVE-2026-20281</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CVE-2026-20212</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I78" headerRowCount="1">
-  <autoFilter ref="A1:I78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I82" headerRowCount="1">
+  <autoFilter ref="A1:I82"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,36 +487,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -531,17 +526,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -551,12 +546,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CVE-2026-86853</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -571,32 +566,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CVE-2026-50696</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -621,7 +616,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -631,12 +626,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-62697</t>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -651,27 +646,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -686,27 +686,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -766,17 +766,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -836,17 +836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -941,17 +941,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1071,37 +1071,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1116,27 +1106,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1161,17 +1161,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1182,36 +1182,31 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1222,31 +1217,36 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1257,31 +1257,41 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Adobe Acrobat and Reader</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1292,31 +1302,31 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1331,27 +1341,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1376,17 +1391,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1411,17 +1426,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1446,17 +1461,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1481,17 +1496,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1516,17 +1531,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1537,41 +1552,31 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1582,36 +1587,31 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>CVE-2026-58612</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1622,36 +1622,31 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CVE-2026-62815</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1662,36 +1657,31 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CVE-2026-84350</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1706,32 +1696,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1756,22 +1751,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1796,22 +1791,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1836,7 +1831,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1846,12 +1841,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1876,7 +1871,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1886,12 +1881,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1916,7 +1911,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1926,12 +1921,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1956,7 +1951,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1966,12 +1961,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1996,7 +1991,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2006,12 +2001,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2036,7 +2031,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2046,12 +2041,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2076,7 +2071,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2086,12 +2081,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2116,7 +2111,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2126,12 +2121,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2156,7 +2151,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2166,12 +2161,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2196,7 +2191,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2206,12 +2201,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2236,7 +2231,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2246,12 +2241,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2276,7 +2271,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2286,12 +2281,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2316,7 +2311,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2326,12 +2321,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2356,7 +2351,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2366,12 +2361,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2396,7 +2391,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2406,12 +2401,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2436,7 +2431,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2446,12 +2441,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2476,7 +2471,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2486,12 +2481,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2516,7 +2511,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2526,12 +2521,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2556,7 +2551,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2566,12 +2561,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2586,32 +2581,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2626,27 +2621,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2661,27 +2661,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2692,36 +2697,36 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2732,36 +2737,36 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-50376</t>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2772,36 +2777,31 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>CVE-2026-62880</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2812,36 +2812,31 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>CVE-2026-62768</t>
+          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2856,37 +2851,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2901,37 +2891,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>CVE-2026-50376</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2946,32 +2931,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+          <t>CVE-2026-62880</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2986,37 +2971,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement added. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVE-2026-20281</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>7.5</t>
+          <t>CVE-2026-62768</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3041,7 +3021,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3051,7 +3031,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CVE-2026-20212</t>
+          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3061,7 +3041,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3076,27 +3056,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3111,27 +3101,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3146,27 +3141,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CVE-2026-20281</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3181,27 +3186,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CVE-2026-20212</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3226,17 +3241,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3261,17 +3276,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3296,17 +3311,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3331,17 +3346,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3366,17 +3381,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3401,20 +3416,160 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I82" headerRowCount="1">
-  <autoFilter ref="A1:I82"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I77" headerRowCount="1">
+  <autoFilter ref="A1:I77"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,27 +491,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,36 +527,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -562,36 +562,31 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CVE-2026-86853</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -606,32 +601,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-50696</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -646,32 +641,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-62697</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -686,27 +681,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -721,27 +721,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -756,27 +761,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -791,27 +801,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -826,27 +841,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -861,27 +881,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -896,27 +921,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -931,27 +961,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -966,27 +1001,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1001,27 +1041,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1036,27 +1081,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1071,27 +1116,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1106,37 +1156,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1151,27 +1191,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1186,27 +1226,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1221,32 +1261,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1261,37 +1296,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1302,31 +1327,31 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1337,36 +1362,31 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1377,31 +1397,31 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1412,31 +1432,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1447,31 +1467,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1482,31 +1502,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1517,31 +1537,41 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1552,31 +1582,41 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1587,31 +1627,41 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1622,31 +1672,31 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1657,7 +1707,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1671,17 +1721,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1692,41 +1742,36 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1737,36 +1782,41 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Adobe Acrobat and Reader</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-58612</t>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1777,36 +1827,31 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>CVE-2026-62815</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1817,36 +1862,36 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1857,36 +1902,31 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>CVE-2026-84348</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1897,36 +1937,31 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>CVE-2026-84324</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1937,36 +1972,31 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>CVE-2026-84347</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -1977,36 +2007,31 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>CVE-2026-84325</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2017,36 +2042,31 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>CVE-2026-84349</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2057,36 +2077,31 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>CVE-2026-84331</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2097,36 +2112,31 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>CVE-2026-84355</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2137,36 +2147,31 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>CVE-2026-84334</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2177,36 +2182,31 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>CVE-2026-84358</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2221,32 +2221,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2271,22 +2276,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2311,22 +2316,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2351,7 +2356,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2361,12 +2366,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2391,7 +2396,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2401,12 +2406,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2431,7 +2436,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2441,12 +2446,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2471,7 +2476,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2481,12 +2486,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2511,7 +2516,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2521,12 +2526,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2551,7 +2556,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2561,12 +2566,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2591,7 +2596,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2601,12 +2606,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2631,7 +2636,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2641,12 +2646,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2671,7 +2676,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2681,12 +2686,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2711,7 +2716,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2721,12 +2726,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2741,32 +2746,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2781,27 +2786,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2816,27 +2826,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2847,36 +2862,36 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.62) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CVE-2026-41107, CVE-2024-29991, CVE-2023-33145, CVE-2025-29834, CVE-2022-44688, CVE-2021-31937, CVE-2023-38158, CVE-2024-38221, CVE-2025-25000, CVE-2022-26895, CVE-2021-37975, CVE-2023-38157, CVE-2026-66314, CVE-2023-21719, CVE-2024-21423, CVE-2021-34475, CVE-2024-26246, CVE-2023-38187, CVE-2022-21954, CVE-2022-2856, CVE-2020-16017, CVE-2024-30058, CVE-2025-21262, CVE-2024-21385, CVE-2025-21279, CVE-2024-20675, CVE-2024-38082, CVE-2025-26643, CVE-2024-5274, CVE-2022-21929, CVE-2026-72984, CVE-2021-36928, CVE-2026-2441, CVE-2026-11645, CVE-2025-21283, CVE-2022-24523, CVE-2020-16009, CVE-2025-21404, CVE-2024-26163, CVE-2024-38093, CVE-2024-38207, CVE-2026-66316, CVE-2025-21253, CVE-2021-38642, CVE-2022-41115, CVE-2025-6558, CVE-2024-43472, CVE-2026-65802, CVE-2024-38083, CVE-2023-29350, CVE-2025-60711, CVE-2025-5419, CVE-2024-43587, CVE-2024-38103, CVE-2021-37976, CVE-2021-26439, CVE-2024-26247, CVE-2025-21399, CVE-2026-66323, CVE-2024-21337, CVE-2024-21336, CVE-2020-1195, CVE-2022-33680, CVE-2025-21185, CVE-2024-30055, CVE-2022-29147, CVE-2026-66317, CVE-2023-29334, CVE-2026-66321, CVE-2025-6554, CVE-2022-41035, CVE-2021-4102, CVE-2026-66310, CVE-2022-23261, CVE-2026-66322, CVE-2024-26167, CVE-2022-33639, CVE-2021-36930, CVE-2021-30563, CVE-2026-66315, CVE-2025-24201, CVE-2022-38012, CVE-2023-36008, CVE-2021-26436, CVE-2022-22021, CVE-2022-21930, CVE-2022-23264, CVE-2026-45495, CVE-2026-3909, CVE-2024-49025, CVE-2023-6345, CVE-2024-43578, CVE-2023-21794, CVE-2023-36887, CVE-2021-42308, CVE-2020-6418, CVE-2022-33638, CVE-2026-66313, CVE-2025-47964, CVE-2023-36741, CVE-2023-7024, CVE-2023-36026, CVE-2024-29981, CVE-2024-38209, CVE-2020-1341, CVE-2022-26909, CVE-2023-28261, CVE-2026-3910, CVE-2022-0609, CVE-2021-37973, CVE-2024-4761, CVE-2025-10585, CVE-2025-4664, CVE-2023-36880, CVE-2023-36562, CVE-2023-2136, CVE-2026-66312, CVE-2026-5281, CVE-2026-26133, CVE-2023-36883, CVE-2023-0941, CVE-2022-21970, CVE-2021-36929, CVE-2021-21148, CVE-2024-21387, CVE-2026-42838, CVE-2024-38156, CVE-2022-29144, CVE-2022-29146, CVE-2024-38218, CVE-2021-30551, CVE-2024-29057, CVE-2024-4671, CVE-2023-36888, CVE-2021-21193, CVE-2024-49054, CVE-2025-62223, CVE-2025-13223, CVE-2024-26192, CVE-2024-43577, CVE-2021-38000, CVE-2022-23262, CVE-2025-21342, CVE-2024-49023, CVE-2026-66318, CVE-2024-4947, CVE-2021-30633, CVE-2025-47963, CVE-2024-7965, CVE-2026-62904, CVE-2023-21795, CVE-2024-43566, CVE-2023-28284, CVE-2025-29825, CVE-2021-21224, CVE-2020-16013, CVE-2022-1364, CVE-2026-65804, CVE-2025-47181, CVE-2024-38208, CVE-2022-26908, CVE-2024-26196, CVE-2024-43596, CVE-2024-2883, CVE-2025-21408, CVE-2024-20721, CVE-2022-26894, CVE-2022-30192, CVE-2026-45492, CVE-2024-39379, CVE-2023-36029, CVE-2026-72970, CVE-2025-2783, CVE-2024-43496, CVE-2024-21326, CVE-2023-4863, CVE-2023-36787, CVE-2022-30128, CVE-2023-36034, CVE-2024-43579, CVE-2021-24113, CVE-2026-58616, CVE-2023-36878, CVE-2024-21383, CVE-2025-21401, CVE-2024-30056, CVE-2023-36024, CVE-2023-38173, CVE-2022-3723, CVE-2024-0519, CVE-2021-38003, CVE-2023-36727, CVE-2025-29795, CVE-2026-66325, CVE-2024-26188, CVE-2023-28301, CVE-2025-49713, CVE-2021-36931, CVE-2021-34506, CVE-2026-45494, CVE-2023-29345, CVE-2022-4262, CVE-2023-36735, CVE-2021-38641, CVE-2025-47967, CVE-2024-21399, CVE-2026-66311, CVE-2024-29049, CVE-2024-20709, CVE-2022-26891, CVE-2023-29354, CVE-2024-7971, CVE-2026-66324, CVE-2026-21223, CVE-2022-33649, CVE-2022-1096, CVE-2026-0102, CVE-2021-33741, CVE-2023-33143, CVE-2021-31982, CVE-2024-41879, CVE-2024-43489, CVE-2022-35796, CVE-2024-29986, CVE-2022-3075, CVE-2021-43220, CVE-2022-26905, CVE-2022-33636, CVE-2024-21388, CVE-2024-29987, CVE-2022-2294, CVE-2023-2033, CVE-2023-38174, CVE-2022-26899, CVE-2021-30554, CVE-2022-26912, CVE-2025-29796, CVE-2022-24475, CVE-2024-43595, CVE-2020-15999, CVE-2026-33119, CVE-2023-36559, CVE-2022-23258, CVE-2021-21166, CVE-2023-35392, CVE-2026-33118, CVE-2024-38222, CVE-2022-44708, CVE-2022-30127, CVE-2023-35618, CVE-2023-23374, CVE-2024-30057, CVE-2024-21382, CVE-2023-21775, CVE-2024-38210, CVE-2026-66326, CVE-2024-38219, CVE-2023-36014, CVE-2022-21931, CVE-2023-36027, CVE-2023-24935, CVE-2024-49041, CVE-2026-70341, CVE-2021-30632, CVE-2025-53791, CVE-2023-44323, CVE-2024-43580, CVE-2025-47182, CVE-2022-23263, CVE-2023-21720, CVE-2021-21206, CVE-2021-21220, CVE-2026-40416, CVE-2026-66798, CVE-2022-4135, CVE-2023-5217, CVE-2023-36022, CVE-2025-21267, CVE-2021-43221, CVE-2022-26900, CVE-2021-38669, CVE-2023-3079, CVE-2026-0385, CVE-2023-21796, CVE-2023-28286</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-2-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2887,7 +2902,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2901,22 +2916,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"CVE-2026-50376 Windows Remote Desktop Client Information Disclosure Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CVE-2026-50376</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50376</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2927,7 +2942,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2941,22 +2956,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"CVE-2026-62880 Windows NTFS Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CVE-2026-62880</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62880</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2967,7 +2982,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2981,22 +2996,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"CVE-2026-62768 Windows Installer Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""Acknowledgement added. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVE-2026-62768</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62768</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3007,41 +3022,36 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CVE-2026-20277, CVE-2026-20274, CVE-2026-20276, CVE-2026-20279, CVE-2026-20278, CVE-2026-20275, CVE-2026-20280</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3052,41 +3062,36 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3097,36 +3102,36 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 2, 2026, Security Advisories"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CVE-2026-20281, CVE-2026-20277, CVE-2026-20279, CVE-2026-20276, CVE-2026-20274, CVE-2026-20278, CVE-2026-20275, CVE-2026-20212, CVE-2026-20355, CVE-2026-20354, CVE-2026-20280</t>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-f2SiMFxl</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3137,41 +3142,36 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Cisco Desk Phone 9800 Series, IP Phone 7800 and 8800 Series, and Video Phone 8875 with SIP Software Denial of Service Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CVE-2026-20281</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>7.5</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-phone-dos-txMYNRzv</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3182,41 +3182,36 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Cisco Nexus 9000 Series Switches Silicon One Remote Code Execution Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CVE-2026-20212</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-n9k-s1-rce-EH8dEtr</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3227,31 +3222,36 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>""HPESBNW05133 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking Fabric Composer""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05133en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3262,31 +3262,36 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""HPESBNW05134 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ArubaOS-CX (AOS-CX)""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05134en_us&amp;docLocale=en_US</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3297,31 +3302,31 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""HPESBNW05139 rev.1 - HPE Networking Advance Notification of Security Advisories for September 9, 2026""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05139en_us&amp;docLocale=en_US</t>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3332,31 +3337,31 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BarracudaAdvisories</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""HPESBHF05087 rev.1 - HPE ProLiant DL/ML/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05087en_us&amp;docLocale=en_US</t>
+          <t>https://trust.barracuda.com/security/no-affiliation-with-ransomware-group</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3367,7 +3372,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3381,195 +3386,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>""HPESBHF05088 rev.1 - HPE ProLiant DL/ML/XL, Apollo, Alletra, MicroServer, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05088en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>"HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>""HPESBHF05107 rev.2 - HPE ProLiant DL/ML/XD/XL, Alletra, Apollo, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01437, Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05107en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>"HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>""HPESBHF05101 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05101en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>"HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>""HPESBHF05116 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05116en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>"HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>""HPESBHF05117 rev.2 - HPE ProLiant DL/ML/XD, Alletra, Edgeline, and Synergy Server Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05117en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>"HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service"</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>""HPESBHF05118 rev.1 - HPE ProLiant DL/XL, Apollo, Synergy and Edgeline Servers Using Certain Intel Processors, INTEL-SA-01443, Intel 3rd Gen Intel Xeon Scalable Processor Firmware Advisory, Local Denial of Service""</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05118en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I77" headerRowCount="1">
-  <autoFilter ref="A1:I77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I88" headerRowCount="1">
+  <autoFilter ref="A1:I88"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,32 +491,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-0307</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -531,27 +531,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""""</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CVE-2026-0305</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -566,27 +571,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""""</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CVE-2026-0306</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -597,36 +607,36 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>CVE-2026-0310</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -637,36 +647,36 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-86853</t>
+          <t>CVE-2026-0304</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -677,36 +687,36 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>CVE-2026-0309</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -717,36 +727,36 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-50696</t>
+          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -757,7 +767,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -771,22 +781,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-62697</t>
+          <t>CVE-2026-85046</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -797,36 +807,36 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-54990</t>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -837,36 +847,41 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-44814</t>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -877,36 +892,31 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CVE-2026-69845</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -917,36 +927,31 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CVE-2026-57085</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -957,36 +962,31 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CVE-2026-42914</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -997,36 +997,31 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CVE-2026-62747</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1041,32 +1036,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1081,27 +1076,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1116,32 +1116,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1156,27 +1156,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1191,27 +1196,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1226,27 +1236,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1261,27 +1276,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1296,27 +1316,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1331,27 +1356,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1366,27 +1396,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1401,27 +1436,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1436,27 +1476,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1471,27 +1516,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1506,27 +1551,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1541,37 +1591,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1586,37 +1626,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1631,37 +1661,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1676,27 +1696,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1711,27 +1731,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1746,32 +1766,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1786,37 +1801,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1827,31 +1832,31 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1862,36 +1867,31 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1902,31 +1902,31 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1937,31 +1937,31 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1972,31 +1972,41 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2007,31 +2017,41 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2042,31 +2062,41 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2077,31 +2107,31 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2112,7 +2142,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2126,17 +2156,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2147,31 +2177,36 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2182,31 +2217,41 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Adobe Acrobat and Reader</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2217,41 +2262,31 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2262,36 +2297,36 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-58612</t>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2302,36 +2337,31 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>CVE-2026-62815</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2342,36 +2372,31 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>CVE-2026-84350</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2382,36 +2407,31 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>CVE-2026-84348</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2422,36 +2442,31 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>CVE-2026-84324</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2462,36 +2477,31 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>CVE-2026-84347</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2502,36 +2512,31 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>CVE-2026-84325</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2542,36 +2547,31 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>CVE-2026-84349</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2582,36 +2582,31 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>CVE-2026-84331</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2622,36 +2617,31 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>CVE-2026-84355</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2666,32 +2656,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2716,22 +2711,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2756,22 +2751,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2796,7 +2791,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2806,12 +2801,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2836,7 +2831,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2846,12 +2841,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2876,7 +2871,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2886,12 +2881,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2916,7 +2911,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2926,12 +2921,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2956,7 +2951,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2966,12 +2961,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2996,7 +2991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3006,12 +3001,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3036,7 +3031,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3046,12 +3041,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3076,7 +3071,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3086,12 +3081,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3116,7 +3111,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3126,12 +3121,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3156,7 +3151,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3166,12 +3161,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3196,7 +3191,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3206,12 +3201,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3236,7 +3231,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3246,12 +3241,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3266,32 +3261,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3306,27 +3301,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3341,27 +3341,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3376,30 +3381,460 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CVE-2026-84329</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>CVE-2026-84356</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CVE-2026-84359</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CVE-2026-84353</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CVE-2026-84335</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CVE-2026-84357</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Google Chrome Releases</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>"Stable Channel Update for Desktop"</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BarracudaAdvisories</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BarracudaAdvisories</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://trust.barracuda.com/security/no-affiliation-with-ransomware-group</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I88" headerRowCount="1">
-  <autoFilter ref="A1:I88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I95" headerRowCount="1">
+  <autoFilter ref="A1:I95"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,32 +491,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
+          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""""</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CVE-2026-0307</t>
+          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
+          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +536,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -551,12 +546,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CVE-2026-0305</t>
+          <t>CVE-2026-0307</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -581,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,12 +586,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CVE-2026-0306</t>
+          <t>CVE-2026-0305</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -621,7 +616,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
+          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -631,12 +626,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-0310</t>
+          <t>CVE-2026-0306</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -661,7 +656,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -671,12 +666,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-0304</t>
+          <t>CVE-2026-0310</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -701,7 +696,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -711,12 +706,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2026-0309</t>
+          <t>CVE-2026-0304</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -741,7 +736,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
+          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -751,12 +746,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
+          <t>CVE-2026-0309</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -771,32 +766,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
+          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-85046</t>
+          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
+          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -811,32 +806,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-85046</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -851,37 +846,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
+          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-20079</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>10.0</t>
+          <t>CVE-2026-69777</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -896,27 +886,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
+          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CVE-2026-45499</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -931,27 +926,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CVE-2026-68877</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -966,27 +966,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"Importing external certificates to Stork"</t>
+          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CVE-2026-62693</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1001,27 +1006,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CVE-2026-69508</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1032,21 +1042,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1056,12 +1066,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1072,21 +1082,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1096,12 +1106,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-86853</t>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1112,36 +1127,31 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1152,36 +1162,31 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>CVE-2026-50696</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1192,36 +1197,31 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>CVE-2026-62697</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1232,36 +1232,31 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>CVE-2026-54990</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1272,36 +1267,31 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>CVE-2026-44814</t>
+          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1316,32 +1306,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVE-2026-69845</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1356,32 +1346,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CVE-2026-57085</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1396,32 +1386,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVE-2026-42914</t>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1446,22 +1436,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CVE-2026-62747</t>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1486,22 +1476,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1516,27 +1506,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1551,32 +1546,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1591,27 +1586,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1626,27 +1626,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1661,27 +1666,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1696,27 +1706,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1731,27 +1746,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1766,27 +1786,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1801,27 +1821,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1846,17 +1871,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,17 +1906,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1916,17 +1941,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1951,17 +1976,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -1976,37 +2001,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2021,37 +2036,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2066,37 +2071,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2111,27 +2106,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2146,27 +2141,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2181,32 +2176,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2221,37 +2211,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2262,31 +2242,41 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2297,36 +2287,41 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2337,31 +2332,41 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2372,31 +2377,31 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2407,7 +2412,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2421,17 +2426,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2442,31 +2447,36 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2477,31 +2487,41 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Adobe Acrobat and Reader</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2512,31 +2532,31 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2551,27 +2571,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2596,17 +2621,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2631,17 +2656,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2652,41 +2677,31 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2697,36 +2712,31 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>CVE-2026-58612</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2737,36 +2747,31 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>CVE-2026-62815</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2777,36 +2782,31 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>CVE-2026-84350</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2817,36 +2817,31 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>CVE-2026-84348</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2857,36 +2852,31 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CVE-2026-84324</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2897,36 +2887,31 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>CVE-2026-84347</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2941,32 +2926,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SonicWall</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2991,22 +2981,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-58612</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3031,22 +3021,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-62815</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3071,7 +3061,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3081,12 +3071,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3111,7 +3101,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3121,12 +3111,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3151,7 +3141,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3161,12 +3151,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3191,7 +3181,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3201,12 +3191,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3231,7 +3221,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3241,12 +3231,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3271,7 +3261,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3281,12 +3271,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3311,7 +3301,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3321,12 +3311,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3351,7 +3341,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3361,12 +3351,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3391,7 +3381,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3401,12 +3391,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3431,7 +3421,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3441,12 +3431,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3471,7 +3461,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3481,12 +3471,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3511,7 +3501,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3521,12 +3511,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3551,7 +3541,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3561,12 +3551,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3591,7 +3581,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3601,12 +3591,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3631,7 +3621,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3641,12 +3631,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3671,7 +3661,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3681,12 +3671,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3701,32 +3691,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3741,27 +3731,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3776,27 +3771,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/no-affiliation-with-ransomware-group</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3811,30 +3811,300 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CVE-2026-84335</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CVE-2026-84357</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Google Chrome Releases</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>"Stable Channel Update for Desktop"</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BarracudaAdvisories</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>BarracudaAdvisories</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://trust.barracuda.com/security/no-affiliation-with-ransomware-group</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>Aruba</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I95" headerRowCount="1">
-  <autoFilter ref="A1:I95"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I93" headerRowCount="1">
+  <autoFilter ref="A1:I93"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,32 +1046,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-69334</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1086,37 +1086,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
+          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-20079</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>10.0</t>
+          <t>CVE-2026-69492</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1131,27 +1126,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
+          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CVE-2026-73024</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1166,27 +1166,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1201,27 +1206,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Importing external certificates to Stork"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1236,27 +1251,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1271,27 +1286,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1302,36 +1317,31 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1342,36 +1352,31 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CVE-2026-86853</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1382,36 +1387,31 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1422,36 +1422,31 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>CVE-2026-50696</t>
+          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1462,36 +1457,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>CVE-2026-62697</t>
+          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1506,32 +1496,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVE-2026-54990</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1546,32 +1536,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-44814</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1586,32 +1576,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-69845</t>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1636,22 +1626,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-57085</t>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1676,22 +1666,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-42914</t>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1716,22 +1706,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-62747</t>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1756,7 +1746,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1766,12 +1756,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1786,27 +1776,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1821,32 +1816,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1861,27 +1856,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1896,27 +1896,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1931,27 +1936,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1966,27 +1976,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2001,27 +2016,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2036,27 +2056,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2071,27 +2096,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2106,27 +2136,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2141,27 +2176,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2176,27 +2216,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2211,27 +2256,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2246,37 +2296,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2291,37 +2336,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2336,37 +2376,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2381,27 +2416,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2416,27 +2456,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2451,32 +2496,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2491,37 +2536,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2532,31 +2572,36 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2567,36 +2612,36 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2607,31 +2652,36 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2642,31 +2692,36 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2677,31 +2732,36 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2712,31 +2772,36 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2747,31 +2812,36 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2782,31 +2852,36 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2817,31 +2892,31 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2852,31 +2927,36 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2887,31 +2967,31 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -2922,41 +3002,31 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SonicWall</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://psirtapi.global.sonicwall.com/api/v1/feed/rss.xml</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"SonicWall NSM On-Prem Affected By Multiple Vulnerabilities"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""1) CVE-2026-78327 - Authenticated Command Injection Vulnerability An Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows an authenticated attacker with SuperAdmin privileges to inject arbitrary commands that are executed on the underlying host, resulting in remote code execution. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-78: Improper Neutralization of Special Elements used in an OS Command ('OS Command Injection') 2) CVE-2026-78328 - Privilege Escalation from Admin to SuperAdmin Vulnerability A missing authorization vulnerability in the SonicWall Network Security Manager (NSM) On-Prem Management interface allows a lower-privileged Admin user to escalate privileges to SuperAdmin. CVSS Score: 7.2 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:H/I:H/A:H CWE-862: Missing Authorization 3) CVE-2026-81939 - Zip Slip Vulnerability A Zip Slip vulnerability in the SonicWall Network Security Manager (NSM) On-Prem file upload and archive processing functionality allows an attacker to extract files outside the intended destination directory using a specially crafted archive. CVSS Score: 9.1 CVSS Vector: CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:C/C:H/I:H/A:H CWE-22: Improper Limitation of a Pathname to a Restricted Directory ('Path Traversal') SonicWall strongly advises users of the Network Security Manager (NSM) On-Prem (VMWare, Hyper-V, Azure and KVM) to upgrade to the mentioned fixed release version to address these vulnerabilities. There is currently no evidence any of the vulnerabilities addressed in this release are being exploited in the wild and NSM SaaS versions are not affected by these vulnerabilities. CVE: CVE-2026-78327, CVE-2026-78328, CVE-2026-81939 Last updated: Sept. 3, 2026, 11:35 a.m.""</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>CVE-2026-78328, CVE-2026-78327, CVE-2026-81939</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://psirt.global.sonicwall.com/vuln-detail/SNWLID-2026-0015</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -2967,36 +3037,31 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"CVE-2026-58612 PowerShell Information Disclosure Vulnerability"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>CVE-2026-58612</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-58612</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3007,36 +3072,31 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"CVE-2026-62815 Microsoft QUIC Remote Code Execution Vulnerability"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>CVE-2026-62815</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62815</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3047,36 +3107,31 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>CVE-2026-84350</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3087,36 +3142,31 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>CVE-2026-84348</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3127,36 +3177,31 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>CVE-2026-84324</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3167,36 +3212,31 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>CVE-2026-84347</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3207,36 +3247,31 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>CVE-2026-84325</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3247,36 +3282,31 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>CVE-2026-84349</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3287,36 +3317,31 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>CVE-2026-84331</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3327,36 +3352,41 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3367,36 +3397,41 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3407,36 +3442,41 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3447,36 +3487,31 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>CVE-2026-84351</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3487,36 +3522,31 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>CVE-2026-84323</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3527,36 +3557,36 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3567,36 +3597,41 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Adobe Acrobat and Reader</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3607,36 +3642,31 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>CVE-2026-84327</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3647,36 +3677,36 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3687,36 +3717,31 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>CVE-2026-84356</t>
+          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3727,36 +3752,31 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>CVE-2026-84359</t>
+          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3767,36 +3787,31 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>CVE-2026-84353</t>
+          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3807,36 +3822,31 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>CVE-2026-84328</t>
+          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3847,36 +3857,31 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>CVE-2026-84335</t>
+          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3887,36 +3892,31 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>CVE-2026-84357</t>
+          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -3927,36 +3927,31 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>CVE-2026-84354</t>
+          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -3967,36 +3962,31 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>CVE-2026-85050, CVE-2026-85053, CVE-2026-85052, CVE-2026-85046, CVE-2026-85043, CVE-2026-85045, CVE-2026-85042, CVE-2026-85051, CVE-2026-85044, CVE-2026-85049, CVE-2026-85048, CVE-2026-85047</t>
+          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_01882797386.html</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4007,104 +3997,34 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BarracudaAdvisories</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
+          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://trust.barracuda.com/security/information/no-affiliation-with-ransomware-group</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>BarracudaAdvisories</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>https://www.barracuda.com/company/legal/security-advisory</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>"No Affiliation with “Barracuda” Ransomware Group"</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>https://trust.barracuda.com/security/no-affiliation-with-ransomware-group</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>"HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities"</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>""HPESBNW05145 rev.1 - HPE Telco Intelligent Assurance, Multiple Vulnerabilities""</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05145en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I93" headerRowCount="1">
-  <autoFilter ref="A1:I93"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I84" headerRowCount="1">
+  <autoFilter ref="A1:I84"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,31 +487,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
+          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
+          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -526,32 +526,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
+          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""""</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CVE-2026-0307</t>
+          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
+          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -576,7 +571,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,12 +581,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CVE-2026-0305</t>
+          <t>CVE-2026-0307</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -616,7 +611,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -626,12 +621,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-0306</t>
+          <t>CVE-2026-0305</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -656,7 +651,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
+          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,12 +661,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-0310</t>
+          <t>CVE-2026-0306</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -696,7 +691,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -706,12 +701,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2026-0304</t>
+          <t>CVE-2026-0310</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -736,7 +731,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -746,12 +741,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-0309</t>
+          <t>CVE-2026-0304</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -776,7 +771,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
+          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -786,12 +781,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
+          <t>CVE-2026-0309</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -806,32 +801,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
+          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-85046</t>
+          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
+          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -856,22 +851,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-69777</t>
+          <t>CVE-2026-85046</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -896,7 +891,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -906,12 +901,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CVE-2026-45499</t>
+          <t>CVE-2026-69777</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -936,7 +931,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -946,12 +941,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-68877</t>
+          <t>CVE-2026-45499</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -976,7 +971,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -986,12 +981,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-62693</t>
+          <t>CVE-2026-68877</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1016,7 +1011,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1026,12 +1021,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-69508</t>
+          <t>CVE-2026-62693</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1056,7 +1051,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1066,12 +1061,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-69334</t>
+          <t>CVE-2026-69508</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1096,7 +1091,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1106,12 +1101,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-69492</t>
+          <t>CVE-2026-69334</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1136,7 +1131,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1146,12 +1141,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-73024</t>
+          <t>CVE-2026-69492</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1166,32 +1161,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-73024</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1206,17 +1201,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1226,17 +1221,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-20079</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>10.0</t>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1261,7 +1251,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1269,9 +1259,19 @@
           <t>""</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1286,27 +1286,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Importing external certificates to Stork"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1356,27 +1356,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
+          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
+          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
+          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
+          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1492,36 +1492,31 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1536,17 +1531,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1556,12 +1551,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-86853</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1576,32 +1571,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1616,32 +1611,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-50696</t>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1666,7 +1661,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1676,12 +1671,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-62697</t>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1706,7 +1701,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1716,12 +1711,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-54990</t>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1746,22 +1741,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-44814</t>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1786,7 +1781,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1796,12 +1791,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-69845</t>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1826,7 +1821,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1836,12 +1831,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-57085</t>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1866,7 +1861,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1876,12 +1871,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-42914</t>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1906,7 +1901,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1916,12 +1911,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-62747</t>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1946,7 +1941,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1956,12 +1951,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1986,22 +1981,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2026,7 +2021,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2036,12 +2031,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2066,7 +2061,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2076,12 +2071,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2106,7 +2101,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2116,12 +2111,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2146,7 +2141,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2156,12 +2151,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2186,7 +2181,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2196,12 +2191,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2226,7 +2221,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2236,12 +2231,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2266,7 +2261,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2276,12 +2271,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2306,7 +2301,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2316,12 +2311,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2346,7 +2341,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2356,12 +2351,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2386,7 +2381,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2396,12 +2391,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2426,7 +2421,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2436,12 +2431,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2466,7 +2461,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2476,12 +2471,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2506,7 +2501,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2516,12 +2511,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2546,7 +2541,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2556,12 +2551,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2586,7 +2581,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2596,12 +2591,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2626,7 +2621,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2636,12 +2631,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2666,7 +2661,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2676,12 +2671,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2706,7 +2701,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2716,12 +2711,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2746,7 +2741,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2756,12 +2751,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2786,7 +2781,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2796,12 +2791,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2826,7 +2821,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2836,12 +2831,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2866,7 +2861,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2876,12 +2871,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2896,27 +2891,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2931,32 +2931,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2971,27 +2966,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3051,17 +3051,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3191,17 +3191,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3226,17 +3226,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3356,37 +3356,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3411,7 +3401,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3421,17 +3411,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+          <t>CVE-2026-20293</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3456,7 +3446,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3466,17 +3456,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3491,27 +3481,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3526,27 +3526,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3561,32 +3561,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3601,17 +3596,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3621,17 +3616,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3642,31 +3632,41 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Adobe Acrobat and Reader</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3677,354 +3677,34 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 152.0.4191.66) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>CVE-2021-31937, CVE-2021-21206, CVE-2022-44708, CVE-2021-43221, CVE-2026-0102, CVE-2024-26246, CVE-2022-23263, CVE-2024-38103, CVE-2026-66323, CVE-2025-26643, CVE-2023-2033, CVE-2022-33680, CVE-2023-28286, CVE-2021-21224, CVE-2023-36880, CVE-2021-30632, CVE-2024-21326, CVE-2025-4664, CVE-2021-36929, CVE-2024-38093, CVE-2024-26196, CVE-2020-6418, CVE-2024-38221, CVE-2022-29147, CVE-2025-21253, CVE-2024-38218, CVE-2024-26163, CVE-2022-21931, CVE-2022-30128, CVE-2022-1096, CVE-2022-26895, CVE-2024-29981, CVE-2023-5217, CVE-2025-29825, CVE-2022-33636, CVE-2024-43489, CVE-2023-21720, CVE-2024-4761, CVE-2024-2883, CVE-2022-3723, CVE-2023-6345, CVE-2024-43496, CVE-2024-0519, CVE-2024-43579, CVE-2023-36887, CVE-2025-24201, CVE-2026-66316, CVE-2023-36888, CVE-2026-66317, CVE-2024-38083, CVE-2025-47963, CVE-2023-21775, CVE-2025-21342, CVE-2022-33639, CVE-2022-24523, CVE-2023-36727, CVE-2026-65804, CVE-2022-41035, CVE-2026-3909, CVE-2024-38219, CVE-2023-23374, CVE-2026-11645, CVE-2022-35796, CVE-2022-29144, CVE-2021-43220, CVE-2021-30633, CVE-2024-30056, CVE-2025-47964, CVE-2024-5274, CVE-2021-34475, CVE-2022-33638, CVE-2022-30127, CVE-2023-38173, CVE-2022-23261, CVE-2026-58616, CVE-2025-13223, CVE-2025-5419, CVE-2023-36024, CVE-2022-41115, CVE-2022-2856, CVE-2021-38669, CVE-2026-66312, CVE-2023-21719, CVE-2023-44323, CVE-2026-72984, CVE-2024-41879, CVE-2023-36008, CVE-2021-21220, CVE-2024-49025, CVE-2023-0941, CVE-2022-23258, CVE-2021-38641, CVE-2026-72970, CVE-2024-20709, CVE-2026-21223, CVE-2025-62223, CVE-2023-38174, CVE-2023-29350, CVE-2023-36034, CVE-2022-2294, CVE-2023-7024, CVE-2026-66324, CVE-2023-33145, CVE-2026-45492, CVE-2023-36741, CVE-2020-16009, CVE-2025-21185, CVE-2024-20675, CVE-2023-28261, CVE-2021-37975, CVE-2021-36931, CVE-2021-21193, CVE-2021-42308, CVE-2024-43580, CVE-2025-6554, CVE-2024-21336, CVE-2021-34506, CVE-2021-36928, CVE-2025-47182, CVE-2023-38157, CVE-2024-26192, CVE-2021-37976, CVE-2026-2441, CVE-2022-33649, CVE-2024-39379, CVE-2026-5281, CVE-2026-41107, CVE-2020-1195, CVE-2026-85046, CVE-2021-4102, CVE-2024-26188, CVE-2024-21383, CVE-2026-0385, CVE-2022-26908, CVE-2022-22021, CVE-2022-4135, CVE-2026-66311, CVE-2024-49041, CVE-2021-38642, CVE-2025-21267, CVE-2024-49054, CVE-2021-26436, CVE-2026-33119, CVE-2024-30058, CVE-2020-1341, CVE-2023-29345, CVE-2022-4262, CVE-2022-26900, CVE-2022-1364, CVE-2021-26439, CVE-2024-21385, CVE-2025-21399, CVE-2026-33118, CVE-2022-3075, CVE-2024-38207, CVE-2024-29986, CVE-2022-0609, CVE-2023-4863, CVE-2021-30554, CVE-2026-65802, CVE-2026-42838, CVE-2023-36027, CVE-2024-20721, CVE-2023-24935, CVE-2023-36026, CVE-2021-37973, CVE-2026-66798, CVE-2023-36883, CVE-2022-23264, CVE-2021-21148, CVE-2026-26133, CVE-2024-4947, CVE-2024-38208, CVE-2022-21954, CVE-2024-7965, CVE-2020-15999, CVE-2025-29796, CVE-2024-43587, CVE-2023-36878, CVE-2023-29354, CVE-2025-29795, CVE-2024-26247, CVE-2023-3079, CVE-2025-25000, CVE-2025-60711, CVE-2021-24113, CVE-2023-21796, CVE-2020-16013, CVE-2021-21166, CVE-2024-43472, CVE-2022-21929, CVE-2026-66322, CVE-2026-62904, CVE-2022-30192, CVE-2025-21401, CVE-2024-29049, CVE-2026-40416, CVE-2025-10585, CVE-2024-26167, CVE-2022-29146, CVE-2025-21404, CVE-2022-24475, CVE-2026-66313, CVE-2025-21283, CVE-2026-70341, CVE-2024-49023, CVE-2024-21423, CVE-2026-66321, CVE-2026-3910, CVE-2024-38210, CVE-2024-38082, CVE-2024-21388, CVE-2023-36029, CVE-2023-38187, CVE-2024-29987, CVE-2023-36735, CVE-2023-29334, CVE-2025-47967, CVE-2025-21279, CVE-2024-7971, CVE-2023-33143, CVE-2021-30551, CVE-2024-38209, CVE-2024-38156, CVE-2024-21382, CVE-2024-29991, CVE-2026-66325, CVE-2024-21387, CVE-2025-53791, CVE-2026-66310, CVE-2023-28284, CVE-2025-6558, CVE-2023-35618, CVE-2023-36022, CVE-2023-36559, CVE-2025-21262, CVE-2022-38012, CVE-2020-16017, CVE-2024-43595, CVE-2023-38158, CVE-2026-66326, CVE-2024-43566, CVE-2025-47181, CVE-2022-26891, CVE-2024-29057, CVE-2024-43578, CVE-2022-26894, CVE-2022-26899, CVE-2025-21408, CVE-2026-66318, CVE-2024-38222, CVE-2024-30057, CVE-2025-2783, CVE-2024-4671, CVE-2023-36787, CVE-2023-35392, CVE-2023-2136, CVE-2021-38003, CVE-2021-33741, CVE-2026-66314, CVE-2024-21337, CVE-2023-21795, CVE-2022-44688, CVE-2024-43596, CVE-2022-26905, CVE-2023-21794, CVE-2022-26912, CVE-2023-36562, CVE-2021-38000, CVE-2022-26909, CVE-2024-30055, CVE-2026-45495, CVE-2025-29834, CVE-2022-21970, CVE-2026-45494, CVE-2025-49713, CVE-2023-36014, CVE-2022-23262, CVE-2021-36930, CVE-2022-21930, CVE-2024-21399, CVE-2024-43577, CVE-2021-31982, CVE-2023-28301, CVE-2021-30563, CVE-2026-66315</t>
+          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-4-2026</t>
+          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>"HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>""HPESBHF05109 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01437, Intel Intel UEFI Firmware Advisory, Disclosure of Information Vulnerability""</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05109en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>"HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>""HPESBHF05094 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01372, VRT0010, Intel Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05094en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>"HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege"</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>""HPESBHF05120 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01442, Intel Xeon Processor Firmware Advisory, Local Escalation of Privilege""</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05120en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>"HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>""HPESBHF05128 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01423, 2026.3 IPU, Intel Processor Load Value Injection Zero Data Advisory, Local Disclosure of Information Vulnerability""</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05128en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>"HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities"</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>""HPESBHF05108 rev.1 - HPE StoreEasy Server Using Certain Intel Processors, INTEL-SA-01436, Intel Trust Domain Extensions (Intel TDX) module Advisory, Multiple Vulnerabilities""</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05108en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>"HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>""HPESBHF05110 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05110en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>"HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege"</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>""HPESBHF05143 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01439, Intel Xeon processor with Alias Checking Trusted Module Advisory, Local Escalation of Privilege""</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05143en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>"HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability"</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>""HPESBHF05095 rev.1 - HPE StoreEasy Servers Using Certain Intel Processors, INTEL-SA-01371, VRT0011, Intel® Chipset Firmware Advisory, Local Escalation of Privilege Vulnerability""</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05095en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>未投稿</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>"HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities"</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>""HPESBNW05141 rev.1 - HPE Telco Network Function Virtual Orchestrator, Multiple Vulnerabilities""</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05141en_us&amp;docLocale=en_US</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I84" headerRowCount="1">
-  <autoFilter ref="A1:I84"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I85" headerRowCount="1">
+  <autoFilter ref="A1:I85"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,27 +491,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
+          <t>"CVE-2026-70334 Visual Studio Code Security Feature Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CVE-2026-70334</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-70334</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,31 +527,31 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
+          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
+          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -561,32 +566,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
+          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""""</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CVE-2026-0307</t>
+          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
+          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -621,12 +621,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-0305</t>
+          <t>CVE-2026-0307</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-0306</t>
+          <t>CVE-2026-0305</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
+          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2026-0310</t>
+          <t>CVE-2026-0306</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-0304</t>
+          <t>CVE-2026-0310</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-0309</t>
+          <t>CVE-2026-0304</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
+          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
+          <t>CVE-2026-0309</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -841,32 +841,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
+          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-85046</t>
+          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
+          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CVE-2026-69777</t>
+          <t>CVE-2026-85046</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-45499</t>
+          <t>CVE-2026-69777</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-68877</t>
+          <t>CVE-2026-45499</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-62693</t>
+          <t>CVE-2026-68877</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-69508</t>
+          <t>CVE-2026-62693</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-69334</t>
+          <t>CVE-2026-69508</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-69492</t>
+          <t>CVE-2026-69334</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-73024</t>
+          <t>CVE-2026-69492</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1201,32 +1201,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-73024</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1241,17 +1241,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1261,17 +1261,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-20079</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>10.0</t>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1296,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1304,9 +1299,19 @@
           <t>""</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1321,27 +1326,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1366,17 +1371,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Importing external certificates to Stork"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1391,27 +1396,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1436,17 +1441,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1471,17 +1476,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
+          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
+          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1506,17 +1511,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
+          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
+          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1527,36 +1532,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-86853</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1611,32 +1611,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-50696</t>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-62697</t>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-54990</t>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-44814</t>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-69845</t>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-57085</t>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1911,12 +1911,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-42914</t>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-62747</t>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1991,12 +1991,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2271,12 +2271,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2931,27 +2931,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2966,32 +2971,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3006,27 +3006,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3051,17 +3056,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3086,17 +3091,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3121,17 +3126,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3156,17 +3161,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3191,17 +3196,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3226,17 +3231,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3261,17 +3266,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3296,17 +3301,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3331,17 +3336,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3366,17 +3371,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3391,37 +3396,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"Open Redirect on FortiSIEM"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3446,7 +3441,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3456,17 +3451,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+          <t>CVE-2026-20293</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3491,7 +3486,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3501,17 +3496,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3526,27 +3521,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>5.9</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3561,27 +3566,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3596,32 +3601,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>Android OS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"September 2026"</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3656,17 +3656,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3677,34 +3672,79 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat and Reader</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>BIND</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I85" headerRowCount="1">
-  <autoFilter ref="A1:I85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I126" headerRowCount="1">
+  <autoFilter ref="A1:I126"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,27 +531,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
+          <t>"Chromium CVE-2026-76023:Improper resource control in Linux Toolkit Theming"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CVE-2026-76023</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76023</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -562,31 +567,36 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
+          <t>"CVE-2026-69314 Windows Device Association Broker Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CVE-2026-69314</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69314</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -597,36 +607,36 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-77490 Microsoft Edge (Chromium-based) Spoofing Vulnerability"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""Improper neutralization of input during web page generation ('cross-site scripting') in Microsoft Edge (Chromium-based) allows an unauthorized attacker to perform spoofing over a network.""</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-0307</t>
+          <t>CVE-2026-77490</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77490</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -637,36 +647,36 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
+          <t>"Chromium CVE-2026-76018:Privilege elevation in Import"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-0305</t>
+          <t>CVE-2026-76018</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76018</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -677,36 +687,36 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-62799 Windows SMB Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2026-0306</t>
+          <t>CVE-2026-62799</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62799</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -717,36 +727,36 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
+          <t>"CVE-2026-73016 DirectWrite Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-0310</t>
+          <t>CVE-2026-73016</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73016</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -757,36 +767,36 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-69860 Windows Imaging Component Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-0304</t>
+          <t>CVE-2026-69860</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69860</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -797,36 +807,36 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
+          <t>"Chromium: CVE-2026-84333 Use after free in Dawn"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-0309</t>
+          <t>CVE-2026-84333</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84333</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -837,36 +847,36 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
+          <t>"Chromium CVE-2026-76036:Buffer overflow in Dawn"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
+          <t>CVE-2026-76036</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76036</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -877,7 +887,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -891,22 +901,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
+          <t>"Chromium CVE-2026-85042:Use after free in DevTools"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CVE-2026-85046</t>
+          <t>CVE-2026-85042</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85042</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -917,7 +927,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -931,22 +941,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85049:Use after free in Skia"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-69777</t>
+          <t>CVE-2026-85049</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85049</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -957,7 +967,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -971,7 +981,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-81963 Windows Update Stack Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -981,12 +991,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-45499</t>
+          <t>CVE-2026-81963</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81963</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -997,7 +1007,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1011,7 +1021,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-77499 Windows DHCP Server Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1021,12 +1031,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-68877</t>
+          <t>CVE-2026-77499</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77499</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1037,7 +1047,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1051,7 +1061,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-80080 Microsoft Office Word Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1061,12 +1071,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-62693</t>
+          <t>CVE-2026-80080</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-80080</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1077,7 +1087,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-81379 Visual Studio Code Security Feature Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1101,12 +1111,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-69508</t>
+          <t>CVE-2026-81379</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81379</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1117,7 +1127,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1131,7 +1141,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-68894 Windows Error Reporting Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1141,12 +1151,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-69334</t>
+          <t>CVE-2026-68894</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68894</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1157,7 +1167,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1171,7 +1181,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69732 Windows Link Layer Topology Discovery Protocol Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1181,12 +1191,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-69492</t>
+          <t>CVE-2026-69732</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69732</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1197,7 +1207,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1211,22 +1221,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85043:Incomplete cleanup in Network"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-73024</t>
+          <t>CVE-2026-85043</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85043</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1237,36 +1247,36 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"Chromium CVE-2026-85045:Race condition in V8"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-85045</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85045</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1277,41 +1287,36 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
+          <t>"CVE-2026-81355 Virtual Hard Disk (VHD) Miniport Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CVE-2026-20079</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>10.0</t>
+          <t>CVE-2026-81355</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81355</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1322,31 +1327,36 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
+          <t>"Chromium CVE-2026-85051:Type confusion in Compositing"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CVE-2026-85051</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85051</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1357,31 +1367,36 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"Chromium: CVE-2026-84352 Use after free in WebGL"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CVE-2026-84352</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84352</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1392,31 +1407,36 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"Importing external certificates to Stork"</t>
+          <t>"CVE-2026-69468 Windows Volume Manager Extension Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CVE-2026-69468</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69468</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1427,31 +1447,36 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"CVE-2026-71336 Windows Work Folder Service Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CVE-2026-71336</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-71336</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1462,31 +1487,36 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
+          <t>"Chromium CVE-2026-85048:Use after free in Compositing"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CVE-2026-85048</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85048</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1497,31 +1527,36 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
+          <t>"Chromium CVE-2026-76021:Use after free in DOM"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>CVE-2026-76021</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76021</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1532,31 +1567,36 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
+          <t>"Chromium CVE-2026-85052:Out of bounds read in CrashReporting"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CVE-2026-85052</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85052</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1567,36 +1607,36 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"CVE-2026-50676 Windows Media Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>CVE-2026-50676</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50676</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1607,36 +1647,36 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"Chromium CVE-2026-85053:Improper resource exposure in CacheStorage"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-86853</t>
+          <t>CVE-2026-85053</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85053</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1647,36 +1687,36 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"CVE-2026-69461 Windows NTFS Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>CVE-2026-69461</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69461</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1687,7 +1727,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1701,22 +1741,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-54124 Windows Terminal Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-50696</t>
+          <t>CVE-2026-54124</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54124</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1727,7 +1767,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1741,22 +1781,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69405 Windows DHCP Server Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-62697</t>
+          <t>CVE-2026-69405</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69405</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1767,7 +1807,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1781,22 +1821,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-61349 Windows Work Folder Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-54990</t>
+          <t>CVE-2026-61349</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-61349</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1807,7 +1847,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1821,22 +1861,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"Chromium CVE-2026-76017:Use after free in Chromoting"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-44814</t>
+          <t>CVE-2026-76017</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76017</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1847,7 +1887,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1861,7 +1901,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-54112 Windows Win32k Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1871,12 +1911,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-69845</t>
+          <t>CVE-2026-54112</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54112</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1887,7 +1927,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1901,7 +1941,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-50679 Windows Search Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1911,12 +1951,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-57085</t>
+          <t>CVE-2026-50679</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50679</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1927,7 +1967,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1941,22 +1981,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"Chromium CVE-2026-76022:Buffer overflow in Network"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-42914</t>
+          <t>CVE-2026-76022</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76022</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1967,7 +2007,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1981,22 +2021,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-76019:Incorrect authorization in Workers"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-62747</t>
+          <t>CVE-2026-76019</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76019</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2007,7 +2047,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2021,22 +2061,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"Chromium CVE-2026-76039:Incorrect reference resolution in Core"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-76039</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76039</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2047,7 +2087,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2061,7 +2101,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"Chromium: CVE-2026-84330 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2071,12 +2111,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-84330</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84330</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2087,36 +2127,31 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>CVE-2026-84326</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2127,36 +2162,36 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 153.0.4234.32) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2023-33145, CVE-2026-3910, CVE-2026-42838, CVE-2024-21337, CVE-2025-21279, CVE-2024-30056, CVE-2021-30554, CVE-2026-66313, CVE-2022-23263, CVE-2023-35618, CVE-2023-36883, CVE-2024-21382, CVE-2022-3723, CVE-2022-24475, CVE-2020-16017, CVE-2026-66316, CVE-2022-26894, CVE-2024-21388, CVE-2025-26643, CVE-2026-45494, CVE-2026-0102, CVE-2021-38669, CVE-2026-66315, CVE-2023-36727, CVE-2026-66311, CVE-2023-36559, CVE-2023-2033, CVE-2023-0941, CVE-2022-30192, CVE-2021-21224, CVE-2020-6418, CVE-2024-38082, CVE-2023-21720, CVE-2026-11645, CVE-2022-26912, CVE-2023-2136, CVE-2024-21336, CVE-2023-36008, CVE-2023-28286, CVE-2022-38012, CVE-2022-30127, CVE-2025-49713, CVE-2023-36014, CVE-2025-62223, CVE-2024-4947, CVE-2025-21408, CVE-2026-66317, CVE-2025-21253, CVE-2024-20675, CVE-2024-26246, CVE-2022-33680, CVE-2024-41879, CVE-2024-38209, CVE-2021-30563, CVE-2025-5419, CVE-2025-29834, CVE-2026-66321, CVE-2023-36741, CVE-2022-44688, CVE-2021-30551, CVE-2023-36878, CVE-2024-30058, CVE-2024-43496, CVE-2025-53791, CVE-2024-7971, CVE-2024-26192, CVE-2022-26891, CVE-2026-33119, CVE-2025-29825, CVE-2026-2441, CVE-2023-24935, CVE-2025-47182, CVE-2025-10585, CVE-2025-21267, CVE-2023-36022, CVE-2023-33143, CVE-2026-62904, CVE-2023-21795, CVE-2022-30128, CVE-2022-21970, CVE-2026-40416, CVE-2026-66798, CVE-2026-66325, CVE-2024-21326, CVE-2025-47181, CVE-2026-45495, CVE-2024-7965, CVE-2022-26909, CVE-2026-70341, CVE-2023-29334, CVE-2021-4102, CVE-2024-38083, CVE-2024-0519, CVE-2022-4135, CVE-2021-21148, CVE-2023-6345, CVE-2020-15999, CVE-2021-26439, CVE-2021-43221, CVE-2024-21387, CVE-2021-37973, CVE-2021-30633, CVE-2023-44323, CVE-2024-43595, CVE-2026-58616, CVE-2024-26196, CVE-2023-36562, CVE-2023-36024, CVE-2023-29350, CVE-2025-47967, CVE-2025-21283, CVE-2022-23261, CVE-2026-65802, CVE-2022-26895, CVE-2023-3079, CVE-2025-21262, CVE-2026-66326, CVE-2026-72970, CVE-2026-33118, CVE-2025-47964, CVE-2025-21404, CVE-2023-38173, CVE-2024-49023, CVE-2024-38207, CVE-2023-21775, CVE-2022-26900, CVE-2024-21399, CVE-2025-29795, CVE-2024-38218, CVE-2022-4262, CVE-2021-36931, CVE-2026-66324, CVE-2022-2856, CVE-2020-1195, CVE-2024-21383, CVE-2021-36929, CVE-2021-30632, CVE-2022-21954, CVE-2024-43587, CVE-2023-35392, CVE-2024-38221, CVE-2024-26167, CVE-2025-47963, CVE-2023-38157, CVE-2025-6554, CVE-2024-2883, CVE-2024-20709, CVE-2023-7024, CVE-2022-33638, CVE-2023-28301, CVE-2023-36034, CVE-2024-38219, CVE-2021-38642, CVE-2024-30057, CVE-2026-26133, CVE-2024-43578, CVE-2021-38003, CVE-2023-21794, CVE-2020-1341, CVE-2024-38222, CVE-2022-0609, CVE-2026-65804, CVE-2026-72984, CVE-2022-29146, CVE-2022-23264, CVE-2026-21223, CVE-2025-21401, CVE-2021-37976, CVE-2026-85046, CVE-2021-21220, CVE-2022-41035, CVE-2023-4863, CVE-2023-36026, CVE-2023-36888, CVE-2026-66312, CVE-2025-24201, CVE-2023-23374, CVE-2021-34506, CVE-2022-26899, CVE-2024-4671, CVE-2021-31982, CVE-2026-0385, CVE-2024-49054, CVE-2023-36735, CVE-2023-28284, CVE-2022-1364, CVE-2024-43577, CVE-2024-26188, CVE-2021-36930, CVE-2024-29987, CVE-2026-66310, CVE-2023-38158, CVE-2020-16013, CVE-2025-6558, CVE-2021-21166, CVE-2026-3909, CVE-2024-38156, CVE-2021-38000, CVE-2023-29354, CVE-2026-66318, CVE-2024-30055, CVE-2026-45492, CVE-2022-29147, CVE-2022-29144, CVE-2024-43472, CVE-2022-24523, CVE-2023-28261, CVE-2023-36880, CVE-2024-38103, CVE-2025-21399, CVE-2024-29991, CVE-2022-26908, CVE-2021-34475, CVE-2025-2783, CVE-2024-21385, CVE-2023-21796, CVE-2021-33741, CVE-2022-2294, CVE-2024-20721, CVE-2026-66314, CVE-2024-21423, CVE-2024-29057, CVE-2022-21929, CVE-2023-36029, CVE-2025-13223, CVE-2024-29981, CVE-2022-21931, CVE-2024-43596, CVE-2024-38208, CVE-2026-41107, CVE-2022-21930, CVE-2025-60711, CVE-2023-36787, CVE-2024-29049, CVE-2022-33649, CVE-2025-4664, CVE-2021-21206, CVE-2024-4761, CVE-2025-21342, CVE-2020-16009, CVE-2022-26905, CVE-2025-25000, CVE-2021-43220, CVE-2021-24113, CVE-2026-66322, CVE-2021-21193, CVE-2024-26247, CVE-2024-43579, CVE-2024-43489, CVE-2022-33639, CVE-2025-29796, CVE-2023-36027, CVE-2022-3075, CVE-2022-35796, CVE-2021-26436, CVE-2024-38093, CVE-2024-5274, CVE-2024-39379, CVE-2024-38210, CVE-2021-42308, CVE-2025-21185, CVE-2024-29986, CVE-2021-37975, CVE-2022-22021, CVE-2026-5281, CVE-2026-66323, CVE-2024-49041, CVE-2024-43566, CVE-2023-5217, CVE-2021-38641, CVE-2026-85892, CVE-2022-23262, CVE-2021-36928, CVE-2021-31937, CVE-2024-43580, CVE-2022-33636, CVE-2024-49025, CVE-2023-21719, CVE-2022-44708, CVE-2023-29345, CVE-2023-36887, CVE-2023-38174, CVE-2026-87491, CVE-2022-41115, CVE-2022-1096, CVE-2023-38187, CVE-2022-23258, CVE-2024-26163</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-10-2026</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2167,36 +2202,31 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>CVE-2026-84324</t>
+          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2207,36 +2237,36 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-0307</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2247,36 +2277,36 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-0305</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2287,36 +2317,36 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-0306</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2327,36 +2357,36 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-0310</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2367,36 +2397,36 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-0304</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2407,36 +2437,36 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-0309</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2447,36 +2477,36 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2487,7 +2517,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2501,22 +2531,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-85046</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2527,7 +2557,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2541,22 +2571,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-69777</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2567,7 +2597,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2581,22 +2611,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-45499</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2607,7 +2637,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2621,22 +2651,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-68877</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2647,7 +2677,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2661,22 +2691,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-62693</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2687,7 +2717,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2701,22 +2731,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-69508</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2727,7 +2757,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2741,22 +2771,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-69334</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2767,7 +2797,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2781,22 +2811,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-69492</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2807,7 +2837,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2821,22 +2851,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-73024</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2847,36 +2877,36 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2887,36 +2917,41 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2927,36 +2962,31 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CVE-2026-84328</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2967,31 +2997,31 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3002,36 +3032,31 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3042,31 +3067,31 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3077,31 +3102,31 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3112,31 +3137,31 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3147,31 +3172,31 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3186,27 +3211,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3221,27 +3251,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3256,27 +3291,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3291,27 +3331,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3326,27 +3371,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3361,27 +3411,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Acknowledgement Updated""</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3396,27 +3451,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3431,37 +3491,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3476,37 +3531,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3521,37 +3571,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3566,27 +3611,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3601,27 +3651,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3636,32 +3691,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3676,37 +3731,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3717,34 +3767,1624 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CVE-2026-84329</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CVE-2026-84324</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CVE-2026-84357</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CVE-2026-84354</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CVE-2026-84353</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CVE-2026-84350</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CVE-2026-84348</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CVE-2026-84331</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CVE-2026-84351</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CVE-2026-84335</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>CVE-2026-84334</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CVE-2026-84323</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CVE-2026-84358</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CVE-2026-84355</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CVE-2026-84347</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>CVE-2026-84356</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>CVE-2026-84332</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CVE-2026-84359</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CVE-2026-84327</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CVE-2026-84349</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Microsoft Edge</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ivanti</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>"September 2026 Security Update"</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Google Chrome Releases</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>"Stable Channel Update for Desktop"</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>"Workflow session email approval process bypass"</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>"Cron Job Injection in Remote Backup"</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>"Null Pointer Dereference in Log Report"</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>"Broken Access control on Websocket streams"</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>"Improper Authentication of FortiPAM Server"</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>"Open Redirect on FortiSIEM"</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BIND</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://kb.isc.org/v1/rss/en</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Android OS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>"September 2026"</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat and Reader</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
         <v>46272</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>BIND</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>"DNSSEC Key and Signing Policy"</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I126" headerRowCount="1">
-  <autoFilter ref="A1:I126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I133" headerRowCount="1">
+  <autoFilter ref="A1:I133"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,36 +487,36 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"CVE-2026-70334 Visual Studio Code Security Feature Bypass Vulnerability"</t>
+          <t>"CVE-2026-0295 GlobalProtect App: Local Privilege Escalation via Race Condition on macOS (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CVE-2026-70334</t>
+          <t>CVE-2026-0295</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-70334</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0295</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -527,36 +527,36 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76023:Improper resource control in Linux Toolkit Theming"</t>
+          <t>"CVE-2026-0298 GlobalProtect App: Code Execution Vulnerability in Windows Pre-Logon Access Provider (PLAP) (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CVE-2026-76023</t>
+          <t>CVE-2026-0298</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76023</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0298</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -567,36 +567,36 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"CVE-2026-69314 Windows Device Association Broker Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-0250 GlobalProtect App: Buffer Overflow Vulnerability during connection to Portal or Gateway (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CVE-2026-69314</t>
+          <t>CVE-2026-0250</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69314</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0250</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,36 +607,36 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-77490 Microsoft Edge (Chromium-based) Spoofing Vulnerability"</t>
+          <t>"CVE-2026-0299 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""Improper neutralization of input during web page generation ('cross-site scripting') in Microsoft Edge (Chromium-based) allows an unauthorized attacker to perform spoofing over a network.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-77490</t>
+          <t>CVE-2026-0299</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77490</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0299</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -647,36 +647,36 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76018:Privilege elevation in Import"</t>
+          <t>"CVE-2026-0297 GlobalProtect App: Buffer Overflow Vulnerability during UDP Tunnel Handshake (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-76018</t>
+          <t>CVE-2026-0297</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76018</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0297</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -687,36 +687,36 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"CVE-2026-62799 Windows SMB Client Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-0296 GlobalProtect App: Improper Certificate Validation Bypass Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2026-62799</t>
+          <t>CVE-2026-0296</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62799</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0296</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"CVE-2026-73016 DirectWrite Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-70334 Visual Studio Code Security Feature Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-73016</t>
+          <t>CVE-2026-70334</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73016</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-70334</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -781,22 +781,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"CVE-2026-69860 Windows Imaging Component Remote Code Execution Vulnerability"</t>
+          <t>"Chromium CVE-2026-76023:Improper resource control in Linux Toolkit Theming"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-69860</t>
+          <t>CVE-2026-76023</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69860</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76023</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -821,22 +821,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84333 Use after free in Dawn"</t>
+          <t>"CVE-2026-69314 Windows Device Association Broker Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-84333</t>
+          <t>CVE-2026-69314</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84333</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69314</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -861,22 +861,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76036:Buffer overflow in Dawn"</t>
+          <t>"CVE-2026-77490 Microsoft Edge (Chromium-based) Spoofing Vulnerability"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Improper neutralization of input during web page generation ('cross-site scripting') in Microsoft Edge (Chromium-based) allows an unauthorized attacker to perform spoofing over a network.""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-76036</t>
+          <t>CVE-2026-77490</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76036</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77490</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85042:Use after free in DevTools"</t>
+          <t>"Chromium CVE-2026-76018:Privilege elevation in Import"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CVE-2026-85042</t>
+          <t>CVE-2026-76018</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85042</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76018</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85049:Use after free in Skia"</t>
+          <t>"CVE-2026-62799 Windows SMB Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-85049</t>
+          <t>CVE-2026-62799</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85049</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62799</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-81963 Windows Update Stack Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-73016 DirectWrite Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-81963</t>
+          <t>CVE-2026-73016</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81963</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73016</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-77499 Windows DHCP Server Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-69860 Windows Imaging Component Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-77499</t>
+          <t>CVE-2026-69860</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77499</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69860</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"CVE-2026-80080 Microsoft Office Word Remote Code Execution Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84333 Use after free in Dawn"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-80080</t>
+          <t>CVE-2026-84333</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-80080</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84333</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"CVE-2026-81379 Visual Studio Code Security Feature Bypass Vulnerability"</t>
+          <t>"Chromium CVE-2026-76036:Buffer overflow in Dawn"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-81379</t>
+          <t>CVE-2026-76036</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81379</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76036</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1141,22 +1141,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"CVE-2026-68894 Windows Error Reporting Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85042:Use after free in DevTools"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-68894</t>
+          <t>CVE-2026-85042</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68894</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85042</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"CVE-2026-69732 Windows Link Layer Topology Discovery Protocol Remote Code Execution Vulnerability"</t>
+          <t>"Chromium CVE-2026-85049:Use after free in Skia"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-69732</t>
+          <t>CVE-2026-85049</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69732</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85049</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1221,22 +1221,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85043:Incomplete cleanup in Network"</t>
+          <t>"CVE-2026-81963 Windows Update Stack Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-85043</t>
+          <t>CVE-2026-81963</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85043</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81963</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85045:Race condition in V8"</t>
+          <t>"CVE-2026-77499 Windows DHCP Server Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-85045</t>
+          <t>CVE-2026-77499</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85045</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77499</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"CVE-2026-81355 Virtual Hard Disk (VHD) Miniport Driver Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-80080 Microsoft Office Word Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CVE-2026-81355</t>
+          <t>CVE-2026-80080</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-80080</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85051:Type confusion in Compositing"</t>
+          <t>"CVE-2026-81379 Visual Studio Code Security Feature Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVE-2026-85051</t>
+          <t>CVE-2026-81379</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85051</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81379</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1381,22 +1381,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84352 Use after free in WebGL"</t>
+          <t>"CVE-2026-68894 Windows Error Reporting Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CVE-2026-84352</t>
+          <t>CVE-2026-68894</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84352</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68894</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"CVE-2026-69468 Windows Volume Manager Extension Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69732 Windows Link Layer Topology Discovery Protocol Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVE-2026-69468</t>
+          <t>CVE-2026-69732</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69468</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69732</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1461,22 +1461,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"CVE-2026-71336 Windows Work Folder Service Remote Code Execution Vulnerability"</t>
+          <t>"Chromium CVE-2026-85043:Incomplete cleanup in Network"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CVE-2026-71336</t>
+          <t>CVE-2026-85043</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-71336</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85043</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85048:Use after free in Compositing"</t>
+          <t>"Chromium CVE-2026-85045:Race condition in V8"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVE-2026-85048</t>
+          <t>CVE-2026-85045</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85048</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85045</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76021:Use after free in DOM"</t>
+          <t>"CVE-2026-81355 Virtual Hard Disk (VHD) Miniport Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVE-2026-76021</t>
+          <t>CVE-2026-81355</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76021</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81355</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85052:Out of bounds read in CrashReporting"</t>
+          <t>"Chromium CVE-2026-85051:Type confusion in Compositing"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-85052</t>
+          <t>CVE-2026-85051</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85052</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85051</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1621,22 +1621,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"CVE-2026-50676 Windows Media Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84352 Use after free in WebGL"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-50676</t>
+          <t>CVE-2026-84352</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50676</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84352</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85053:Improper resource exposure in CacheStorage"</t>
+          <t>"CVE-2026-69468 Windows Volume Manager Extension Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-85053</t>
+          <t>CVE-2026-69468</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85053</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69468</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"CVE-2026-69461 Windows NTFS Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-71336 Windows Work Folder Service Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-69461</t>
+          <t>CVE-2026-71336</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69461</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-71336</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1741,22 +1741,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"CVE-2026-54124 Windows Terminal Remote Code Execution Vulnerability"</t>
+          <t>"Chromium CVE-2026-85048:Use after free in Compositing"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-54124</t>
+          <t>CVE-2026-85048</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54124</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85048</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1781,22 +1781,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"CVE-2026-69405 Windows DHCP Server Denial of Service Vulnerability"</t>
+          <t>"Chromium CVE-2026-76021:Use after free in DOM"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-69405</t>
+          <t>CVE-2026-76021</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69405</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76021</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1821,22 +1821,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"CVE-2026-61349 Windows Work Folder Service Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85052:Out of bounds read in CrashReporting"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-61349</t>
+          <t>CVE-2026-85052</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-61349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85052</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1861,22 +1861,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76017:Use after free in Chromoting"</t>
+          <t>"CVE-2026-50676 Windows Media Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-76017</t>
+          <t>CVE-2026-50676</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76017</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50676</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1901,22 +1901,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"CVE-2026-54112 Windows Win32k Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85053:Improper resource exposure in CacheStorage"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-54112</t>
+          <t>CVE-2026-85053</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54112</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85053</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"CVE-2026-50679 Windows Search Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-69461 Windows NTFS Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-50679</t>
+          <t>CVE-2026-69461</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50679</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69461</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1981,22 +1981,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76022:Buffer overflow in Network"</t>
+          <t>"CVE-2026-54124 Windows Terminal Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-76022</t>
+          <t>CVE-2026-54124</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76022</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54124</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76019:Incorrect authorization in Workers"</t>
+          <t>"CVE-2026-69405 Windows DHCP Server Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-76019</t>
+          <t>CVE-2026-69405</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76019</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69405</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76039:Incorrect reference resolution in Core"</t>
+          <t>"CVE-2026-61349 Windows Work Folder Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-76039</t>
+          <t>CVE-2026-61349</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76039</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-61349</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84330 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium CVE-2026-76017:Use after free in Chromoting"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-84330</t>
+          <t>CVE-2026-76017</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84330</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76017</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,27 +2131,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
+          <t>"CVE-2026-54112 Windows Win32k Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CVE-2026-54112</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54112</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2162,36 +2167,36 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"CVE-2026-50679 Windows Search Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 153.0.4234.32) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2023-33145, CVE-2026-3910, CVE-2026-42838, CVE-2024-21337, CVE-2025-21279, CVE-2024-30056, CVE-2021-30554, CVE-2026-66313, CVE-2022-23263, CVE-2023-35618, CVE-2023-36883, CVE-2024-21382, CVE-2022-3723, CVE-2022-24475, CVE-2020-16017, CVE-2026-66316, CVE-2022-26894, CVE-2024-21388, CVE-2025-26643, CVE-2026-45494, CVE-2026-0102, CVE-2021-38669, CVE-2026-66315, CVE-2023-36727, CVE-2026-66311, CVE-2023-36559, CVE-2023-2033, CVE-2023-0941, CVE-2022-30192, CVE-2021-21224, CVE-2020-6418, CVE-2024-38082, CVE-2023-21720, CVE-2026-11645, CVE-2022-26912, CVE-2023-2136, CVE-2024-21336, CVE-2023-36008, CVE-2023-28286, CVE-2022-38012, CVE-2022-30127, CVE-2025-49713, CVE-2023-36014, CVE-2025-62223, CVE-2024-4947, CVE-2025-21408, CVE-2026-66317, CVE-2025-21253, CVE-2024-20675, CVE-2024-26246, CVE-2022-33680, CVE-2024-41879, CVE-2024-38209, CVE-2021-30563, CVE-2025-5419, CVE-2025-29834, CVE-2026-66321, CVE-2023-36741, CVE-2022-44688, CVE-2021-30551, CVE-2023-36878, CVE-2024-30058, CVE-2024-43496, CVE-2025-53791, CVE-2024-7971, CVE-2024-26192, CVE-2022-26891, CVE-2026-33119, CVE-2025-29825, CVE-2026-2441, CVE-2023-24935, CVE-2025-47182, CVE-2025-10585, CVE-2025-21267, CVE-2023-36022, CVE-2023-33143, CVE-2026-62904, CVE-2023-21795, CVE-2022-30128, CVE-2022-21970, CVE-2026-40416, CVE-2026-66798, CVE-2026-66325, CVE-2024-21326, CVE-2025-47181, CVE-2026-45495, CVE-2024-7965, CVE-2022-26909, CVE-2026-70341, CVE-2023-29334, CVE-2021-4102, CVE-2024-38083, CVE-2024-0519, CVE-2022-4135, CVE-2021-21148, CVE-2023-6345, CVE-2020-15999, CVE-2021-26439, CVE-2021-43221, CVE-2024-21387, CVE-2021-37973, CVE-2021-30633, CVE-2023-44323, CVE-2024-43595, CVE-2026-58616, CVE-2024-26196, CVE-2023-36562, CVE-2023-36024, CVE-2023-29350, CVE-2025-47967, CVE-2025-21283, CVE-2022-23261, CVE-2026-65802, CVE-2022-26895, CVE-2023-3079, CVE-2025-21262, CVE-2026-66326, CVE-2026-72970, CVE-2026-33118, CVE-2025-47964, CVE-2025-21404, CVE-2023-38173, CVE-2024-49023, CVE-2024-38207, CVE-2023-21775, CVE-2022-26900, CVE-2024-21399, CVE-2025-29795, CVE-2024-38218, CVE-2022-4262, CVE-2021-36931, CVE-2026-66324, CVE-2022-2856, CVE-2020-1195, CVE-2024-21383, CVE-2021-36929, CVE-2021-30632, CVE-2022-21954, CVE-2024-43587, CVE-2023-35392, CVE-2024-38221, CVE-2024-26167, CVE-2025-47963, CVE-2023-38157, CVE-2025-6554, CVE-2024-2883, CVE-2024-20709, CVE-2023-7024, CVE-2022-33638, CVE-2023-28301, CVE-2023-36034, CVE-2024-38219, CVE-2021-38642, CVE-2024-30057, CVE-2026-26133, CVE-2024-43578, CVE-2021-38003, CVE-2023-21794, CVE-2020-1341, CVE-2024-38222, CVE-2022-0609, CVE-2026-65804, CVE-2026-72984, CVE-2022-29146, CVE-2022-23264, CVE-2026-21223, CVE-2025-21401, CVE-2021-37976, CVE-2026-85046, CVE-2021-21220, CVE-2022-41035, CVE-2023-4863, CVE-2023-36026, CVE-2023-36888, CVE-2026-66312, CVE-2025-24201, CVE-2023-23374, CVE-2021-34506, CVE-2022-26899, CVE-2024-4671, CVE-2021-31982, CVE-2026-0385, CVE-2024-49054, CVE-2023-36735, CVE-2023-28284, CVE-2022-1364, CVE-2024-43577, CVE-2024-26188, CVE-2021-36930, CVE-2024-29987, CVE-2026-66310, CVE-2023-38158, CVE-2020-16013, CVE-2025-6558, CVE-2021-21166, CVE-2026-3909, CVE-2024-38156, CVE-2021-38000, CVE-2023-29354, CVE-2026-66318, CVE-2024-30055, CVE-2026-45492, CVE-2022-29147, CVE-2022-29144, CVE-2024-43472, CVE-2022-24523, CVE-2023-28261, CVE-2023-36880, CVE-2024-38103, CVE-2025-21399, CVE-2024-29991, CVE-2022-26908, CVE-2021-34475, CVE-2025-2783, CVE-2024-21385, CVE-2023-21796, CVE-2021-33741, CVE-2022-2294, CVE-2024-20721, CVE-2026-66314, CVE-2024-21423, CVE-2024-29057, CVE-2022-21929, CVE-2023-36029, CVE-2025-13223, CVE-2024-29981, CVE-2022-21931, CVE-2024-43596, CVE-2024-38208, CVE-2026-41107, CVE-2022-21930, CVE-2025-60711, CVE-2023-36787, CVE-2024-29049, CVE-2022-33649, CVE-2025-4664, CVE-2021-21206, CVE-2024-4761, CVE-2025-21342, CVE-2020-16009, CVE-2022-26905, CVE-2025-25000, CVE-2021-43220, CVE-2021-24113, CVE-2026-66322, CVE-2021-21193, CVE-2024-26247, CVE-2024-43579, CVE-2024-43489, CVE-2022-33639, CVE-2025-29796, CVE-2023-36027, CVE-2022-3075, CVE-2022-35796, CVE-2021-26436, CVE-2024-38093, CVE-2024-5274, CVE-2024-39379, CVE-2024-38210, CVE-2021-42308, CVE-2025-21185, CVE-2024-29986, CVE-2021-37975, CVE-2022-22021, CVE-2026-5281, CVE-2026-66323, CVE-2024-49041, CVE-2024-43566, CVE-2023-5217, CVE-2021-38641, CVE-2026-85892, CVE-2022-23262, CVE-2021-36928, CVE-2021-31937, CVE-2024-43580, CVE-2022-33636, CVE-2024-49025, CVE-2023-21719, CVE-2022-44708, CVE-2023-29345, CVE-2023-36887, CVE-2023-38174, CVE-2026-87491, CVE-2022-41115, CVE-2022-1096, CVE-2023-38187, CVE-2022-23258, CVE-2024-26163</t>
+          <t>CVE-2026-50679</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-10-2026</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50679</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2202,31 +2207,36 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ShareFile</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/history.rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
+          <t>"Chromium CVE-2026-76022:Buffer overflow in Network"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CVE-2026-76022</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76022</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2237,36 +2247,36 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
+          <t>"Chromium CVE-2026-76019:Incorrect authorization in Workers"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-0307</t>
+          <t>CVE-2026-76019</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76019</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2277,36 +2287,36 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
+          <t>"Chromium CVE-2026-76039:Incorrect reference resolution in Core"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-0305</t>
+          <t>CVE-2026-76039</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76039</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2317,36 +2327,36 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
+          <t>"Chromium: CVE-2026-84330 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-0306</t>
+          <t>CVE-2026-84330</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84330</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2357,36 +2367,36 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
+          <t>"Chromium CVE-2026-87491:Out of bounds write in V8"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-87491 exists in the wild.""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-0310</t>
+          <t>CVE-2026-87491</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-87491</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2397,36 +2407,36 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
+          <t>"CVE-2026-85892 Microsoft Edge (Chromium-based) Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""Concurrent execution using shared resource with improper synchronization ('race condition') in Microsoft Edge (Chromium-based) allows an authorized attacker to elevate privileges locally.""</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CVE-2026-0304</t>
+          <t>CVE-2026-85892</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85892</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2437,36 +2447,31 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
+          <t>"ESET Customer Advisory: Modules Review, August 2026"</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>""""</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>CVE-2026-0309</t>
+          <t>""</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
+          <t>https://support-feed.eset.com/link/15370/17445349/ca9007</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2477,36 +2482,36 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Stable (Version 153.0.4234.32) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
+          <t>CVE-2023-33145, CVE-2026-3910, CVE-2026-42838, CVE-2024-21337, CVE-2025-21279, CVE-2024-30056, CVE-2021-30554, CVE-2026-66313, CVE-2022-23263, CVE-2023-35618, CVE-2023-36883, CVE-2024-21382, CVE-2022-3723, CVE-2022-24475, CVE-2020-16017, CVE-2026-66316, CVE-2022-26894, CVE-2024-21388, CVE-2025-26643, CVE-2026-45494, CVE-2026-0102, CVE-2021-38669, CVE-2026-66315, CVE-2023-36727, CVE-2026-66311, CVE-2023-36559, CVE-2023-2033, CVE-2023-0941, CVE-2022-30192, CVE-2021-21224, CVE-2020-6418, CVE-2024-38082, CVE-2023-21720, CVE-2026-11645, CVE-2022-26912, CVE-2023-2136, CVE-2024-21336, CVE-2023-36008, CVE-2023-28286, CVE-2022-38012, CVE-2022-30127, CVE-2025-49713, CVE-2023-36014, CVE-2025-62223, CVE-2024-4947, CVE-2025-21408, CVE-2026-66317, CVE-2025-21253, CVE-2024-20675, CVE-2024-26246, CVE-2022-33680, CVE-2024-41879, CVE-2024-38209, CVE-2021-30563, CVE-2025-5419, CVE-2025-29834, CVE-2026-66321, CVE-2023-36741, CVE-2022-44688, CVE-2021-30551, CVE-2023-36878, CVE-2024-30058, CVE-2024-43496, CVE-2025-53791, CVE-2024-7971, CVE-2024-26192, CVE-2022-26891, CVE-2026-33119, CVE-2025-29825, CVE-2026-2441, CVE-2023-24935, CVE-2025-47182, CVE-2025-10585, CVE-2025-21267, CVE-2023-36022, CVE-2023-33143, CVE-2026-62904, CVE-2023-21795, CVE-2022-30128, CVE-2022-21970, CVE-2026-40416, CVE-2026-66798, CVE-2026-66325, CVE-2024-21326, CVE-2025-47181, CVE-2026-45495, CVE-2024-7965, CVE-2022-26909, CVE-2026-70341, CVE-2023-29334, CVE-2021-4102, CVE-2024-38083, CVE-2024-0519, CVE-2022-4135, CVE-2021-21148, CVE-2023-6345, CVE-2020-15999, CVE-2021-26439, CVE-2021-43221, CVE-2024-21387, CVE-2021-37973, CVE-2021-30633, CVE-2023-44323, CVE-2024-43595, CVE-2026-58616, CVE-2024-26196, CVE-2023-36562, CVE-2023-36024, CVE-2023-29350, CVE-2025-47967, CVE-2025-21283, CVE-2022-23261, CVE-2026-65802, CVE-2022-26895, CVE-2023-3079, CVE-2025-21262, CVE-2026-66326, CVE-2026-72970, CVE-2026-33118, CVE-2025-47964, CVE-2025-21404, CVE-2023-38173, CVE-2024-49023, CVE-2024-38207, CVE-2023-21775, CVE-2022-26900, CVE-2024-21399, CVE-2025-29795, CVE-2024-38218, CVE-2022-4262, CVE-2021-36931, CVE-2026-66324, CVE-2022-2856, CVE-2020-1195, CVE-2024-21383, CVE-2021-36929, CVE-2021-30632, CVE-2022-21954, CVE-2024-43587, CVE-2023-35392, CVE-2024-38221, CVE-2024-26167, CVE-2025-47963, CVE-2023-38157, CVE-2025-6554, CVE-2024-2883, CVE-2024-20709, CVE-2023-7024, CVE-2022-33638, CVE-2023-28301, CVE-2023-36034, CVE-2024-38219, CVE-2021-38642, CVE-2024-30057, CVE-2026-26133, CVE-2024-43578, CVE-2021-38003, CVE-2023-21794, CVE-2020-1341, CVE-2024-38222, CVE-2022-0609, CVE-2026-65804, CVE-2026-72984, CVE-2022-29146, CVE-2022-23264, CVE-2026-21223, CVE-2025-21401, CVE-2021-37976, CVE-2026-85046, CVE-2021-21220, CVE-2022-41035, CVE-2023-4863, CVE-2023-36026, CVE-2023-36888, CVE-2026-66312, CVE-2025-24201, CVE-2023-23374, CVE-2021-34506, CVE-2022-26899, CVE-2024-4671, CVE-2021-31982, CVE-2026-0385, CVE-2024-49054, CVE-2023-36735, CVE-2023-28284, CVE-2022-1364, CVE-2024-43577, CVE-2024-26188, CVE-2021-36930, CVE-2024-29987, CVE-2026-66310, CVE-2023-38158, CVE-2020-16013, CVE-2025-6558, CVE-2021-21166, CVE-2026-3909, CVE-2024-38156, CVE-2021-38000, CVE-2023-29354, CVE-2026-66318, CVE-2024-30055, CVE-2026-45492, CVE-2022-29147, CVE-2022-29144, CVE-2024-43472, CVE-2022-24523, CVE-2023-28261, CVE-2023-36880, CVE-2024-38103, CVE-2025-21399, CVE-2024-29991, CVE-2022-26908, CVE-2021-34475, CVE-2025-2783, CVE-2024-21385, CVE-2023-21796, CVE-2021-33741, CVE-2022-2294, CVE-2024-20721, CVE-2026-66314, CVE-2024-21423, CVE-2024-29057, CVE-2022-21929, CVE-2023-36029, CVE-2025-13223, CVE-2024-29981, CVE-2022-21931, CVE-2024-43596, CVE-2024-38208, CVE-2026-41107, CVE-2022-21930, CVE-2025-60711, CVE-2023-36787, CVE-2024-29049, CVE-2022-33649, CVE-2025-4664, CVE-2021-21206, CVE-2024-4761, CVE-2025-21342, CVE-2020-16009, CVE-2022-26905, CVE-2025-25000, CVE-2021-43220, CVE-2021-24113, CVE-2026-66322, CVE-2021-21193, CVE-2024-26247, CVE-2024-43579, CVE-2024-43489, CVE-2022-33639, CVE-2025-29796, CVE-2023-36027, CVE-2022-3075, CVE-2022-35796, CVE-2021-26436, CVE-2024-38093, CVE-2024-5274, CVE-2024-39379, CVE-2024-38210, CVE-2021-42308, CVE-2025-21185, CVE-2024-29986, CVE-2021-37975, CVE-2022-22021, CVE-2026-5281, CVE-2026-66323, CVE-2024-49041, CVE-2024-43566, CVE-2023-5217, CVE-2021-38641, CVE-2026-85892, CVE-2022-23262, CVE-2021-36928, CVE-2021-31937, CVE-2024-43580, CVE-2022-33636, CVE-2024-49025, CVE-2023-21719, CVE-2022-44708, CVE-2023-29345, CVE-2023-36887, CVE-2023-38174, CVE-2026-87491, CVE-2022-41115, CVE-2022-1096, CVE-2023-38187, CVE-2022-23258, CVE-2024-26163</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-10-2026</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2521,32 +2526,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>ShareFile</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://status.sharefile.com/history.rss</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
+          <t>"ShareFile customers may experience delays of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts"</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>CVE-2026-85046</t>
+          <t>""Sep 9 , 15:44 EDT Monitoring - We have identified the issue affecting email delivery and have implemented a fix. We are monitoring the issue. Sep 9 , 14:38 EDT Investigating - We have identified an issue affecting email delivery across ShareFile services. Customers may experience delays or non-delivery of transactional emails, including Password Reset links, New User Welcome emails, and Upload/Download notification alerts.""</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
+          <t>https://status.sharefile.com/incidents/9s6431qlrcsp</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-0307 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CVE-2026-69777</t>
+          <t>CVE-2026-0307</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0307</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2601,32 +2601,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-0305 Prisma Access Agent: Information Disclosure Vulnerability on Linux (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CVE-2026-45499</t>
+          <t>CVE-2026-0305</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0305</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2641,32 +2641,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-0306 Prisma Access Agent: EndPoint DLP Bypass Vulnerability on Windows (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CVE-2026-68877</t>
+          <t>CVE-2026-0306</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0306</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2681,32 +2681,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-0310 PAN-OS: Buffer Overflow Vulnerability via XML Processing(Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CVE-2026-62693</t>
+          <t>CVE-2026-0310</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0310</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2721,32 +2721,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
+          <t>"CVE-2026-0304 Cortex XDR Broker VM: Privilege Escalation Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CVE-2026-69508</t>
+          <t>CVE-2026-0304</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0304</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2761,32 +2761,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-0309 PAN-OS: Authenticated Command Injection in CLI with Luna HSM Configuration (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CVE-2026-69334</t>
+          <t>CVE-2026-0309</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0309</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2801,32 +2801,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
+          <t>"PAN-SA-2026-0012 Chromium: Monthly Vulnerability Update (September 2026) (Severity: HIGH)"</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CVE-2026-69492</t>
+          <t>CVE-2026-7928615, CVE-2026-7929015, CVE-2026-79286, CVE-2026-7604715, CVE-2026-79290, CVE-2026-7603815, CVE-2026-84357, CVE-2026-7928215, CVE-2026-7602215, CVE-2026-8435115, CVE-2026-84351, CVE-2026-76047, CVE-2026-79032, CVE-2026-84359, CVE-2026-84348, CVE-2026-79293, CVE-2026-7919515, CVE-2026-8435015, CVE-2026-8435815, CVE-2026-76038, CVE-2026-8435715, CVE-2026-76046, CVE-2026-8435915, CVE-2026-8434815, CVE-2026-79016, CVE-2026-79195, CVE-2026-7929315, CVE-2026-79118, CVE-2026-84350, CVE-2026-76020, CVE-2026-7903215, CVE-2026-7604615, CVE-2026-76022, CVE-2026-7901615, CVE-2026-79282, CVE-2026-84358, CVE-2026-7911815, CVE-2026-7602015</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
+          <t>https://security.paloaltonetworks.com/PAN-SA-2026-0012</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -2851,22 +2851,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-85046 Type confusion in V8"</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-85046 exists in the wild.""</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CVE-2026-73024</t>
+          <t>CVE-2026-85046</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85046</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -2881,32 +2881,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ESET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/advisories/</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
+          <t>"CVE-2026-69777 Windows DHCP Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CVE-2026-12858</t>
+          <t>CVE-2026-69777</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69777</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2921,37 +2921,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
+          <t>"CVE-2026-45499 Azure OpenAI Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CVE-2026-20079</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>10.0</t>
+          <t>CVE-2026-45499</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-45499</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2966,27 +2961,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
+          <t>"CVE-2026-68877 Windows Storage Spaces Controller Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CVE-2026-68877</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68877</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3001,27 +3001,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>"How can I check the default option values in named.conf?"</t>
+          <t>"CVE-2026-62693 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CVE-2026-62693</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/aa-00704</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62693</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3036,27 +3041,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>"Importing external certificates to Stork"</t>
+          <t>"CVE-2026-69508 Windows MIDI Service Module Elevation of Privileges Vulnerability"</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CVE-2026-69508</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69508</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3071,27 +3081,32 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
+          <t>"CVE-2026-69334 Windows Volume Manager Extension Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CVE-2026-69334</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69334</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3106,27 +3121,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
+          <t>"CVE-2026-69492 Windows Partition Management Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CVE-2026-69492</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69492</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3141,27 +3161,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
+          <t>"CVE-2026-73024 Windows Services for NFS ONCRPC XDR Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CVE-2026-73024</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73024</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3176,27 +3201,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>ESET</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://support-feed.eset.com/advisories/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
+          <t>"ESET Customer Advisory: Local privilege escalation vulnerability in ESET AV Remover fixed"</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CVE-2026-12858</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
+          <t>https://support-feed.eset.com/link/15370/17443273/ca9000</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3207,21 +3237,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>"September Patch Day Security Notes"</t>
+          <t>"Cisco Secure Firewall Management Center Software Authentication Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3231,12 +3261,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
+          <t>CVE-2026-20079</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>10.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-onprem-fmc-authbypass-5JPp45V2</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3247,21 +3282,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mozilla Security Advisories</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
+          <t>"Cisco Advance Notification for Publication of September 16, 2026, Security Advisories"</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3269,14 +3304,9 @@
           <t>""</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>CVE-2026-86853</t>
-        </is>
-      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-notice-jfxK98ZP</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3287,36 +3317,31 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Microsoft Edge Security Updates</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>"Microsoft Edge Security Updates"</t>
+          <t>"How can I check the default option values in named.conf?"</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
+          <t>""There wasn't any command for BIND 9 that would list all named.conf options and their default settings, but checking the defaults can sometimes be helpful in understanding why BIND is doing something that you didn't expect it to, particularly if you've recently upgraded. From versions 9.18.3 (and backported to 9.16.29) a new switch is available for named; -C. Here is a sample of the output it produces: %named -C # Built-in default values. This is NOT the run-time configuration! options { . All c ...""</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
+          <t>https://kb.isc.org/docs/aa-00704</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3327,36 +3352,31 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>BIND</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
+          <t>"Importing external certificates to Stork"</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>CVE-2026-50696</t>
+          <t>""Certificate management The Stork server generates its CA (Certificate Authority) and will use it to then generate its own server certificate and also any certificates needed for agents that will connect to it. This is done automatically and does not require any user intervention. The typical user does not need to interact with the PKI in any way. However, in some environments, the administrator may prefer to generate the certificates externally and import them into Stork. This might be preferabl ...""</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
+          <t>https://kb.isc.org/docs/importing-external-certificates-to-stork</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3367,36 +3387,31 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
+          <t>"HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026."</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>CVE-2026-62697</t>
+          <t>""HPESBNW05126 rev.1 - HPE Networking Advance Notification of Security Advisories for September 15, 2026.""</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05126en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3407,36 +3422,31 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
+          <t>"HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)"</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>CVE-2026-54990</t>
+          <t>""HPESBNW05130 rev.1 - Multiple Vulnerabilities in HPE Aruba Networking ClearPass Policy Manager (CPPM)""</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbnw05130en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3447,36 +3457,31 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
+          <t>"HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability"</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>CVE-2026-44814</t>
+          <t>""HPESBMU05147 rev.1 - HPE IceWall products, Denial of Service vulnerability""</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05147en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3487,36 +3492,31 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
+          <t>"HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions"</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>CVE-2026-69845</t>
+          <t>""HPESBMU05142 rev.1 - HPE IceWall products, Remote Bypass of Security Restrictions""</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbmu05142en_us&amp;docLocale=en_US</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news.html</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
+          <t>"September Patch Day Security Notes"</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CVE-2026-57085</t>
+          <t>CVE-2026-76977, CVE-2026-76959, CVE-2026-76969, CVE-2026-44756, CVE-2026-66767, CVE-2026-58243, CVE-2026-76971, CVE-2026-2332, CVE-2026-58234, CVE-2026-76963, CVE-2026-58240, CVE-2026-76967, CVE-2026-34477, CVE-2026-76960, CVE-2026-76961, CVE-2026-66768, CVE-2026-76962, CVE-2026-76968, CVE-2026-76958, CVE-2026-44766</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
+          <t>https://support.sap.com/en/my-support/knowledge-base/security-notes-news/september-2026.html</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3571,32 +3571,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Mozilla Security Advisories</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
+          <t>"MFSA 2026-89 Security Vulnerabilities fixed in Firefox for iOS 155.1"</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CVE-2026-42914</t>
+          <t>CVE-2026-86853</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
+          <t>https://www.mozilla.org/en-US/security/advisories/mfsa2026-89/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android (Version 152.0.4191.65) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CVE-2026-62747</t>
+          <t>CVE-2024-21382, CVE-2026-70341, CVE-2026-5281, CVE-2024-26163, CVE-2020-15999, CVE-2022-1096, CVE-2023-36727, CVE-2022-26912, CVE-2025-21404, CVE-2022-22021, CVE-2021-30632, CVE-2026-62904, CVE-2024-38209, CVE-2023-21795, CVE-2023-28284, CVE-2024-38222, CVE-2023-29345, CVE-2022-33638, CVE-2024-7971, CVE-2024-38082, CVE-2024-29987, CVE-2026-85046, CVE-2026-33118, CVE-2026-41107, CVE-2025-29825, CVE-2023-24935, CVE-2025-24201, CVE-2021-37976, CVE-2025-29796, CVE-2024-43577, CVE-2024-43496, CVE-2024-38218, CVE-2025-5419, CVE-2025-21399, CVE-2026-72970, CVE-2023-36026, CVE-2023-4863, CVE-2023-2033, CVE-2022-33649, CVE-2023-36022, CVE-2023-35392, CVE-2024-38156, CVE-2025-21408, CVE-2024-26188, CVE-2021-31937, CVE-2026-3909, CVE-2024-26247, CVE-2026-66315, CVE-2023-28301, CVE-2026-3910, CVE-2021-4102, CVE-2024-43578, CVE-2023-28286, CVE-2025-29834, CVE-2025-21283, CVE-2021-30551, CVE-2021-30563, CVE-2024-29049, CVE-2023-6345, CVE-2024-21388, CVE-2025-4664, CVE-2025-53791, CVE-2026-66324, CVE-2025-26643, CVE-2024-38103, CVE-2023-36735, CVE-2026-66313, CVE-2024-21387, CVE-2022-44708, CVE-2022-26900, CVE-2023-36029, CVE-2021-21148, CVE-2025-2783, CVE-2021-36931, CVE-2023-28261, CVE-2025-49713, CVE-2024-4671, CVE-2021-37973, CVE-2026-66311, CVE-2026-66317, CVE-2022-2294, CVE-2023-36878, CVE-2024-30058, CVE-2025-21401, CVE-2022-41035, CVE-2020-6418, CVE-2022-33680, CVE-2026-66314, CVE-2025-47967, CVE-2023-36741, CVE-2026-58616, CVE-2021-30554, CVE-2025-25000, CVE-2022-4262, CVE-2025-21267, CVE-2024-38207, CVE-2022-2856, CVE-2022-26894, CVE-2026-66326, CVE-2021-33741, CVE-2022-41115, CVE-2025-29795, CVE-2026-72984, CVE-2026-65804, CVE-2023-2136, CVE-2020-16009, CVE-2024-29981, CVE-2022-26909, CVE-2022-26899, CVE-2024-38210, CVE-2023-36880, CVE-2022-23264, CVE-2023-21794, CVE-2022-21929, CVE-2024-21385, CVE-2022-29144, CVE-2025-6554, CVE-2022-21931, CVE-2026-33119, CVE-2021-38003, CVE-2023-38157, CVE-2021-43221, CVE-2024-20709, CVE-2022-3075, CVE-2024-20675, CVE-2022-26895, CVE-2022-23258, CVE-2026-66318, CVE-2025-47964, CVE-2025-47963, CVE-2023-36559, CVE-2024-38219, CVE-2022-38012, CVE-2024-38208, CVE-2022-24523, CVE-2023-35618, CVE-2025-21342, CVE-2023-23374, CVE-2024-30057, CVE-2023-3079, CVE-2021-36929, CVE-2022-26891, CVE-2023-29354, CVE-2024-43579, CVE-2021-21220, CVE-2023-36562, CVE-2024-41879, CVE-2021-21193, CVE-2026-0102, CVE-2024-49025, CVE-2026-66323, CVE-2021-24113, CVE-2026-66310, CVE-2023-44323, CVE-2021-38642, CVE-2026-66316, CVE-2023-36787, CVE-2022-23262, CVE-2023-38174, CVE-2022-26908, CVE-2024-26196, CVE-2024-43580, CVE-2024-43566, CVE-2026-66325, CVE-2026-26133, CVE-2024-30055, CVE-2023-38187, CVE-2024-49023, CVE-2025-60711, CVE-2021-30633, CVE-2024-38083, CVE-2023-5217, CVE-2026-42838, CVE-2023-36027, CVE-2024-4947, CVE-2024-43472, CVE-2024-26246, CVE-2024-26192, CVE-2021-38669, CVE-2024-21336, CVE-2024-21337, CVE-2026-66322, CVE-2023-38158, CVE-2025-47181, CVE-2022-23263, CVE-2021-21166, CVE-2024-0519, CVE-2025-10585, CVE-2023-21796, CVE-2022-24475, CVE-2024-20721, CVE-2026-2441, CVE-2024-2883, CVE-2024-26167, CVE-2024-38221, CVE-2022-21930, CVE-2022-3723, CVE-2025-47182, CVE-2020-1195, CVE-2026-45495, CVE-2020-1341, CVE-2025-21185, CVE-2024-29057, CVE-2026-66798, CVE-2024-21423, CVE-2021-34506, CVE-2023-21719, CVE-2021-42308, CVE-2024-49041, CVE-2022-29146, CVE-2024-30056, CVE-2025-13223, CVE-2024-29991, CVE-2023-36034, CVE-2023-33145, CVE-2026-11645, CVE-2022-21970, CVE-2021-26436, CVE-2021-36928, CVE-2022-35796, CVE-2024-43596, CVE-2021-36930, CVE-2026-45492, CVE-2024-7965, CVE-2023-33143, CVE-2023-29350, CVE-2022-30192, CVE-2022-23261, CVE-2021-21206, CVE-2022-33636, CVE-2022-1364, CVE-2022-4135, CVE-2023-0941, CVE-2023-36883, CVE-2024-29986, CVE-2022-26905, CVE-2021-38641, CVE-2024-43587, CVE-2023-7024, CVE-2023-36887, CVE-2022-30128, CVE-2026-21223, CVE-2024-43595, CVE-2022-21954, CVE-2021-31982, CVE-2021-26439, CVE-2024-38093, CVE-2026-45494, CVE-2023-29334, CVE-2025-21262, CVE-2026-0385, CVE-2024-21399, CVE-2026-65802, CVE-2024-39379, CVE-2022-0609, CVE-2025-62223, CVE-2025-21279, CVE-2024-4761, CVE-2024-5274, CVE-2023-36008, CVE-2022-33639, CVE-2021-43220, CVE-2021-21224, CVE-2020-16013, CVE-2024-21326, CVE-2024-21383, CVE-2023-21775, CVE-2025-21253, CVE-2022-30127, CVE-2021-34475, CVE-2021-37975, CVE-2024-49054, CVE-2023-36014, CVE-2023-36888, CVE-2023-36024, CVE-2023-21720, CVE-2022-44688, CVE-2025-6558, CVE-2020-16017, CVE-2026-66312, CVE-2024-43489, CVE-2026-40416, CVE-2023-38173, CVE-2026-66321, CVE-2022-29147, CVE-2021-38000</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-8-2026</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -3661,22 +3661,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
+          <t>"CVE-2026-50696 Internet Key Exchange (IKE) Protocol Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CVE-2026-50453</t>
+          <t>CVE-2026-50696</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50696</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3701,22 +3701,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
+          <t>"CVE-2026-62697 Windows Push Notifications Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CVE-2026-84325</t>
+          <t>CVE-2026-62697</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62697</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3741,22 +3741,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
+          <t>"CVE-2026-54990 Remote Desktop Client Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CVE-2026-84326</t>
+          <t>CVE-2026-54990</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54990</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
+          <t>"CVE-2026-44814 Windows DWM Core Library Information DisclosureVulnerability"</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CVE-2026-84329</t>
+          <t>CVE-2026-44814</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-44814</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3821,22 +3821,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
+          <t>"CVE-2026-69845 Windows DHCP Server Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CVE-2026-84324</t>
+          <t>CVE-2026-69845</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69845</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3861,22 +3861,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
+          <t>"CVE-2026-57085 Windows Print Spooler Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CVE-2026-84357</t>
+          <t>CVE-2026-57085</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-57085</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3901,22 +3901,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
+          <t>"CVE-2026-42914 Windows Kerberos Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CVE-2026-84354</t>
+          <t>CVE-2026-42914</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-42914</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3941,22 +3941,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
+          <t>"CVE-2026-62747 Windows Device Association Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CVE-2026-84353</t>
+          <t>CVE-2026-62747</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62747</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -3981,22 +3981,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
+          <t>"CVE-2026-50453 Windows USB Audio Class Driver Information Disclosure Vulnerability"</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CVE-2026-84350</t>
+          <t>CVE-2026-50453</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50453</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
+          <t>"Chromium: CVE-2026-84325 Improper input validation in DataTransfer"</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CVE-2026-84348</t>
+          <t>CVE-2026-84325</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84325</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
+          <t>"Chromium: CVE-2026-84326 Uninitialized resource in V8"</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CVE-2026-84331</t>
+          <t>CVE-2026-84326</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84326</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
+          <t>"Chromium: CVE-2026-84329 Confused deputy in CredentialProvider"</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CVE-2026-84351</t>
+          <t>CVE-2026-84329</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84329</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
+          <t>"Chromium: CVE-2026-84324 Use after free in Proxy"</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CVE-2026-84335</t>
+          <t>CVE-2026-84324</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84324</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
+          <t>"Chromium: CVE-2026-84357 Improper input validation in Omnibox"</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CVE-2026-84334</t>
+          <t>CVE-2026-84357</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84357</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84354 Incorrect authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CVE-2026-84323</t>
+          <t>CVE-2026-84354</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84354</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
+          <t>"Chromium: CVE-2026-84353 Use after free in Shared Tab Groups"</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CVE-2026-84358</t>
+          <t>CVE-2026-84353</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84353</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
+          <t>"Chromium: CVE-2026-84350 Use after free in TabStrip"</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CVE-2026-84355</t>
+          <t>CVE-2026-84350</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84350</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
+          <t>"Chromium: CVE-2026-84348 Information leak in MediaCapture"</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CVE-2026-84347</t>
+          <t>CVE-2026-84348</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84348</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
+          <t>"Chromium: CVE-2026-84331 Incorrect authorization in Actor"</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CVE-2026-84356</t>
+          <t>CVE-2026-84331</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84331</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
+          <t>"Chromium: CVE-2026-84351 Buffer overflow in GPU"</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CVE-2026-84332</t>
+          <t>CVE-2026-84351</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84351</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
+          <t>"Chromium: CVE-2026-84335 Incorrect authorization in TabStrip"</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4471,12 +4471,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CVE-2026-84359</t>
+          <t>CVE-2026-84335</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84335</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
+          <t>"Chromium: CVE-2026-84334 Incorrect authorization in Chromoting"</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CVE-2026-84327</t>
+          <t>CVE-2026-84334</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84334</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
+          <t>"Chromium: CVE-2026-84323 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CVE-2026-84349</t>
+          <t>CVE-2026-84323</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84323</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
+          <t>"Chromium: CVE-2026-84358 Improper privilege management in Downloads"</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4591,12 +4591,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CVE-2026-84328</t>
+          <t>CVE-2026-84358</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84358</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4611,27 +4611,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ivanti</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>"September 2026 Security Update"</t>
+          <t>"Chromium: CVE-2026-84355 Incorrect authorization in Navigation"</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CVE-2026-84355</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84355</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4646,32 +4651,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Google Chrome Releases</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>"Stable Channel Update for Desktop"</t>
+          <t>"Chromium: CVE-2026-84347 Use after free in WebRTC"</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
+          <t>CVE-2026-84347</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84347</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -4686,27 +4691,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>"ZTNA Portal Improper Certificate Validation"</t>
+          <t>"Chromium: CVE-2026-84356 UI misrepresentation in FullScreen"</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>CVE-2026-84356</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84356</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -4721,27 +4731,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>"JWT used for authentication in web GUI signed with static key"</t>
+          <t>"Chromium: CVE-2026-84332 Incorrect authorization in SiteSettings"</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>CVE-2026-84332</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84332</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -4756,27 +4771,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>"Workflow session email approval process bypass"</t>
+          <t>"Chromium: CVE-2026-84359 Information leak in Skia"</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>CVE-2026-84359</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84359</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -4791,27 +4811,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
+          <t>"Chromium: CVE-2026-84327 Incorrect authorization in Autofill"</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>CVE-2026-84327</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84327</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -4826,27 +4851,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>"Uncontrolled Resource Consumption in SNMP"</t>
+          <t>"Chromium: CVE-2026-84349 Use after free in Browser"</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>CVE-2026-84349</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84349</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -4861,27 +4891,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>"Cron Job Injection in Remote Backup"</t>
+          <t>"Chromium: CVE-2026-84328 Missing authorization in FileSystem"</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CVE-2026-84328</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84328</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -4896,27 +4931,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Ivanti</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://www.ivanti.com/blog/topics/security-advisory/rss</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>"Null Pointer Dereference in Log Report"</t>
+          <t>"September 2026 Security Update"</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
+          <t>""Ivanti releases standard security patches on the second Tuesday of every month. In today’s rapidly evolving technology and threat landscape, we believe responsible transparency should be a cornerstone of any product security program. AI is compressing the time-to-exploit , and Ivanti uses leading technologies to proactively find and fix issues––including integrating advanced LLMs into our Engineering and product security to enhance the capabilities of our teams and identify vulnerabilities that traditional tools have previously missed. Our philosophy is simple: discovering and communicating vulnerabilities and sharing that information with defenders is not an indication of weakness; rather it is evidence of rigorous scrutiny and a proactive vulnerability management program. By aggressively seeking to identify and address vulnerabilities, our aim is to get ahead of threat actors to ensure our customers can take the steps needed to protect their environments. To that end, today Ivanti is disclosing vulnerabilities in Ivanti Neurons for ITSM, Endpoint Manager Mobile (EPMM), and Sentry. It is important for customers to know: We have no evidence of these vulnerabilities being exploited in the wild. These vulnerabilities do not impact any other Ivanti solutions. More information on these vulnerabilities and detailed instructions on how to remediate the issues can be found in the Security Advisories: Ivanti Neurons for ITSM Ivanti Endpoint Manager Mobile (EPMM) Ivanti Sentry How we are using AI in product security Ivanti continues to explore, test, and implement leading technologies and processes in every stage of our product development. Our security team has integrated multiple advanced LLM models into our product security processes. This has increased the capabilities of our Engineering and Product Security Red Teams to identify and fix vulnerabilities, especially those that are difficult to identify with traditional tooling, such as SAST and DAST. We have already successfully identified vulnerabilities which traditional tools missed, including some that we are disclosing today. As these tools are integrated further into our processes and refined, we expect an increase in vulnerability disclosures. We will continue to share transparently what we have found and resolved to ensure the security of our products. If you are not already following our Security Blog or subscribed to receive alerts for updates on the products you own through the Ivanti Innovators Hub, we highly recommend you do so. Importantly, we are committed to using AI responsibly in product security, including keeping a human in the loop to verify automated or agentic work. While this will result in an uptick in disclosures, we see this as a good thing, and an important part of ensuring our products keep pace with modern security requirements as they change. Our top priority is the security of our customers and believe the increase in identified, resolved, and transparently communicated vulnerabilities demonstrates that commitment. Our Support team is always available to help customers and partners should they have any questions. Cases can be logged via the Ivanti Innovators Hub (login credentials required). Want to stay up to date on Ivanti Security Advisories? Paste https://www.ivanti.com/blog/topics/security-advisory/rss into your preferred RSS reader / functionality in your email program.""</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
+          <t>https://www.ivanti.com/blog/september-2026-security-update</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -4931,27 +4966,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FORTINET</t>
+          <t>Google Chrome Releases</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+          <t>https://chromereleases.googleblog.com/search/label/Stable%20updates</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>"Broken Access control on Websocket streams"</t>
+          <t>"Stable Channel Update for Desktop"</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>CVE-2026-87464, CVE-2026-87634, CVE-2026-87471, CVE-2026-87612, CVE-2026-87507, CVE-2026-87573, CVE-2026-87610, CVE-2026-87652, CVE-2026-87432, CVE-2026-87562, CVE-2026-87434, CVE-2026-87636, CVE-2026-87632, CVE-2026-87591, CVE-2026-87626, CVE-2026-87536, CVE-2026-87587, CVE-2026-87553, CVE-2026-87515, CVE-2026-87457, CVE-2026-87629, CVE-2026-87654, CVE-2026-87501, CVE-2026-87458, CVE-2026-87473, CVE-2026-87579, CVE-2026-87435, CVE-2026-87603, CVE-2026-87592, CVE-2026-87444, CVE-2026-87561, CVE-2026-87448, CVE-2026-87631, CVE-2026-87611, CVE-2026-87540, CVE-2026-87615, CVE-2026-87550, CVE-2026-87648, CVE-2026-87509, CVE-2026-87477, CVE-2026-87651, CVE-2026-87431, CVE-2026-87482, CVE-2026-87549, CVE-2026-87523, CVE-2026-87539, CVE-2026-87568, CVE-2026-87442, CVE-2026-87656, CVE-2026-87460, CVE-2026-87658, CVE-2026-87577, CVE-2026-87588, CVE-2026-87487, CVE-2026-87635, CVE-2026-87571, CVE-2026-87616, CVE-2026-87440, CVE-2026-87456, CVE-2026-87505, CVE-2026-87430, CVE-2026-87528, CVE-2026-87546, CVE-2026-87583, CVE-2026-87506, CVE-2026-87566, CVE-2026-87560, CVE-2026-87639, CVE-2026-87646, CVE-2026-87447, CVE-2026-87499, CVE-2026-87497, CVE-2026-87485, CVE-2026-87498, CVE-2026-87624, CVE-2026-87484, CVE-2026-87584, CVE-2026-87595, CVE-2026-87605, CVE-2026-87450, CVE-2026-87504, CVE-2026-87559, CVE-2026-87459, CVE-2026-87538, CVE-2026-87445, CVE-2026-87617, CVE-2026-87476, CVE-2026-87530, CVE-2026-87545, CVE-2026-87534, CVE-2026-87582, CVE-2026-87513, CVE-2026-87628, CVE-2026-87599, CVE-2026-87608, CVE-2026-87614, CVE-2026-87500, CVE-2026-87594, CVE-2026-87438, CVE-2026-87541, CVE-2026-87552, CVE-2026-87478, CVE-2026-87517, CVE-2026-87508, CVE-2026-87535, CVE-2026-87581, CVE-2026-87503, CVE-2026-87653, CVE-2026-87461, CVE-2026-87585, CVE-2026-87618, CVE-2026-87512, CVE-2026-87436, CVE-2026-87479, CVE-2026-87567, CVE-2026-87494, CVE-2026-87522, CVE-2026-87491, CVE-2026-87467, CVE-2026-87527, CVE-2026-87619, CVE-2026-87511, CVE-2026-87601, CVE-2026-87564, CVE-2026-87589, CVE-2026-87623, CVE-2026-87490, CVE-2026-87606, CVE-2026-87557, CVE-2026-87647, CVE-2026-87649, CVE-2026-87569, CVE-2026-87469, CVE-2026-87475, CVE-2026-87600, CVE-2026-87514, CVE-2026-87451, CVE-2026-87453, CVE-2026-87443, CVE-2026-87598, CVE-2026-87637, CVE-2026-87526, CVE-2026-87486, CVE-2026-87519, CVE-2026-87650, CVE-2026-87613, CVE-2026-87544, CVE-2026-87483, CVE-2026-87609, CVE-2026-87620, CVE-2026-87474, CVE-2026-87518, CVE-2026-87630, CVE-2026-87510, CVE-2026-87565, CVE-2026-87446, CVE-2026-87493, CVE-2026-87492, CVE-2026-87433, CVE-2026-87531, CVE-2026-87525, CVE-2026-87521, CVE-2026-87576, CVE-2026-87437, CVE-2026-87570, CVE-2026-87645, CVE-2026-87554, CVE-2026-87657, CVE-2026-87558, CVE-2026-87439, CVE-2026-87454, CVE-2026-87638, CVE-2026-87516, CVE-2026-87533, CVE-2026-87642, CVE-2026-87496, CVE-2026-87622, CVE-2026-87495, CVE-2026-87465, CVE-2026-87532, CVE-2026-87641, CVE-2026-87470, CVE-2026-87524, CVE-2026-87627, CVE-2026-87488, CVE-2026-87593, CVE-2026-87607, CVE-2026-87575, CVE-2026-87602, CVE-2026-87580, CVE-2026-87586, CVE-2026-87449, CVE-2026-87542, CVE-2026-87462, CVE-2026-87543, CVE-2026-87441, CVE-2026-87563, CVE-2026-87597, CVE-2026-87644, CVE-2026-87481, CVE-2026-87537, CVE-2026-87455, CVE-2026-87572, CVE-2026-87529, CVE-2026-87621, CVE-2026-87547, CVE-2026-87556, CVE-2026-87578, CVE-2026-87551, CVE-2026-87480, CVE-2026-87596, CVE-2026-87655, CVE-2026-87468, CVE-2026-87625, CVE-2026-87489, CVE-2026-87604, CVE-2026-87590, CVE-2026-87472, CVE-2026-87502, CVE-2026-87633, CVE-2026-87452, CVE-2026-87574, CVE-2026-87643, CVE-2026-87463, CVE-2026-87555, CVE-2026-87640, CVE-2026-87520, CVE-2026-87548, CVE-2026-87429, CVE-2026-87466</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
+          <t>https://chromereleases.googleblog.com/2026/09/stable-channel-update-for-desktop_0808145027.html</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -4976,17 +5016,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
+          <t>"ZTNA Portal Improper Certificate Validation"</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 7.3 An improper certificate validation vulnerability [CWE-295] in FortiOS and FortiProxy Agentless ZTNA portal may allow a remote and unauthenticated attacker to perform a Man-in-the-Middle attack on the communication channel between the ZTNA portal and the backend destination website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-174</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5011,17 +5051,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>"Improper Authentication of FortiPAM Server"</t>
+          <t>"JWT used for authentication in web GUI signed with static key"</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 9.6 An Inclusion of Sensitive Information in Source Code vulnerability [CWE-540] in FortiMonitorOnSight web portal may allow a remote unauthenticated attacker to bypass authentication via forged or reused JWT Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-170</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5046,17 +5086,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>"Open Redirect on FortiSIEM"</t>
+          <t>"Workflow session email approval process bypass"</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+          <t>""CVSSv3 Score: 4.7 An improper access control vulnerability [CWE-284] in FortiManager may allow an administrator to bypass the approval process for workflow sessions via crafted HTTP or HTTPs requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-171</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5071,37 +5111,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+          <t>"Unauthenticated Control of NAT Rules Leading to Exposure of Sensitive Information"</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>CVE-2026-20293</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>7.1</t>
+          <t>""CVSSv3 Score: 8.9 An improper access control vulnerability [CWE-284] in FortiSandbox, FortiSandbox Cloud and FortiSandbox PaaS WEB UI may allow an unauthenticated attacker to access sensitive information via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-166</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5116,37 +5146,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+          <t>"Uncontrolled Resource Consumption in SNMP"</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>9.8</t>
+          <t>""CVSSv3 Score: 5.9 A Use of Uninitialized Variable [CWE-457] vulnerability in Fortinet FortiAnalyzer SNMP daemon may allow a remote authenticated attacker with user permission to cause a denial of service via SNMP GETBULK requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-172</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5161,37 +5181,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+          <t>"Cron Job Injection in Remote Backup"</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>CVE-2026-20354, CVE-2026-20355</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>5.9</t>
+          <t>""CVSSv3 Score: 6.7 An Improper Neutralization of Special Elements used in a Command ('Command Injection') vulnerability [CWE-77] in FortiSandbox may allow a privileged attacker to execute unauthorized code or commands via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-167</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5206,27 +5216,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>BIND</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/v1/rss/en</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+          <t>"Null Pointer Dereference in Log Report"</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+          <t>""CVSSv3 Score: 2.5 A NULL Pointer Dereference vulnerability [CWE-476] in FortiOS, FortiProxy and FortiPAM may allow an authenticated attacker to crash the httpsd daemon via crafted HTTP requests. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-173</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5241,27 +5251,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+          <t>"Broken Access control on Websocket streams"</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+          <t>""CVSSv3 Score: 4.9 An Improper Access control vulnerability [CWE-284] in FortiSOAR may allow an authenticated attacker with zero permissions to subscribe to websocket streams and topics and to inject broadcast messages to the stream via crafted websocket requests Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-164</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5276,32 +5286,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Android OS</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>"September 2026"</t>
+          <t>"Arbitrary process termination from exposed minifilter communication port"</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+          <t>""CVSSv3 Score: 4.7 An Unverified Ownership Vulnerability [CWE-283] in FortiClient Windows fortimon3 driver may allow an authenticated attacker to terminate arbitrary processes via an exposed minifilter communication port. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-165</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5316,37 +5321,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Adobe Acrobat and Reader</t>
+          <t>FORTINET</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+          <t>"Improper Authentication of FortiPAM Server"</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>""</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>8.8</t>
+          <t>""CVSSv3 Score: 9.1 An improper authentication vulnerability [CWE-287] in the Fortinet Privileged Access Agent Chrome Extension may allow a remote unauthenticated attacker to proxy a user's browser traffic through attacker controlled servers if the user visits a malicious website. Revised on 2026-09-08 00:00:00""</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-168</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5357,34 +5352,324 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>FORTINET</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://filestore.fortinet.com/fortiguard/rss/ir.xml</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>"Open Redirect on FortiSIEM"</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>""CVSSv3 Score: 2.8 An URL redirection to untrusted site ('open redirect') [CWE-601] vulnerability in FortiSIEM may allow an authenticated attacker to cause a redirection to any website via specially crafted HTTP requests Revised on 2026-09-08 00:00:00""</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://fortiguard.fortinet.com/psirt/FG-IR-26-169</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>"Cisco UCS and UCS-Based Appliances UEFI Shell Secure Boot Bypass Vulnerability"</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>CVE-2026-20293</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-ucs-uefi-sb-bypass-eb6xC5GW</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>"Cisco IOS XR Software Security Hardening Release: September 2026"</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>CVE-2026-20279, CVE-2026-20280, CVE-2026-20275, CVE-2026-20276, CVE-2026-20277, CVE-2026-20274, CVE-2026-20278</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-iosxr-qg64NcM</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>"Cisco Secure Email Secure/Multipurpose Internet Mail Extensions Ciphertext Decryption Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>CVE-2026-20354, CVE-2026-20355</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-smime-disc-dzw4rEdY</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>BIND</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>https://kb.isc.org/v1/rss/en</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>"DNSSEC Key and Signing Policy"</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>""BIND 9.16 introduced a new method to maintain DNSSEC on your zones. In addition to the inline-signing and auto-dnssec configuration options, there is now dnssec-policy (also see the configuration reference in the ARM). dnssec-policy replaces auto-dnssec auto-dnssec has been removed since the 9.19.16 development release in favour of the newer, more flexible dnssec-policy. With dnssec-policy, you can specify a Key And Signing Policy (KASP) and group all KASP-related configurations together, maki ...""</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>https://kb.isc.org/docs/dnssec-key-and-signing-policy</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>"Standard DHCP Options Defined in ISC DHCP and Kea"</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>""These tables show the standard options currrently defined for both DHCPv4 and DHCPv6 and which ones are supported in the ISC DHCP server and Kea DHCP servers. They may be helpful in planning migration from one server to the other. If there is any doubt, the Kea User Guide includes two tables: supported standard options for DHCPv4 and DHCPv6. The tables below are meant to be a super-set of those. DHCPv4 Options - updated 2024-01-26 code Name Reference DHCP Kea 0 Pad RFC 2132 Yes Yes 1 Subnet M ...""</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://kb.isc.org/docs/standard-dhcp-options</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/api/document/sec_bull_rss_feed</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>"HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities"</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>""HPESBHF05102 rev.1 - HPE ProLiant DL/ML, Alletra, MicroServer, Edgeline and Synergy Server Using Certain Intel Processors, INTEL-SA-01427, Intel Chipset Firmware Advisory, Multiple Vulnerabilities""</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://support.hpe.com/hpesc/public/docDisplay?docId=hpesbhf05102en_us&amp;docLocale=en_US</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Android OS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>https://source.android.com/docs/security/bulletin/asb-overview</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>"September 2026"</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>CVE-2026-41157, CVE-2026-28600, CVE-2026-28599, CVE-2026-34196, CVE-2026-20502, CVE-2026-28631, CVE-2026-20460, CVE-2026-55290, CVE-2026-28609, CVE-2026-28590, CVE-2026-4967, CVE-2026-49913, CVE-2026-28627, CVE-2026-7477, CVE-2026-0084, CVE-2026-28617, CVE-2026-34193, CVE-2026-28620, CVE-2026-34195, CVE-2026-20459, CVE-2026-24092, CVE-2026-25289, CVE-2026-28604, CVE-2026-7476, CVE-2026-28668, CVE-2026-45531, CVE-2026-28624, CVE-2026-28638, CVE-2026-28636, CVE-2026-28583, CVE-2026-34194, CVE-2026-45200, CVE-2026-28655, CVE-2026-41158, CVE-2026-20467, CVE-2026-49879, CVE-2026-49887, CVE-2026-12387, CVE-2026-21551, CVE-2026-21553, CVE-2026-28630, CVE-2026-24084, CVE-2026-31629, CVE-2026-0008, CVE-2026-7639, CVE-2026-28656, CVE-2026-25260, CVE-2026-28662, CVE-2026-28657, CVE-2026-21550, CVE-2026-20504, CVE-2026-28584, CVE-2026-28652, CVE-2026-49743, CVE-2026-20477, CVE-2026-28642, CVE-2026-25288, CVE-2026-49881, CVE-2025-48566, CVE-2026-58848, CVE-2026-28663, CVE-2026-0010, CVE-2026-58839, CVE-2025-48564, CVE-2026-55285, CVE-2026-28660, CVE-2026-49884, CVE-2026-28634, CVE-2025-48651, CVE-2026-0065, CVE-2026-45521, CVE-2026-20503, CVE-2026-43049, CVE-2026-28596, CVE-2026-25275, CVE-2026-45519, CVE-2026-49746, CVE-2026-41156, CVE-2026-21383, CVE-2026-28572, CVE-2026-49918, CVE-2026-28593, CVE-2026-20501, CVE-2026-28658, CVE-2026-58874, CVE-2026-21548, CVE-2026-45525, CVE-2026-28644, CVE-2026-28603, CVE-2026-20469, CVE-2026-24080, CVE-2026-55273, CVE-2026-49927, CVE-2026-28606, CVE-2025-48565, CVE-2026-0054, CVE-2026-28594, CVE-2026-45527, CVE-2026-45197, CVE-2026-55277, CVE-2026-27280, CVE-2026-49882, CVE-2026-25294, CVE-2026-28581, CVE-2026-58822, CVE-2026-21733, CVE-2026-45202, CVE-2026-21552, CVE-2026-49921, CVE-2026-52993, CVE-2026-25259, CVE-2026-20500, CVE-2026-28664, CVE-2026-28618, CVE-2026-20475, CVE-2026-45518, CVE-2026-21734, CVE-2026-28614, CVE-2026-28582, CVE-2026-20461, CVE-2026-28602, CVE-2026-20474, CVE-2026-58941, CVE-2026-28650, CVE-2026-45528, CVE-2026-20481, CVE-2026-58823, CVE-2026-28633, CVE-2026-49919, CVE-2026-28623, CVE-2026-49895, CVE-2026-22166, CVE-2026-24079, CVE-2026-45520, CVE-2026-28626, CVE-2026-28653, CVE-2026-28607, CVE-2026-28616, CVE-2026-45203, CVE-2026-20464, CVE-2026-0001, CVE-2026-12285, CVE-2026-28622, CVE-2026-55294, CVE-2026-58820, CVE-2026-24091, CVE-2026-45529, CVE-2026-28639, CVE-2026-28666, CVE-2026-34192, CVE-2026-28671, CVE-2026-20479, CVE-2026-45517, CVE-2026-21549, CVE-2026-49926, CVE-2026-28612, CVE-2026-20468, CVE-2026-45515, CVE-2026-5729, CVE-2026-21732, CVE-2026-24087, CVE-2026-24081, CVE-2026-20497, CVE-2026-28613, CVE-2026-45196, CVE-2026-49932, CVE-2026-24088, CVE-2026-22164, CVE-2026-58846, CVE-2026-20457, CVE-2026-20473, CVE-2026-45198, CVE-2026-24090, CVE-2026-33636, CVE-2026-45195, CVE-2026-20458, CVE-2026-49745, CVE-2026-49744, CVE-2026-55256, CVE-2026-28611</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://source.android.com/docs/security/bulletin/2026/2026-09-01</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>未投稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat and Reader</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://helpx.adobe.com/security/security-bulletin.html#acrobat</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>"APSB26-141 : Security update available for Adobe Acrobat and Reader"</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>CVE-2026-81979, CVE-2026-81987, CVE-2026-81980, CVE-2026-81994, CVE-2026-81981, CVE-2026-47965, CVE-2026-81992, CVE-2026-80160, CVE-2026-47952, CVE-2026-79910, CVE-2026-79908, CVE-2026-81991, CVE-2026-82001, CVE-2026-81989, CVE-2026-81984, CVE-2026-80162, CVE-2026-81985, CVE-2026-81988, CVE-2026-81986, CVE-2026-81993, CVE-2026-81978, CVE-2026-81983, CVE-2026-81982, CVE-2026-80161, CVE-2026-79909, CVE-2026-81975, CVE-2026-81990, CVE-2026-81997, CVE-2026-81977, CVE-2026-80159, CVE-2026-79907, CVE-2026-81996, CVE-2026-81973, CVE-2026-81976, CVE-2026-48373</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://helpx.adobe.com/security/products/acrobat/apsb26-141.html</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
         <is>
           <t>未投稿</t>
         </is>

--- a/FilterVulnerability.xlsx
+++ b/FilterVulnerability.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I133" headerRowCount="1">
-  <autoFilter ref="A1:I133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Vulnerability" displayName="Vulnerability" ref="A1:I141" headerRowCount="1">
+  <autoFilter ref="A1:I141"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Site"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,36 +487,36 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Microsoft Edge Security Updates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"CVE-2026-0295 GlobalProtect App: Local Privilege Escalation via Race Condition on macOS (Severity: MEDIUM)"</t>
+          <t>"Microsoft Edge Security Updates"</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>"Microsoft released the latest Microsoft Edge for Android and iOS (Version 153.0.4234.32) which incorporates the latest Security Updates of the Chromium project. For more information, see the Security Update Guide."</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CVE-2026-0295</t>
+          <t>CVE-2023-6345, CVE-2024-7971, CVE-2024-29057, CVE-2026-66324, CVE-2026-58616, CVE-2021-30551, CVE-2022-26899, CVE-2021-36931, CVE-2023-36027, CVE-2022-26894, CVE-2024-29981, CVE-2024-21387, CVE-2025-29825, CVE-2025-10585, CVE-2024-43580, CVE-2024-29049, CVE-2023-38173, CVE-2026-66310, CVE-2026-45494, CVE-2023-21719, CVE-2024-38103, CVE-2024-21383, CVE-2024-21337, CVE-2022-33680, CVE-2023-21794, CVE-2021-30563, CVE-2021-43220, CVE-2021-38003, CVE-2026-66322, CVE-2025-47963, CVE-2022-0609, CVE-2024-30055, CVE-2024-38082, CVE-2024-21336, CVE-2023-36029, CVE-2022-29144, CVE-2025-21283, CVE-2024-21385, CVE-2022-33649, CVE-2021-21220, CVE-2020-1341, CVE-2023-0941, CVE-2024-38093, CVE-2025-47964, CVE-2024-26188, CVE-2023-36878, CVE-2022-1364, CVE-2026-65802, CVE-2022-21931, CVE-2025-6558, CVE-2021-37975, CVE-2026-2441, CVE-2021-21166, CVE-2021-31937, CVE-2025-47181, CVE-2021-30554, CVE-2020-16013, CVE-2023-35618, CVE-2025-21267, CVE-2023-24935, CVE-2021-37976, CVE-2024-20675, CVE-2022-2294, CVE-2022-33639, CVE-2022-26891, CVE-2021-21224, CVE-2021-24113, CVE-2024-26192, CVE-2024-38156, CVE-2022-29146, CVE-2022-3075, CVE-2026-21223, CVE-2026-66318, CVE-2024-38210, CVE-2024-2883, CVE-2021-42308, CVE-2026-33119, CVE-2023-36562, CVE-2024-26163, CVE-2022-3723, CVE-2022-2856, CVE-2022-26908, CVE-2020-1195, CVE-2022-24475, CVE-2022-41035, CVE-2026-66313, CVE-2026-0102, CVE-2024-30058, CVE-2022-44688, CVE-2022-21929, CVE-2023-36883, CVE-2023-38157, CVE-2025-47182, CVE-2022-33638, CVE-2022-30192, CVE-2025-21404, CVE-2025-62223, CVE-2023-36887, CVE-2024-49041, CVE-2025-13223, CVE-2024-30057, CVE-2023-29350, CVE-2022-23264, CVE-2024-4671, CVE-2025-25000, CVE-2024-43579, CVE-2026-85046, CVE-2021-30633, CVE-2021-33741, CVE-2026-45492, CVE-2022-23261, CVE-2026-40416, CVE-2021-34506, CVE-2026-45495, CVE-2023-4863, CVE-2026-87491, CVE-2024-26196, CVE-2021-38642, CVE-2026-66317, CVE-2026-5281, CVE-2023-33143, CVE-2022-26909, CVE-2021-21206, CVE-2023-38158, CVE-2024-39379, CVE-2021-38669, CVE-2025-29834, CVE-2024-29991, CVE-2023-36559, CVE-2023-36888, CVE-2024-21326, CVE-2026-42838, CVE-2023-35392, CVE-2024-4761, CVE-2023-28301, CVE-2021-36930, CVE-2026-26133, CVE-2022-23263, CVE-2025-21342, CVE-2024-7965, CVE-2025-5419, CVE-2023-3079, CVE-2023-36741, CVE-2024-20709, CVE-2023-28286, CVE-2023-38174, CVE-2022-30127, CVE-2023-5217, CVE-2020-6418, CVE-2021-34475, CVE-2026-72984, CVE-2021-26436, CVE-2023-23374, CVE-2025-21399, CVE-2021-36928, CVE-2022-21954, CVE-2021-43221, CVE-2025-24201, CVE-2024-38222, CVE-2022-35796, CVE-2025-29795, CVE-2025-21279, CVE-2026-66311, CVE-2025-21253, CVE-2022-4262, CVE-2024-26246, CVE-2025-49713, CVE-2023-36014, CVE-2024-43577, CVE-2023-2033, CVE-2021-4102, CVE-2026-41107, CVE-2024-21423, CVE-2023-36026, CVE-2022-21970, CVE-2026-70341, CVE-2022-26912, CVE-2023-36008, CVE-2020-16017, CVE-2025-21408, CVE-2026-65804, CVE-2026-11645, CVE-2026-3910, CVE-2025-21185, CVE-2023-36787, CVE-2022-1096, CVE-2021-30632, CVE-2025-2783, CVE-2024-49025, CVE-2024-43595, CVE-2023-36735, CVE-2023-21795, CVE-2021-36929, CVE-2022-26895, CVE-2026-62904, CVE-2022-29147, CVE-2024-0519, CVE-2021-37973, CVE-2024-49054, CVE-2026-33118, CVE-2023-7024, CVE-2023-21775, CVE-2022-22021, CVE-2024-43578, CVE-2024-38221, CVE-2022-23262, CVE-2024-49023, CVE-2022-44708, CVE-2022-26900, CVE-2026-66326, CVE-2026-0385, CVE-2023-36024, CVE-2021-21193, CVE-2026-3909, CVE-2024-20721, CVE-2025-60711, CVE-2025-6554, CVE-2021-31982, CVE-2026-66321, CVE-2022-33636, CVE-2024-29986, CVE-2026-66798, CVE-2025-53791, CVE-2022-24523, CVE-2024-43489, CVE-2022-30128, CVE-2024-21388, CVE-2023-38187, CVE-2024-21382, CVE-2022-21930, CVE-2021-38000, CVE-2021-38641, CVE-2021-21148, CVE-2024-26167, CVE-2023-28284, CVE-2022-26905, CVE-2025-21401, CVE-2023-2136, CVE-2023-36727, CVE-2023-29354, CVE-2023-36880, CVE-2023-29334, CVE-2023-36022, CVE-2024-43596, CVE-2024-4947, CVE-2024-43566, CVE-2022-38012, CVE-2025-29796, CVE-2026-66314, CVE-2021-26439, CVE-2023-36034, CVE-2024-38207, CVE-2024-43496, CVE-2025-47967, CVE-2023-21720, CVE-2024-21399, CVE-2024-26247, CVE-2024-41879, CVE-2025-21262, CVE-2024-43472, CVE-2024-38218, CVE-2025-26643, CVE-2024-38083, CVE-2026-85892, CVE-2026-66316, CVE-2022-41115, CVE-2022-23258, CVE-2024-38219, CVE-2023-29345, CVE-2026-66315, CVE-2020-16009, CVE-2026-66312, CVE-2023-44323, CVE-2025-4664, CVE-2024-30056, CVE-2023-33145, CVE-2020-15999, CVE-2026-66325, CVE-2026-66323, CVE-2024-43587, CVE-2023-28261, CVE-2024-38208, CVE-2024-29987, CVE-2022-4135, CVE-2023-21796, CVE-2024-5274, CVE-2024-38209, CVE-2026-72970</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0295</t>
+          <t>https://learn.microsoft.com/en-us/deployedge/microsoft-edge-relnotes-security#september-14-2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -527,36 +527,41 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"CVE-2026-0298 GlobalProtect App: Code Execution Vulnerability in Windows Pre-Logon Access Provider (PLAP) (Severity: MEDIUM)"</t>
+          <t>"Cisco Secure Email Gateway and Secure Email and Web Manager Security Hardening Release: September 2026"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CVE-2026-0298</t>
+          <t>CVE-2026-20353, CVE-2026-76443, CVE-2026-76441, CVE-2026-76440, CVE-2026-76442</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0298</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-hardening-esa-dfCrfXkm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -567,36 +572,41 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/publicationListing.x</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"CVE-2026-0250 GlobalProtect App: Buffer Overflow Vulnerability during connection to Portal or Gateway (Severity: MEDIUM)"</t>
+          <t>"Cisco Secure Email Gateway SQL Injection Vulnerability"</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CVE-2026-0250</t>
+          <t>CVE-2026-76461</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0250</t>
+          <t>https://sec.cloudapps.cisco.com/security/center/content/CiscoSecurityAdvisory/cisco-sa-esa-inj-2bLVGmhX</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -607,36 +617,36 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://support.apple.com/en-us/100100</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"CVE-2026-0299 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
+          <t>"iOS 26.7 and iPadOS 26.7"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CVE-2026-0299</t>
+          <t>CVE-2026-86869, CVE-2026-84598, CVE-2026-84621, CVE-2026-65344, CVE-2026-43715, CVE-2026-43664, CVE-2026-86882, CVE-2026-86887, CVE-2026-84607, CVE-2026-84617, CVE-2026-84524, CVE-2026-65402, CVE-2026-84523, CVE-2026-43689, CVE-2026-43743, CVE-2026-84491, CVE-2026-84487, CVE-2026-84546, CVE-2026-65412, CVE-2026-65399, CVE-2026-84564, CVE-2026-28968, CVE-2026-65407, CVE-2026-65359, CVE-2026-65345, CVE-2026-84630, CVE-2026-84566, CVE-2026-86904, CVE-2026-28966, CVE-2026-65411, CVE-2026-84622, CVE-2026-64718, CVE-2026-65360, CVE-2026-43661, CVE-2026-84624, CVE-2026-84507, CVE-2026-86897, CVE-2026-84623, CVE-2026-84561, CVE-2026-84519, CVE-2026-84602, CVE-2026-84492, CVE-2026-65414, CVE-2026-65395, CVE-2026-65408, CVE-2026-86886, CVE-2026-84620, CVE-2026-86881, CVE-2026-65377, CVE-2026-65409, CVE-2026-65403, CVE-2026-43684, CVE-2026-84497, CVE-2026-65405, CVE-2026-84513, CVE-2026-84532, CVE-2026-84521, CVE-2026-43687, CVE-2026-86892, CVE-2026-86924, CVE-2026-84583, CVE-2026-86870, CVE-2026-86876, CVE-2026-84534, CVE-2026-84615, CVE-2026-84510, CVE-2026-84612, CVE-2026-86890, CVE-2026-65410, CVE-2026-84530, CVE-2026-43686, CVE-2026-84626, CVE-2026-84632, CVE-2026-43702, CVE-2026-84611, CVE-2026-84552, CVE-2026-65406, CVE-2026-43737, CVE-2026-64758, CVE-2026-84616, CVE-2026-65348, CVE-2026-84526</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0299</t>
+          <t>https://support.apple.com/en-us/149041</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -647,36 +657,36 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://support.apple.com/en-us/100100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"CVE-2026-0297 GlobalProtect App: Buffer Overflow Vulnerability during UDP Tunnel Handshake (Severity: MEDIUM)"</t>
+          <t>"macOS Tahoe 26.7"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CVE-2026-0297</t>
+          <t>CVE-2026-84573, CVE-2026-86888, CVE-2026-84581, CVE-2026-84517, CVE-2026-84609, CVE-2026-84621, CVE-2026-65344, CVE-2026-84525, CVE-2026-20683, CVE-2026-43787, CVE-2026-84570, CVE-2026-43664, CVE-2026-86882, CVE-2026-43677, CVE-2026-64756, CVE-2026-84580, CVE-2026-43760, CVE-2026-84607, CVE-2026-84506, CVE-2026-65369, CVE-2026-84617, CVE-2026-65381, CVE-2026-84524, CVE-2026-84618, CVE-2026-65361, CVE-2026-84553, CVE-2026-65402, CVE-2026-84523, CVE-2026-84574, CVE-2026-84514, CVE-2026-43692, CVE-2026-84578, CVE-2026-84540, CVE-2026-43743, CVE-2026-43785, CVE-2026-84487, CVE-2026-43786, CVE-2026-84546, CVE-2026-86891, CVE-2026-65412, CVE-2026-65399, CVE-2026-84564, CVE-2026-65358, CVE-2026-28968, CVE-2026-65407, CVE-2026-65359, CVE-2026-65345, CVE-2026-65413, CVE-2026-84576, CVE-2026-65374, CVE-2026-84630, CVE-2026-43763, CVE-2026-86889, CVE-2026-65376, CVE-2026-84566, CVE-2026-84505, CVE-2026-43791, CVE-2026-43789, CVE-2026-28966, CVE-2026-84622, CVE-2026-84559, CVE-2026-84537, CVE-2026-65360, CVE-2026-43697, CVE-2026-84509, CVE-2026-84536, CVE-2026-84516, CVE-2026-84624, CVE-2026-84507, CVE-2026-84541, CVE-2026-43741, CVE-2026-84561, CVE-2026-65342, CVE-2026-84519, CVE-2026-84535, CVE-2026-84602, CVE-2026-84492, CVE-2026-43790, CVE-2026-65414, CVE-2026-65395, CVE-2026-86910, CVE-2026-84587, CVE-2026-28934, CVE-2026-65408, CVE-2026-84550, CVE-2026-84549, CVE-2026-84620, CVE-2026-86881, CVE-2026-65377, CVE-2026-84567, CVE-2026-65409, CVE-2026-65365, CVE-2026-84515, CVE-2026-65400, CVE-2026-84563, CVE-2026-65403, CVE-2026-43695, CVE-2026-84497, CVE-2026-84577, CVE-2026-65405, CVE-2026-84513, CVE-2026-84532, CVE-2022-3437, CVE-2026-65362, CVE-2026-84619, CVE-2026-84521, CVE-2026-43683, CVE-2026-43687, CVE-2026-86924, CVE-2026-84538, CVE-2026-84583, CVE-2026-43690, CVE-2026-86876, CVE-2026-84534, CVE-2026-84575, CVE-2026-28899, CVE-2026-84510, CVE-2026-84612, CVE-2026-28969, CVE-2026-65401, CVE-2026-65410, CVE-2026-84544, CVE-2026-84511, CVE-2026-64712, CVE-2026-65364, CVE-2026-86917, CVE-2026-84512, CVE-2026-84568, CVE-2026-84530, CVE-2026-43686, CVE-2026-84626, CVE-2026-84632, CVE-2026-43702, CVE-2026-84611, CVE-2026-84527, CVE-2026-64790, CVE-2026-84552, CVE-2026-65406, CVE-2026-84565, CVE-2026-43691, CVE-2026-84554, CVE-2026-84572, CVE-2026-84543, CVE-2026-43737, CVE-2026-84556, CVE-2026-84548, CVE-2026-65382, CVE-2026-84616, CVE-2026-65378, CVE-2026-43698, CVE-2026-65348, CVE-2026-43719, CVE-2026-84526</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0297</t>
+          <t>https://support.apple.com/en-us/149042</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -687,36 +697,36 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/rss.xml</t>
+          <t>https://support.apple.com/en-us/100100</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"CVE-2026-0296 GlobalProtect App: Improper Certificate Validation Bypass Vulnerability (Severity: MEDIUM)"</t>
+          <t>"iOS 27 and iPadOS 27"</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>""""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CVE-2026-0296</t>
+          <t>CVE-2026-86888, CVE-2026-65329, CVE-2026-84598, CVE-2026-84609, CVE-2026-84621, CVE-2026-65344, CVE-2026-84518, CVE-2026-20683, CVE-2026-43664, CVE-2026-86882, CVE-2026-64756, CVE-2026-86887, CVE-2026-84607, CVE-2026-84617, CVE-2026-84524, CVE-2026-64752, CVE-2026-65402, CVE-2026-86898, CVE-2026-84523, CVE-2026-43689, CVE-2026-43785, CVE-2026-84489, CVE-2026-43738, CVE-2026-84629, CVE-2026-84491, CVE-2026-84487, CVE-2026-84571, CVE-2026-84533, CVE-2026-84546, CVE-2026-84635, CVE-2026-65412, CVE-2026-65399, CVE-2026-84564, CVE-2026-65358, CVE-2026-28968, CVE-2026-65407, CVE-2026-65359, CVE-2026-65345, CVE-2026-84593, CVE-2026-84630, CVE-2026-84596, CVE-2026-64760, CVE-2026-84566, CVE-2026-86904, CVE-2026-28966, CVE-2026-86879, CVE-2026-65411, CVE-2026-84622, CVE-2026-64718, CVE-2026-84600, CVE-2026-86878, CVE-2026-65360, CVE-2026-84624, CVE-2026-84507, CVE-2026-86897, CVE-2026-65354, CVE-2026-84623, CVE-2026-84561, CVE-2026-84519, CVE-2026-84602, CVE-2026-84492, CVE-2026-65414, CVE-2026-65395, CVE-2026-86895, CVE-2026-84625, CVE-2026-64761, CVE-2026-65408, CVE-2026-86886, CVE-2026-43674, CVE-2026-84620, CVE-2026-86881, CVE-2026-65377, CVE-2026-65409, CVE-2026-65403, CVE-2026-43695, CVE-2026-84497, CVE-2026-65405, CVE-2026-84513, CVE-2026-84532, CVE-2026-84560, CVE-2026-65398, CVE-2026-84628, CVE-2026-84531, CVE-2026-86883, CVE-2026-84521, CVE-2026-43687, CVE-2026-86892, CVE-2026-86924, CVE-2026-84583, CVE-2026-86870, CVE-2026-86876, CVE-2026-84534, CVE-2026-86893, CVE-2026-84615, CVE-2026-43688, CVE-2026-84575, CVE-2026-84510, CVE-2026-84612, CVE-2026-28969, CVE-2026-86890, CVE-2026-65410, CVE-2026-65415, CVE-2026-86903, CVE-2026-84511, CVE-2026-65404, CVE-2026-86905, CVE-2026-86884, CVE-2026-84603, CVE-2026-84530, CVE-2026-43686, CVE-2026-84626, CVE-2026-84632, CVE-2026-64753, CVE-2026-84611, CVE-2026-84527, CVE-2026-84552, CVE-2026-84636, CVE-2026-65406, CVE-2026-84551, CVE-2026-86885, CVE-2026-43737, CVE-2026-84597, CVE-2026-84616, CVE-2026-65348, CVE-2026-84526, CVE-2026-84606</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://security.paloaltonetworks.com/CVE-2026-0296</t>
+          <t>https://support.apple.com/en-us/149034</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -727,36 +737,36 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.apple.com/en-us/100100</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"CVE-2026-70334 Visual Studio Code Security Feature Bypass Vulnerability"</t>
+          <t>"macOS Golden Gate 27"</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>""Acknowledgement Updated""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CVE-2026-70334</t>
+          <t>CVE-2026-84573, CVE-2026-86888, CVE-2026-86869, CVE-2026-84581, CVE-2026-84517, CVE-2026-84609, CVE-2026-84621, CVE-2026-65344, CVE-2026-84525, CVE-2026-84518, CVE-2026-20683, CVE-2026-43787, CVE-2026-84570, CVE-2026-43664, CVE-2026-86882, CVE-2026-43677, CVE-2026-64756, CVE-2026-86911, CVE-2026-84580, CVE-2026-84555, CVE-2026-84584, CVE-2026-84607, CVE-2026-84506, CVE-2026-65369, CVE-2026-84617, CVE-2026-65381, CVE-2026-84524, CVE-2026-84618, CVE-2026-84585, CVE-2026-65361, CVE-2026-84553, CVE-2026-64752, CVE-2026-65402, CVE-2026-86898, CVE-2026-84523, CVE-2026-84574, CVE-2026-43689, CVE-2026-43692, CVE-2026-84514, CVE-2026-84540, CVE-2026-84578, CVE-2026-43785, CVE-2026-84489, CVE-2026-43738, CVE-2026-84491, CVE-2026-84487, CVE-2026-43786, CVE-2026-84571, CVE-2026-84533, CVE-2026-84546, CVE-2026-86891, CVE-2026-84635, CVE-2026-65412, CVE-2026-65399, CVE-2026-65375, CVE-2026-84564, CVE-2026-86900, CVE-2026-65358, CVE-2026-28968, CVE-2026-65407, CVE-2026-65359, CVE-2026-65345, CVE-2026-65383, CVE-2026-65413, CVE-2026-84576, CVE-2026-65374, CVE-2026-84630, CVE-2026-84586, CVE-2026-86889, CVE-2026-65376, CVE-2026-84596, CVE-2026-64760, CVE-2026-84566, CVE-2026-43696, CVE-2026-84505, CVE-2026-43791, CVE-2026-43789, CVE-2026-28966, CVE-2026-64714, CVE-2026-43788, CVE-2026-84622, CVE-2026-84559, CVE-2026-64718, CVE-2026-84600, CVE-2026-84537, CVE-2026-65360, CVE-2026-43697, CVE-2026-84509, CVE-2026-84536, CVE-2026-84516, CVE-2026-84624, CVE-2026-86909, CVE-2026-84507, CVE-2026-86897, CVE-2026-65354, CVE-2026-84541, CVE-2026-43741, CVE-2026-84561, CVE-2026-65342, CVE-2026-84519, CVE-2026-84535, CVE-2026-84602, CVE-2026-84520, CVE-2026-84492, CVE-2026-43790, CVE-2026-65414, CVE-2026-65395, CVE-2026-84625, CVE-2026-86910, CVE-2026-84587, CVE-2026-84558, CVE-2026-28934, CVE-2026-65408, CVE-2026-84550, CVE-2026-84549, CVE-2026-84620, CVE-2026-86881, CVE-2026-65377, CVE-2026-84567, CVE-2026-65409, CVE-2026-65365, CVE-2026-84515, CVE-2026-65400, CVE-2026-84563, CVE-2026-65403, CVE-2026-43695, CVE-2026-43684, CVE-2026-84497, CVE-2026-84577, CVE-2026-65405, CVE-2026-84513, CVE-2026-84522, CVE-2026-84532, CVE-2026-84560, CVE-2022-3437, CVE-2026-65398, CVE-2026-86894, CVE-2026-84628, CVE-2026-65393, CVE-2026-84531, CVE-2026-65362, CVE-2026-84619, CVE-2026-84521, CVE-2026-43683, CVE-2026-84588, CVE-2026-43687, CVE-2026-86901, CVE-2026-86924, CVE-2026-34979, CVE-2026-84538, CVE-2026-84583, CVE-2026-86870, CVE-2026-86902, CVE-2026-43690, CVE-2026-86876, CVE-2026-84534, CVE-2026-65380, CVE-2026-43688, CVE-2026-84575, CVE-2026-84569, CVE-2026-84510, CVE-2026-28899, CVE-2026-84612, CVE-2026-28969, CVE-2026-65401, CVE-2026-65410, CVE-2026-65415, CVE-2026-86903, CVE-2026-84544, CVE-2026-84511, CVE-2026-64712, CVE-2026-65404, CVE-2026-65364, CVE-2026-86905, CVE-2026-86917, CVE-2026-84589, CVE-2026-86884, CVE-2026-84512, CVE-2026-84568, CVE-2026-84530, CVE-2026-43686, CVE-2026-84626, CVE-2026-84632, CVE-2026-64753, CVE-2026-84611, CVE-2026-84527, CVE-2026-64790, CVE-2026-84552, CVE-2026-65406, CVE-2026-84565, CVE-2026-43691, CVE-2026-84554, CVE-2026-84572, CVE-2026-84551, CVE-2026-84631, CVE-2026-43737, CVE-2026-84543, CVE-2026-84556, CVE-2026-84548, CVE-2026-84597, CVE-2026-65382, CVE-2026-84616, CVE-2026-65378, CVE-2026-28937, CVE-2026-43698, CVE-2026-84601, CVE-2026-65348, CVE-2026-43719, CVE-2026-84526, CVE-2026-84606</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-70334</t>
+          <t>https://support.apple.com/en-us/149035</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -767,36 +777,36 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://support.apple.com/en-us/100100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76023:Improper resource control in Linux Toolkit Theming"</t>
+          <t>"macOS Sequoia 15.8"</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CVE-2026-76023</t>
+          <t>CVE-2026-84573, CVE-2026-28935, CVE-2026-84581, CVE-2026-84517, CVE-2026-84609, CVE-2026-84621, CVE-2026-65344, CVE-2026-84525, CVE-2026-20683, CVE-2026-43787, CVE-2026-84570, CVE-2026-43664, CVE-2026-86882, CVE-2026-43677, CVE-2026-64756, CVE-2026-84580, CVE-2026-84555, CVE-2026-84607, CVE-2026-84506, CVE-2026-65369, CVE-2026-84617, CVE-2026-65381, CVE-2026-84524, CVE-2026-84618, CVE-2026-65361, CVE-2026-84553, CVE-2026-65402, CVE-2026-84523, CVE-2026-84574, CVE-2026-84514, CVE-2026-43692, CVE-2026-84578, CVE-2026-84540, CVE-2026-43785, CVE-2026-84487, CVE-2026-43786, CVE-2026-84546, CVE-2026-86891, CVE-2026-65412, CVE-2026-65399, CVE-2026-65375, CVE-2026-84564, CVE-2026-65358, CVE-2026-28968, CVE-2026-65407, CVE-2026-65359, CVE-2026-65345, CVE-2026-65413, CVE-2026-84576, CVE-2026-65374, CVE-2026-84630, CVE-2026-43763, CVE-2026-86889, CVE-2026-65376, CVE-2026-84566, CVE-2026-84505, CVE-2026-43791, CVE-2026-43789, CVE-2026-28966, CVE-2026-84622, CVE-2026-84559, CVE-2026-84537, CVE-2026-65360, CVE-2026-43697, CVE-2026-84509, CVE-2026-84536, CVE-2026-84516, CVE-2026-84624, CVE-2026-65346, CVE-2026-84507, CVE-2026-65330, CVE-2026-65339, CVE-2026-84541, CVE-2026-43741, CVE-2026-84561, CVE-2026-65342, CVE-2026-28930, CVE-2026-84519, CVE-2026-84535, CVE-2026-84602, CVE-2026-84492, CVE-2026-43790, CVE-2026-65414, CVE-2026-65395, CVE-2026-86910, CVE-2026-84587, CVE-2026-28934, CVE-2026-65408, CVE-2026-84550, CVE-2026-84549, CVE-2026-84620, CVE-2026-86881, CVE-2026-65377, CVE-2026-84567, CVE-2026-65409, CVE-2026-65365, CVE-2026-84515, CVE-2026-84563, CVE-2026-65403, CVE-2026-43695, CVE-2026-43684, CVE-2026-84497, CVE-2026-65405, CVE-2026-84513, CVE-2026-84532, CVE-2022-3437, CVE-2026-64736, CVE-2026-65362, CVE-2026-84619, CVE-2026-84521, CVE-2026-43683, CVE-2026-84538, CVE-2026-84583, CVE-2026-43690, CVE-2026-86876, CVE-2026-84534, CVE-2026-65349, CVE-2026-84575, CVE-2026-84510, CVE-2026-28899, CVE-2026-84612, CVE-2026-28969, CVE-2026-84544, CVE-2026-84511, CVE-2026-64712, CVE-2026-65364, CVE-2026-86917, CVE-2026-84512, CVE-2026-84568, CVE-2026-65371, CVE-2026-43686, CVE-2026-84626, CVE-2026-84632, CVE-2026-43702, CVE-2026-84611, CVE-2026-84527, CVE-2026-64790, CVE-2026-84552, CVE-2026-65406, CVE-2026-84565, CVE-2026-43691, CVE-2026-84554, CVE-2026-84572, CVE-2026-84543, CVE-2026-43737, CVE-2026-64758, CVE-2026-84556, CVE-2026-84548, CVE-2026-65382, CVE-2026-84616, CVE-2026-65378, CVE-2026-65348, CVE-2026-43719, CVE-2026-84526</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76023</t>
+          <t>https://support.apple.com/en-us/149043</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -807,36 +817,36 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"CVE-2026-69314 Windows Device Association Broker Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-0295 GlobalProtect App: Local Privilege Escalation via Race Condition on macOS (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CVE-2026-69314</t>
+          <t>CVE-2026-0295</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69314</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0295</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -847,36 +857,36 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>"CVE-2026-77490 Microsoft Edge (Chromium-based) Spoofing Vulnerability"</t>
+          <t>"CVE-2026-0298 GlobalProtect App: Code Execution Vulnerability in Windows Pre-Logon Access Provider (PLAP) (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>""Improper neutralization of input during web page generation ('cross-site scripting') in Microsoft Edge (Chromium-based) allows an unauthorized attacker to perform spoofing over a network.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CVE-2026-77490</t>
+          <t>CVE-2026-0298</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77490</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0298</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -887,36 +897,36 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76018:Privilege elevation in Import"</t>
+          <t>"CVE-2026-0250 GlobalProtect App: Buffer Overflow Vulnerability during connection to Portal or Gateway (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CVE-2026-76018</t>
+          <t>CVE-2026-0250</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76018</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0250</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -927,36 +937,36 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"CVE-2026-62799 Windows SMB Client Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-0299 GlobalProtect App: Local Privilege Escalation Vulnerabilities (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CVE-2026-62799</t>
+          <t>CVE-2026-0299</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62799</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0299</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -967,36 +977,36 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"CVE-2026-73016 DirectWrite Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-0297 GlobalProtect App: Buffer Overflow Vulnerability during UDP Tunnel Handshake (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CVE-2026-73016</t>
+          <t>CVE-2026-0297</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73016</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0297</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1007,36 +1017,36 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Microsoft Edge</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://api.msrc.microsoft.com/update-guide/rss</t>
+          <t>https://security.paloaltonetworks.com/rss.xml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"CVE-2026-69860 Windows Imaging Component Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-0296 GlobalProtect App: Improper Certificate Validation Bypass Vulnerability (Severity: MEDIUM)"</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""""</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CVE-2026-69860</t>
+          <t>CVE-2026-0296</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69860</t>
+          <t>https://security.paloaltonetworks.com/CVE-2026-0296</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1061,22 +1071,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84333 Use after free in Dawn"</t>
+          <t>"CVE-2026-70334 Visual Studio Code Security Feature Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Acknowledgement Updated""</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CVE-2026-84333</t>
+          <t>CVE-2026-70334</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84333</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-70334</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76036:Buffer overflow in Dawn"</t>
+          <t>"Chromium CVE-2026-76023:Improper resource control in Linux Toolkit Theming"</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1111,12 +1121,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CVE-2026-76036</t>
+          <t>CVE-2026-76023</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76036</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76023</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1141,22 +1151,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85042:Use after free in DevTools"</t>
+          <t>"CVE-2026-69314 Windows Device Association Broker Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CVE-2026-85042</t>
+          <t>CVE-2026-69314</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85042</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69314</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1181,22 +1191,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85049:Use after free in Skia"</t>
+          <t>"CVE-2026-77490 Microsoft Edge (Chromium-based) Spoofing Vulnerability"</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Improper neutralization of input during web page generation ('cross-site scripting') in Microsoft Edge (Chromium-based) allows an unauthorized attacker to perform spoofing over a network.""</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CVE-2026-85049</t>
+          <t>CVE-2026-77490</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85049</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77490</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1221,22 +1231,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"CVE-2026-81963 Windows Update Stack Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-76018:Privilege elevation in Import"</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CVE-2026-81963</t>
+          <t>CVE-2026-76018</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81963</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76018</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1261,7 +1271,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"CVE-2026-77499 Windows DHCP Server Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-62799 Windows SMB Client Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1271,12 +1281,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CVE-2026-77499</t>
+          <t>CVE-2026-62799</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77499</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-62799</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1301,7 +1311,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>"CVE-2026-80080 Microsoft Office Word Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-73016 DirectWrite Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1311,12 +1321,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CVE-2026-80080</t>
+          <t>CVE-2026-73016</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-80080</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-73016</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1341,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>"CVE-2026-81379 Visual Studio Code Security Feature Bypass Vulnerability"</t>
+          <t>"CVE-2026-69860 Windows Imaging Component Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1351,12 +1361,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CVE-2026-81379</t>
+          <t>CVE-2026-69860</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81379</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69860</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1381,22 +1391,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>"CVE-2026-68894 Windows Error Reporting Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84333 Use after free in Dawn"</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CVE-2026-68894</t>
+          <t>CVE-2026-84333</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68894</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84333</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1421,22 +1431,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>"CVE-2026-69732 Windows Link Layer Topology Discovery Protocol Remote Code Execution Vulnerability"</t>
+          <t>"Chromium CVE-2026-76036:Buffer overflow in Dawn"</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CVE-2026-69732</t>
+          <t>CVE-2026-76036</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69732</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76036</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1461,7 +1471,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85043:Incomplete cleanup in Network"</t>
+          <t>"Chromium CVE-2026-85042:Use after free in DevTools"</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1471,12 +1481,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CVE-2026-85043</t>
+          <t>CVE-2026-85042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85043</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85042</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1501,7 +1511,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85045:Race condition in V8"</t>
+          <t>"Chromium CVE-2026-85049:Use after free in Skia"</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1511,12 +1521,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CVE-2026-85045</t>
+          <t>CVE-2026-85049</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85045</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85049</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1541,7 +1551,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"CVE-2026-81355 Virtual Hard Disk (VHD) Miniport Driver Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-81963 Windows Update Stack Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1551,12 +1561,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CVE-2026-81355</t>
+          <t>CVE-2026-81963</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81355</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81963</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1581,22 +1591,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85051:Type confusion in Compositing"</t>
+          <t>"CVE-2026-77499 Windows DHCP Server Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CVE-2026-85051</t>
+          <t>CVE-2026-77499</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85051</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-77499</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1621,22 +1631,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84352 Use after free in WebGL"</t>
+          <t>"CVE-2026-80080 Microsoft Office Word Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CVE-2026-84352</t>
+          <t>CVE-2026-80080</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84352</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-80080</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1661,7 +1671,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>"CVE-2026-69468 Windows Volume Manager Extension Driver Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-81379 Visual Studio Code Security Feature Bypass Vulnerability"</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1671,12 +1681,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CVE-2026-69468</t>
+          <t>CVE-2026-81379</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69468</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81379</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1701,7 +1711,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"CVE-2026-71336 Windows Work Folder Service Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-68894 Windows Error Reporting Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1711,12 +1721,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CVE-2026-71336</t>
+          <t>CVE-2026-68894</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-71336</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-68894</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1741,22 +1751,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85048:Use after free in Compositing"</t>
+          <t>"CVE-2026-69732 Windows Link Layer Topology Discovery Protocol Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CVE-2026-85048</t>
+          <t>CVE-2026-69732</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85048</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69732</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1781,7 +1791,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76021:Use after free in DOM"</t>
+          <t>"Chromium CVE-2026-85043:Incomplete cleanup in Network"</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1791,12 +1801,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CVE-2026-76021</t>
+          <t>CVE-2026-85043</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76021</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85043</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1821,7 +1831,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85052:Out of bounds read in CrashReporting"</t>
+          <t>"Chromium CVE-2026-85045:Race condition in V8"</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1831,12 +1841,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CVE-2026-85052</t>
+          <t>CVE-2026-85045</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85052</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85045</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1861,7 +1871,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>"CVE-2026-50676 Windows Media Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-81355 Virtual Hard Disk (VHD) Miniport Driver Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1871,12 +1881,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CVE-2026-50676</t>
+          <t>CVE-2026-81355</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50676</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-81355</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1901,7 +1911,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-85053:Improper resource exposure in CacheStorage"</t>
+          <t>"Chromium CVE-2026-85051:Type confusion in Compositing"</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1911,12 +1921,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CVE-2026-85053</t>
+          <t>CVE-2026-85051</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85053</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85051</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1941,22 +1951,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>"CVE-2026-69461 Windows NTFS Remote Code Execution Vulnerability"</t>
+          <t>"Chromium: CVE-2026-84352 Use after free in WebGL"</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CVE-2026-69461</t>
+          <t>CVE-2026-84352</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69461</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84352</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1981,7 +1991,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>"CVE-2026-54124 Windows Terminal Remote Code Execution Vulnerability"</t>
+          <t>"CVE-2026-69468 Windows Volume Manager Extension Driver Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1991,12 +2001,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CVE-2026-54124</t>
+          <t>CVE-2026-69468</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54124</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69468</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2021,7 +2031,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"CVE-2026-69405 Windows DHCP Server Denial of Service Vulnerability"</t>
+          <t>"CVE-2026-71336 Windows Work Folder Service Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2031,12 +2041,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CVE-2026-69405</t>
+          <t>CVE-2026-71336</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69405</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-71336</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2061,22 +2071,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>"CVE-2026-61349 Windows Work Folder Service Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85048:Use after free in Compositing"</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CVE-2026-61349</t>
+          <t>CVE-2026-85048</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-61349</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85048</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2101,7 +2111,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76017:Use after free in Chromoting"</t>
+          <t>"Chromium CVE-2026-76021:Use after free in DOM"</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2111,12 +2121,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CVE-2026-76017</t>
+          <t>CVE-2026-76021</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76017</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76021</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2141,22 +2151,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>"CVE-2026-54112 Windows Win32k Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-85052:Out of bounds read in CrashReporting"</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>""Updated an acknowledgement. This is an informational change only.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CVE-2026-54112</t>
+          <t>CVE-2026-85052</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54112</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85052</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,7 +2191,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>"CVE-2026-50679 Windows Search Service Elevation of Privilege Vulnerability"</t>
+          <t>"CVE-2026-50676 Windows Media Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2191,12 +2201,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CVE-2026-50679</t>
+          <t>CVE-2026-50676</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50679</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-50676</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2221,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76022:Buffer overflow in Network"</t>
+          <t>"Chromium CVE-2026-85053:Improper resource exposure in CacheStorage"</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2231,12 +2241,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CVE-2026-76022</t>
+          <t>CVE-2026-85053</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76022</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-85053</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2261,22 +2271,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76019:Incorrect authorization in Workers"</t>
+          <t>"CVE-2026-69461 Windows NTFS Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CVE-2026-76019</t>
+          <t>CVE-2026-69461</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76019</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69461</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2301,22 +2311,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-76039:Incorrect reference resolution in Core"</t>
+          <t>"CVE-2026-54124 Windows Terminal Remote Code Execution Vulnerability"</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CVE-2026-76039</t>
+          <t>CVE-2026-54124</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-76039</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-54124</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2341,22 +2351,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>"Chromium: CVE-2026-84330 UI misrepresentation in FullScreen"</t>
+          <t>"CVE-2026-69405 Windows DHCP Server Denial of Service Vulnerability"</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CVE-2026-84330</t>
+          <t>CVE-2026-69405</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-84330</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-69405</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2381,22 +2391,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>"Chromium CVE-2026-87491:Out of bounds write in V8"</t>
+          <t>"CVE-2026-61349 Windows Work Folder Service Elevation of Privilege Vulnerability"</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com/2026) for more information. Google is aware that an exploit for CVE-2026-87491 exists in the wild.""</t>
+          <t>""Updated an acknowledgement. This is an informational change only.""</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CVE-2026-87491</t>
+          <t>CVE-2026-61349</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-87491</t>
+          <t>https://msrc.microsoft.com/update-guide/vulnerability/CVE-2026-61349</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2421,22 +2431,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>"CVE-2026-85892 Microsoft Edge (Chromium-based) Elevation of Privilege Vulnerability"</t>
+          <t>"Chromium CVE-2026-76017:Use after free in Chromoting"</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>""Concurrent execution using shared resource with improper synchronization ('race condition') in Microsoft Edge (Chromium-based) allows an authorized attacker to elevate privileges locally.""</t>
+          <t>""This CVE was assigned by Chrome. Microsoft Edge (Chromium-based) ingests Chromium, which addresses this vulnerability. Please see [Google Chrome Releases](https://chromereleases.googleblog.com